--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916285</v>
+        <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>92609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655855</v>
+        <v>655893</v>
       </c>
       <c r="R3" t="n">
-        <v>7122774</v>
+        <v>7122779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126918405</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
+        <v>77989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655901</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916314</v>
+        <v>126916285</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>78770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655893</v>
+        <v>655855</v>
       </c>
       <c r="R5" t="n">
-        <v>7122779</v>
+        <v>7122774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126910130</v>
+        <v>126914199</v>
       </c>
       <c r="B6" t="n">
-        <v>79569</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,37 +1101,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655841</v>
+        <v>655888</v>
       </c>
       <c r="R6" t="n">
-        <v>7122800</v>
+        <v>7122973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,9 +1158,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,12 +1185,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1191,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916842</v>
+        <v>126916284</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655948</v>
+        <v>655943</v>
       </c>
       <c r="R7" t="n">
-        <v>7122908</v>
+        <v>7122816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,19 +1269,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,12 +1286,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126914199</v>
+        <v>126910394</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655888</v>
+        <v>655885</v>
       </c>
       <c r="R8" t="n">
-        <v>7122973</v>
+        <v>7122738</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,19 +1370,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,12 +1387,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126916284</v>
+        <v>126910130</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655943</v>
+        <v>655841</v>
       </c>
       <c r="R9" t="n">
-        <v>7122816</v>
+        <v>7122800</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,45 +1504,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918405</v>
+        <v>126916842</v>
       </c>
       <c r="B10" t="n">
-        <v>77929</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655901</v>
+        <v>655948</v>
       </c>
       <c r="R10" t="n">
-        <v>7122844</v>
+        <v>7122908</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,9 +1577,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916316</v>
+        <v>126919792</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655863</v>
+        <v>655919</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1693,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1705,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1721,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916306</v>
+        <v>126918646</v>
       </c>
       <c r="B12" t="n">
-        <v>78647</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,21 +1737,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655956</v>
+        <v>656298</v>
       </c>
       <c r="R12" t="n">
-        <v>7122866</v>
+        <v>7122812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1811,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,32 +1827,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916844</v>
+        <v>126916316</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655905</v>
+        <v>655863</v>
       </c>
       <c r="R13" t="n">
-        <v>7122985</v>
+        <v>7122755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,21 +1895,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1913,36 +1908,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1953,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126918421</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>92802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>655890</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2054,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918421</v>
+        <v>126916306</v>
       </c>
       <c r="B15" t="n">
-        <v>92727</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,21 +2040,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655890</v>
+        <v>655956</v>
       </c>
       <c r="R15" t="n">
-        <v>7122888</v>
+        <v>7122866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,12 +2114,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2155,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918646</v>
+        <v>126918044</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,34 +2141,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656298</v>
+        <v>656088</v>
       </c>
       <c r="R16" t="n">
-        <v>7122812</v>
+        <v>7122850</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,15 +2212,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2256,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916278</v>
+        <v>126916299</v>
       </c>
       <c r="B17" t="n">
-        <v>79569</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655957</v>
+        <v>655995</v>
       </c>
       <c r="R17" t="n">
-        <v>7122864</v>
+        <v>7122921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,32 +2347,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126919792</v>
+        <v>126916844</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655919</v>
+        <v>655905</v>
       </c>
       <c r="R18" t="n">
-        <v>7122887</v>
+        <v>7122985</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,14 +2415,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spilning</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,16 +2438,36 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2463,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126909344</v>
+        <v>126916278</v>
       </c>
       <c r="B19" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655890</v>
+        <v>655957</v>
       </c>
       <c r="R19" t="n">
-        <v>7122814</v>
+        <v>7122864</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2548,12 +2563,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2564,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918044</v>
+        <v>126917770</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,34 +2590,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656088</v>
+        <v>655852</v>
       </c>
       <c r="R20" t="n">
-        <v>7122850</v>
+        <v>7122942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,30 +2661,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126917770</v>
+        <v>126909344</v>
       </c>
       <c r="B21" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655852</v>
+        <v>655890</v>
       </c>
       <c r="R21" t="n">
-        <v>7122942</v>
+        <v>7122814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918039</v>
+        <v>126918439</v>
       </c>
       <c r="B22" t="n">
-        <v>79569</v>
+        <v>79629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,34 +2792,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655917</v>
+        <v>655882</v>
       </c>
       <c r="R22" t="n">
-        <v>7122980</v>
+        <v>7122978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,30 +2863,15 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2900,7 +2885,7 @@
         <v>126910226</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +2986,7 @@
         <v>126917790</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3099,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126918439</v>
+        <v>126918039</v>
       </c>
       <c r="B25" t="n">
-        <v>79598</v>
+        <v>79600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3110,34 +3095,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655882</v>
+        <v>655917</v>
       </c>
       <c r="R25" t="n">
-        <v>7122978</v>
+        <v>7122980</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,15 +3166,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3200,32 +3200,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126916397</v>
+        <v>126917813</v>
       </c>
       <c r="B26" t="n">
-        <v>92535</v>
+        <v>78769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655893</v>
+        <v>655710</v>
       </c>
       <c r="R26" t="n">
-        <v>7122752</v>
+        <v>7122853</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917813</v>
+        <v>126918712</v>
       </c>
       <c r="B27" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655710</v>
+        <v>655899</v>
       </c>
       <c r="R27" t="n">
-        <v>7122853</v>
+        <v>7122835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126910403</v>
+        <v>126918424</v>
       </c>
       <c r="B28" t="n">
-        <v>79569</v>
+        <v>92802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655885</v>
+        <v>655961</v>
       </c>
       <c r="R28" t="n">
-        <v>7122738</v>
+        <v>7122865</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918712</v>
+        <v>126916397</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>92609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655899</v>
+        <v>655893</v>
       </c>
       <c r="R29" t="n">
-        <v>7122835</v>
+        <v>7122752</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918424</v>
+        <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>92727</v>
+        <v>79600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655961</v>
+        <v>655885</v>
       </c>
       <c r="R30" t="n">
-        <v>7122865</v>
+        <v>7122738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R31" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R32" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3910,7 +3910,7 @@
         <v>126916289</v>
       </c>
       <c r="B33" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>126918458</v>
       </c>
       <c r="B34" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918438</v>
+        <v>126918037</v>
       </c>
       <c r="B35" t="n">
-        <v>78739</v>
+        <v>79600</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,34 +4120,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655882</v>
+        <v>655903</v>
       </c>
       <c r="R35" t="n">
-        <v>7122978</v>
+        <v>7122984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4191,15 +4191,30 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4210,32 +4225,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126916746</v>
+        <v>126918438</v>
       </c>
       <c r="B36" t="n">
-        <v>91819</v>
+        <v>78770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4245,10 +4260,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655785</v>
+        <v>655882</v>
       </c>
       <c r="R36" t="n">
-        <v>7122898</v>
+        <v>7122978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,22 +4310,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126917804</v>
+        <v>126919804</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>78770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4337,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4361,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655834</v>
+        <v>655989</v>
       </c>
       <c r="R37" t="n">
-        <v>7122923</v>
+        <v>7122922</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4411,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4411,7 +4430,7 @@
         <v>126916287</v>
       </c>
       <c r="B38" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4509,32 +4528,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919804</v>
+        <v>126916746</v>
       </c>
       <c r="B39" t="n">
-        <v>78739</v>
+        <v>91893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4563,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655989</v>
+        <v>655785</v>
       </c>
       <c r="R39" t="n">
-        <v>7122922</v>
+        <v>7122898</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,26 +4613,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>126920137</v>
       </c>
       <c r="B40" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4711,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126918037</v>
+        <v>126917804</v>
       </c>
       <c r="B41" t="n">
-        <v>79569</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4722,34 +4737,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655903</v>
+        <v>655834</v>
       </c>
       <c r="R41" t="n">
-        <v>7122984</v>
+        <v>7122923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4793,30 +4808,15 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126917830</v>
+        <v>126916304</v>
       </c>
       <c r="B42" t="n">
-        <v>78386</v>
+        <v>78678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655749</v>
+        <v>655978</v>
       </c>
       <c r="R42" t="n">
-        <v>7122779</v>
+        <v>7122825</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4931,7 +4931,7 @@
         <v>126920136</v>
       </c>
       <c r="B43" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126916304</v>
+        <v>126917830</v>
       </c>
       <c r="B44" t="n">
-        <v>78647</v>
+        <v>78417</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655978</v>
+        <v>655749</v>
       </c>
       <c r="R44" t="n">
-        <v>7122825</v>
+        <v>7122779</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917785</v>
+        <v>126916741</v>
       </c>
       <c r="B45" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655776</v>
+        <v>655895</v>
       </c>
       <c r="R45" t="n">
-        <v>7122760</v>
+        <v>7122747</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916741</v>
+        <v>126916272</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655895</v>
+        <v>655957</v>
       </c>
       <c r="R46" t="n">
-        <v>7122747</v>
+        <v>7122864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126918406</v>
+        <v>126917825</v>
       </c>
       <c r="B47" t="n">
-        <v>78739</v>
+        <v>77989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655901</v>
+        <v>655749</v>
       </c>
       <c r="R47" t="n">
-        <v>7122844</v>
+        <v>7122779</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5436,7 +5436,7 @@
         <v>126919790</v>
       </c>
       <c r="B48" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126917825</v>
+        <v>126917785</v>
       </c>
       <c r="B49" t="n">
-        <v>77929</v>
+        <v>78770</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655749</v>
+        <v>655776</v>
       </c>
       <c r="R49" t="n">
-        <v>7122779</v>
+        <v>7122760</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126916272</v>
+        <v>126918406</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655957</v>
+        <v>655901</v>
       </c>
       <c r="R50" t="n">
-        <v>7122864</v>
+        <v>7122844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126915088</v>
+        <v>126918397</v>
       </c>
       <c r="B51" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,34 +5747,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655950</v>
+        <v>655892</v>
       </c>
       <c r="R51" t="n">
-        <v>7122893</v>
+        <v>7122986</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126918672</v>
+        <v>126910294</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655882</v>
+        <v>655845</v>
       </c>
       <c r="R52" t="n">
-        <v>7122787</v>
+        <v>7122750</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126910294</v>
+        <v>126919778</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655845</v>
+        <v>655919</v>
       </c>
       <c r="R53" t="n">
-        <v>7122750</v>
+        <v>7122981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918397</v>
+        <v>126920128</v>
       </c>
       <c r="B54" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655892</v>
+        <v>655942</v>
       </c>
       <c r="R54" t="n">
-        <v>7122986</v>
+        <v>7122804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919778</v>
+        <v>126915088</v>
       </c>
       <c r="B55" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655919</v>
+        <v>655950</v>
       </c>
       <c r="R55" t="n">
-        <v>7122981</v>
+        <v>7122893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126920128</v>
+        <v>126918672</v>
       </c>
       <c r="B56" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655942</v>
+        <v>655882</v>
       </c>
       <c r="R56" t="n">
-        <v>7122804</v>
+        <v>7122787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R57" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,30 +6424,15 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6458,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B58" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6469,34 +6454,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R58" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,15 +6525,30 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126917791</v>
+        <v>126917803</v>
       </c>
       <c r="B59" t="n">
-        <v>78739</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,21 +6570,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656327</v>
+        <v>655792</v>
       </c>
       <c r="R59" t="n">
-        <v>7122772</v>
+        <v>7122889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918045</v>
+        <v>126917763</v>
       </c>
       <c r="B60" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,34 +6671,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656177</v>
+        <v>656241</v>
       </c>
       <c r="R60" t="n">
-        <v>7122815</v>
+        <v>7122853</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6742,30 +6742,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6776,10 +6761,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918047</v>
+        <v>126918041</v>
       </c>
       <c r="B61" t="n">
-        <v>78647</v>
+        <v>92802</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6787,21 +6772,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6796,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656203</v>
+        <v>655965</v>
       </c>
       <c r="R61" t="n">
-        <v>7122806</v>
+        <v>7122890</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6892,10 +6877,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919808</v>
+        <v>126916745</v>
       </c>
       <c r="B62" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,21 +6888,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6927,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655921</v>
+        <v>655840</v>
       </c>
       <c r="R62" t="n">
-        <v>7122999</v>
+        <v>7122839</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6977,48 +6962,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916274</v>
+        <v>126916312</v>
       </c>
       <c r="B63" t="n">
-        <v>79569</v>
+        <v>92609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7028,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656012</v>
+        <v>656104</v>
       </c>
       <c r="R63" t="n">
-        <v>7122821</v>
+        <v>7122796</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7094,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126917763</v>
+        <v>126918047</v>
       </c>
       <c r="B64" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,34 +7086,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656241</v>
+        <v>656203</v>
       </c>
       <c r="R64" t="n">
-        <v>7122853</v>
+        <v>7122806</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,15 +7157,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7195,10 +7191,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126916745</v>
+        <v>126915955</v>
       </c>
       <c r="B65" t="n">
-        <v>78647</v>
+        <v>92635</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,37 +7202,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>655840</v>
+        <v>655885</v>
       </c>
       <c r="R65" t="n">
-        <v>7122839</v>
+        <v>7122754</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7274,28 +7273,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>kristina stenmarck</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918041</v>
+        <v>126916274</v>
       </c>
       <c r="B66" t="n">
-        <v>92727</v>
+        <v>79600</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7303,34 +7307,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>655965</v>
+        <v>656012</v>
       </c>
       <c r="R66" t="n">
-        <v>7122890</v>
+        <v>7122821</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7374,30 +7378,15 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7408,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126915955</v>
+        <v>126917791</v>
       </c>
       <c r="B67" t="n">
-        <v>92561</v>
+        <v>78770</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7419,40 +7408,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>655885</v>
+        <v>656327</v>
       </c>
       <c r="R67" t="n">
-        <v>7122754</v>
+        <v>7122772</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7490,19 +7476,18 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7513,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917803</v>
+        <v>126918045</v>
       </c>
       <c r="B68" t="n">
-        <v>80083</v>
+        <v>78770</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7524,34 +7509,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>655792</v>
+        <v>656177</v>
       </c>
       <c r="R68" t="n">
-        <v>7122889</v>
+        <v>7122815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7595,15 +7580,30 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7614,32 +7614,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126916312</v>
+        <v>126919808</v>
       </c>
       <c r="B69" t="n">
-        <v>92535</v>
+        <v>78770</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>656104</v>
+        <v>655921</v>
       </c>
       <c r="R69" t="n">
-        <v>7122796</v>
+        <v>7122999</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7699,12 +7699,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7715,10 +7715,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918042</v>
+        <v>126918443</v>
       </c>
       <c r="B70" t="n">
-        <v>78386</v>
+        <v>80986</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7726,34 +7726,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655954</v>
+        <v>655875</v>
       </c>
       <c r="R70" t="n">
-        <v>7122886</v>
+        <v>7122959</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7815,12 +7815,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7831,32 +7831,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918422</v>
+        <v>126916315</v>
       </c>
       <c r="B71" t="n">
-        <v>91406</v>
+        <v>92609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655890</v>
+        <v>655879</v>
       </c>
       <c r="R71" t="n">
-        <v>7122888</v>
+        <v>7122817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,12 +7916,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,32 +7932,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917789</v>
+        <v>126918422</v>
       </c>
       <c r="B72" t="n">
-        <v>78739</v>
+        <v>91480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655760</v>
+        <v>655890</v>
       </c>
       <c r="R72" t="n">
-        <v>7122811</v>
+        <v>7122888</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,32 +8033,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126916315</v>
+        <v>126917789</v>
       </c>
       <c r="B73" t="n">
-        <v>92535</v>
+        <v>78770</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655879</v>
+        <v>655760</v>
       </c>
       <c r="R73" t="n">
-        <v>7122817</v>
+        <v>7122811</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,12 +8118,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,45 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918650</v>
+        <v>126918042</v>
       </c>
       <c r="B74" t="n">
-        <v>80112</v>
+        <v>78417</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656291</v>
+        <v>655954</v>
       </c>
       <c r="R74" t="n">
-        <v>7122816</v>
+        <v>7122886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,15 +8216,30 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8235,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918443</v>
+        <v>126918650</v>
       </c>
       <c r="B75" t="n">
-        <v>80955</v>
+        <v>80143</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655875</v>
+        <v>656291</v>
       </c>
       <c r="R75" t="n">
-        <v>7122959</v>
+        <v>7122816</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,30 +8332,15 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126919806</v>
+        <v>126918050</v>
       </c>
       <c r="B76" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,34 +8362,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655917</v>
+        <v>656266</v>
       </c>
       <c r="R76" t="n">
-        <v>7122874</v>
+        <v>7122789</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8433,15 +8433,30 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8452,32 +8467,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126916729</v>
+        <v>126915970</v>
       </c>
       <c r="B77" t="n">
-        <v>56849</v>
+        <v>78769</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,13 +8502,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655892</v>
+        <v>655778</v>
       </c>
       <c r="R77" t="n">
-        <v>7122748</v>
+        <v>7122904</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8523,11 +8538,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8542,12 +8552,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8558,10 +8568,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915963</v>
+        <v>126915964</v>
       </c>
       <c r="B78" t="n">
-        <v>78739</v>
+        <v>80114</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8569,21 +8579,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8593,10 +8603,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655813</v>
+        <v>655800</v>
       </c>
       <c r="R78" t="n">
-        <v>7122846</v>
+        <v>7122929</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8659,45 +8669,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918050</v>
+        <v>126917772</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656266</v>
+        <v>655768</v>
       </c>
       <c r="R79" t="n">
-        <v>7122789</v>
+        <v>7122903</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8741,30 +8751,15 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8775,32 +8770,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918404</v>
+        <v>126916729</v>
       </c>
       <c r="B80" t="n">
-        <v>79569</v>
+        <v>56849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8810,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655901</v>
+        <v>655892</v>
       </c>
       <c r="R80" t="n">
-        <v>7122844</v>
+        <v>7122748</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8848,6 +8843,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8860,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8876,32 +8876,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126917772</v>
+        <v>126919806</v>
       </c>
       <c r="B81" t="n">
-        <v>80112</v>
+        <v>78770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655768</v>
+        <v>655917</v>
       </c>
       <c r="R81" t="n">
-        <v>7122903</v>
+        <v>7122874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8961,12 +8961,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126916286</v>
+        <v>126915963</v>
       </c>
       <c r="B82" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655866</v>
+        <v>655813</v>
       </c>
       <c r="R82" t="n">
-        <v>7122779</v>
+        <v>7122846</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,10 +9078,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915964</v>
+        <v>126916286</v>
       </c>
       <c r="B83" t="n">
-        <v>80083</v>
+        <v>78770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9089,21 +9089,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655800</v>
+        <v>655866</v>
       </c>
       <c r="R83" t="n">
-        <v>7122929</v>
+        <v>7122779</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9163,12 +9163,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126915970</v>
+        <v>126918404</v>
       </c>
       <c r="B84" t="n">
-        <v>78738</v>
+        <v>79600</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,13 +9214,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655778</v>
+        <v>655901</v>
       </c>
       <c r="R84" t="n">
-        <v>7122904</v>
+        <v>7122844</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>126918104</v>
       </c>
       <c r="B85" t="n">
-        <v>92529</v>
+        <v>92603</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918040</v>
+        <v>126918677</v>
       </c>
       <c r="B86" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,34 +9392,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655945</v>
+        <v>655893</v>
       </c>
       <c r="R86" t="n">
-        <v>7122909</v>
+        <v>7122814</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9463,30 +9463,15 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9500,7 +9485,7 @@
         <v>126915959</v>
       </c>
       <c r="B87" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9598,10 +9583,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126916394</v>
+        <v>126918040</v>
       </c>
       <c r="B88" t="n">
-        <v>78738</v>
+        <v>78678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9609,37 +9594,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655798</v>
+        <v>655945</v>
       </c>
       <c r="R88" t="n">
-        <v>7122934</v>
+        <v>7122909</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9677,19 +9662,33 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9700,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126918677</v>
+        <v>126916394</v>
       </c>
       <c r="B89" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9711,21 +9710,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9735,13 +9734,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655893</v>
+        <v>655798</v>
       </c>
       <c r="R89" t="n">
-        <v>7122814</v>
+        <v>7122934</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9779,18 +9778,19 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>92802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9905,7 +9905,7 @@
         <v>126918038</v>
       </c>
       <c r="B91" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10018,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918100</v>
+        <v>126918711</v>
       </c>
       <c r="B92" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,37 +10029,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655957</v>
+        <v>655898</v>
       </c>
       <c r="R92" t="n">
-        <v>7122879</v>
+        <v>7122802</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10103,12 +10103,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,10 +10119,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918423</v>
+        <v>126918100</v>
       </c>
       <c r="B93" t="n">
-        <v>92727</v>
+        <v>78770</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10130,37 +10130,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655881</v>
+        <v>655957</v>
       </c>
       <c r="R93" t="n">
-        <v>7122919</v>
+        <v>7122879</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10204,12 +10204,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10223,7 +10223,7 @@
         <v>126917788</v>
       </c>
       <c r="B94" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10321,32 +10321,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918395</v>
+        <v>126916313</v>
       </c>
       <c r="B95" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>655892</v>
+        <v>656087</v>
       </c>
       <c r="R95" t="n">
-        <v>7122986</v>
+        <v>7122806</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126914201</v>
+        <v>126918713</v>
       </c>
       <c r="B96" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,37 +10433,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655947</v>
+        <v>656004</v>
       </c>
       <c r="R96" t="n">
-        <v>7122837</v>
+        <v>7122974</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10490,19 +10490,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10517,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10536,7 +10526,7 @@
         <v>126918681</v>
       </c>
       <c r="B97" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10634,32 +10624,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126916313</v>
+        <v>126918395</v>
       </c>
       <c r="B98" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10669,10 +10659,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656087</v>
+        <v>655892</v>
       </c>
       <c r="R98" t="n">
-        <v>7122806</v>
+        <v>7122986</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10719,12 +10709,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10738,7 +10728,7 @@
         <v>126916276</v>
       </c>
       <c r="B99" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10836,10 +10826,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918713</v>
+        <v>126914201</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>79600</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10847,37 +10837,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656004</v>
+        <v>655947</v>
       </c>
       <c r="R100" t="n">
-        <v>7122974</v>
+        <v>7122837</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10904,9 +10894,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10940,7 +10940,7 @@
         <v>126915962</v>
       </c>
       <c r="B101" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918715</v>
+        <v>126918407</v>
       </c>
       <c r="B102" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656372</v>
+        <v>655901</v>
       </c>
       <c r="R102" t="n">
-        <v>7122721</v>
+        <v>7122844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,12 +11123,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11139,10 +11139,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918407</v>
+        <v>126918715</v>
       </c>
       <c r="B103" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11150,21 +11150,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11174,10 +11174,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655901</v>
+        <v>656372</v>
       </c>
       <c r="R103" t="n">
-        <v>7122844</v>
+        <v>7122721</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11224,12 +11224,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11240,45 +11240,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B104" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R104" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11322,15 +11327,30 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11341,50 +11361,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>79600</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R105" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11428,30 +11443,15 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126916275</v>
+        <v>126919802</v>
       </c>
       <c r="B106" t="n">
-        <v>79569</v>
+        <v>78770</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655900</v>
+        <v>656007</v>
       </c>
       <c r="R106" t="n">
-        <v>7122800</v>
+        <v>7122964</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126916298</v>
+        <v>126920127</v>
       </c>
       <c r="B107" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655900</v>
+        <v>656146</v>
       </c>
       <c r="R107" t="n">
-        <v>7122796</v>
+        <v>7122791</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11642,18 +11642,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11665,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B108" t="n">
-        <v>58087</v>
+        <v>78769</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11676,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11700,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R108" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,12 +11750,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,10 +11766,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126920127</v>
+        <v>126916275</v>
       </c>
       <c r="B109" t="n">
-        <v>78739</v>
+        <v>79600</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,21 +11777,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11801,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>656146</v>
+        <v>655900</v>
       </c>
       <c r="R109" t="n">
-        <v>7122791</v>
+        <v>7122800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,19 +11845,18 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11867,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920120</v>
+        <v>126918657</v>
       </c>
       <c r="B110" t="n">
-        <v>79569</v>
+        <v>58087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11878,21 +11878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11902,10 +11902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>655982</v>
+        <v>655908</v>
       </c>
       <c r="R110" t="n">
-        <v>7122865</v>
+        <v>7122774</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11952,12 +11952,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126919802</v>
+        <v>126920120</v>
       </c>
       <c r="B111" t="n">
-        <v>78739</v>
+        <v>79600</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656007</v>
+        <v>655982</v>
       </c>
       <c r="R111" t="n">
-        <v>7122964</v>
+        <v>7122865</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12069,10 +12069,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918410</v>
+        <v>126914202</v>
       </c>
       <c r="B112" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12100,17 +12100,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>655904</v>
+        <v>655932</v>
       </c>
       <c r="R112" t="n">
-        <v>7122985</v>
+        <v>7122830</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12137,9 +12137,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12154,12 +12164,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12170,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126914200</v>
+        <v>126918410</v>
       </c>
       <c r="B113" t="n">
-        <v>78739</v>
+        <v>79600</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12181,37 +12191,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>655892</v>
+        <v>655904</v>
       </c>
       <c r="R113" t="n">
-        <v>7122864</v>
+        <v>7122985</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12238,19 +12248,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12265,12 +12265,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12281,10 +12281,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126914202</v>
+        <v>126914200</v>
       </c>
       <c r="B114" t="n">
-        <v>79569</v>
+        <v>78770</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12316,13 +12316,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655932</v>
+        <v>655892</v>
       </c>
       <c r="R114" t="n">
-        <v>7122830</v>
+        <v>7122864</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12395,7 +12395,7 @@
         <v>126916733</v>
       </c>
       <c r="B115" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>126950497</v>
       </c>
       <c r="B116" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>126950494</v>
       </c>
       <c r="B117" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>126950495</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>126950493</v>
       </c>
       <c r="B119" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>126950496</v>
       </c>
       <c r="B120" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>126950482</v>
       </c>
       <c r="B121" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>126950498</v>
       </c>
       <c r="B122" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918405</v>
+        <v>126910394</v>
       </c>
       <c r="B4" t="n">
-        <v>77989</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655901</v>
+        <v>655885</v>
       </c>
       <c r="R4" t="n">
-        <v>7122844</v>
+        <v>7122738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916285</v>
+        <v>126918405</v>
       </c>
       <c r="B5" t="n">
-        <v>78770</v>
+        <v>77992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655855</v>
+        <v>655901</v>
       </c>
       <c r="R5" t="n">
-        <v>7122774</v>
+        <v>7122844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,48 +1090,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126914199</v>
+        <v>126916842</v>
       </c>
       <c r="B6" t="n">
-        <v>78770</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655888</v>
+        <v>655948</v>
       </c>
       <c r="R6" t="n">
-        <v>7122973</v>
+        <v>7122908</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1170,7 +1175,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1201,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916284</v>
+        <v>126916285</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655943</v>
+        <v>655855</v>
       </c>
       <c r="R7" t="n">
-        <v>7122816</v>
+        <v>7122774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126910394</v>
+        <v>126914199</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655885</v>
+        <v>655888</v>
       </c>
       <c r="R8" t="n">
-        <v>7122738</v>
+        <v>7122973</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,9 +1375,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,12 +1402,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1403,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126910130</v>
+        <v>126916284</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655841</v>
+        <v>655943</v>
       </c>
       <c r="R9" t="n">
-        <v>7122800</v>
+        <v>7122816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1504,50 +1519,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916842</v>
+        <v>126910130</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655948</v>
+        <v>655841</v>
       </c>
       <c r="R10" t="n">
-        <v>7122908</v>
+        <v>7122800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,19 +1587,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,32 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919792</v>
+        <v>126918421</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>92808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655919</v>
+        <v>655890</v>
       </c>
       <c r="R11" t="n">
-        <v>7122887</v>
+        <v>7122888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,11 +1693,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1710,12 +1705,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1726,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918646</v>
+        <v>126916306</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656298</v>
+        <v>655956</v>
       </c>
       <c r="R12" t="n">
-        <v>7122812</v>
+        <v>7122866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1827,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916316</v>
+        <v>126916299</v>
       </c>
       <c r="B13" t="n">
-        <v>92609</v>
+        <v>78772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655863</v>
+        <v>655995</v>
       </c>
       <c r="R13" t="n">
-        <v>7122755</v>
+        <v>7122921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918421</v>
+        <v>126916844</v>
       </c>
       <c r="B14" t="n">
-        <v>92802</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655890</v>
+        <v>655905</v>
       </c>
       <c r="R14" t="n">
-        <v>7122888</v>
+        <v>7122985</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,11 +1991,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2009,16 +2014,36 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2029,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916306</v>
+        <v>126916278</v>
       </c>
       <c r="B15" t="n">
-        <v>78678</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2040,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655956</v>
+        <v>655957</v>
       </c>
       <c r="R15" t="n">
-        <v>7122866</v>
+        <v>7122864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918044</v>
+        <v>126917770</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,34 +2166,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656088</v>
+        <v>655852</v>
       </c>
       <c r="R16" t="n">
-        <v>7122850</v>
+        <v>7122942</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2212,30 +2237,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2246,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916299</v>
+        <v>126909344</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,21 +2267,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655995</v>
+        <v>655890</v>
       </c>
       <c r="R17" t="n">
-        <v>7122921</v>
+        <v>7122814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,12 +2341,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2347,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126916844</v>
+        <v>126919792</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655905</v>
+        <v>655919</v>
       </c>
       <c r="R18" t="n">
-        <v>7122985</v>
+        <v>7122887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,19 +2425,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:47</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spilning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,36 +2443,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,32 +2463,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916278</v>
+        <v>126916316</v>
       </c>
       <c r="B19" t="n">
-        <v>79600</v>
+        <v>92615</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2498,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655957</v>
+        <v>655863</v>
       </c>
       <c r="R19" t="n">
-        <v>7122864</v>
+        <v>7122755</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917770</v>
+        <v>126918044</v>
       </c>
       <c r="B20" t="n">
-        <v>79600</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,34 +2575,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655852</v>
+        <v>656088</v>
       </c>
       <c r="R20" t="n">
-        <v>7122942</v>
+        <v>7122850</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,15 +2646,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126909344</v>
+        <v>126918646</v>
       </c>
       <c r="B21" t="n">
-        <v>79600</v>
+        <v>57817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655890</v>
+        <v>656298</v>
       </c>
       <c r="R21" t="n">
-        <v>7122814</v>
+        <v>7122812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2784,7 +2784,7 @@
         <v>126918439</v>
       </c>
       <c r="B22" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>126910226</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>126917790</v>
       </c>
       <c r="B24" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>126918039</v>
       </c>
       <c r="B25" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126917813</v>
+        <v>126918712</v>
       </c>
       <c r="B26" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655710</v>
+        <v>655899</v>
       </c>
       <c r="R26" t="n">
-        <v>7122853</v>
+        <v>7122835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918712</v>
+        <v>126916397</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655899</v>
+        <v>655893</v>
       </c>
       <c r="R27" t="n">
-        <v>7122835</v>
+        <v>7122752</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918424</v>
+        <v>126910403</v>
       </c>
       <c r="B28" t="n">
-        <v>92802</v>
+        <v>79603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655961</v>
+        <v>655885</v>
       </c>
       <c r="R28" t="n">
-        <v>7122865</v>
+        <v>7122738</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126916397</v>
+        <v>126918424</v>
       </c>
       <c r="B29" t="n">
-        <v>92609</v>
+        <v>92808</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655893</v>
+        <v>655961</v>
       </c>
       <c r="R29" t="n">
-        <v>7122752</v>
+        <v>7122865</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126910403</v>
+        <v>126917813</v>
       </c>
       <c r="B30" t="n">
-        <v>79600</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655885</v>
+        <v>655710</v>
       </c>
       <c r="R30" t="n">
-        <v>7122738</v>
+        <v>7122853</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3708,7 +3708,7 @@
         <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>126916288</v>
       </c>
       <c r="B32" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>126916289</v>
       </c>
       <c r="B33" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918458</v>
+        <v>126917804</v>
       </c>
       <c r="B34" t="n">
-        <v>78417</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,21 +4019,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655914</v>
+        <v>655834</v>
       </c>
       <c r="R34" t="n">
-        <v>7122985</v>
+        <v>7122923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918037</v>
+        <v>126918458</v>
       </c>
       <c r="B35" t="n">
-        <v>79600</v>
+        <v>78420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,34 +4120,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655903</v>
+        <v>655914</v>
       </c>
       <c r="R35" t="n">
-        <v>7122984</v>
+        <v>7122985</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4191,30 +4191,15 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4225,10 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918438</v>
+        <v>126920137</v>
       </c>
       <c r="B36" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,21 +4221,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4260,10 +4245,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655882</v>
+        <v>655990</v>
       </c>
       <c r="R36" t="n">
-        <v>7122978</v>
+        <v>7122926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4310,12 +4295,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4326,32 +4311,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919804</v>
+        <v>126916746</v>
       </c>
       <c r="B37" t="n">
-        <v>78770</v>
+        <v>91899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4361,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655989</v>
+        <v>655785</v>
       </c>
       <c r="R37" t="n">
-        <v>7122922</v>
+        <v>7122898</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,26 +4396,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126916287</v>
+        <v>126918438</v>
       </c>
       <c r="B38" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4462,10 +4443,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655900</v>
+        <v>655882</v>
       </c>
       <c r="R38" t="n">
-        <v>7122798</v>
+        <v>7122978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4512,12 +4493,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4528,32 +4509,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126916746</v>
+        <v>126919804</v>
       </c>
       <c r="B39" t="n">
-        <v>91893</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4563,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655785</v>
+        <v>655989</v>
       </c>
       <c r="R39" t="n">
-        <v>7122898</v>
+        <v>7122922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4613,22 +4594,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126920137</v>
+        <v>126918037</v>
       </c>
       <c r="B40" t="n">
-        <v>78678</v>
+        <v>79603</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4636,34 +4621,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655990</v>
+        <v>655903</v>
       </c>
       <c r="R40" t="n">
-        <v>7122926</v>
+        <v>7122984</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,15 +4692,30 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917804</v>
+        <v>126916287</v>
       </c>
       <c r="B41" t="n">
-        <v>80114</v>
+        <v>78773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655834</v>
+        <v>655900</v>
       </c>
       <c r="R41" t="n">
-        <v>7122923</v>
+        <v>7122798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4830,7 +4830,7 @@
         <v>126916304</v>
       </c>
       <c r="B42" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>126920136</v>
       </c>
       <c r="B43" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>126917830</v>
       </c>
       <c r="B44" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>126916741</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916272</v>
+        <v>126917825</v>
       </c>
       <c r="B46" t="n">
-        <v>79629</v>
+        <v>77992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655957</v>
+        <v>655749</v>
       </c>
       <c r="R46" t="n">
-        <v>7122864</v>
+        <v>7122779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126917825</v>
+        <v>126916272</v>
       </c>
       <c r="B47" t="n">
-        <v>77989</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655749</v>
+        <v>655957</v>
       </c>
       <c r="R47" t="n">
-        <v>7122779</v>
+        <v>7122864</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919790</v>
+        <v>126917785</v>
       </c>
       <c r="B48" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655973</v>
+        <v>655776</v>
       </c>
       <c r="R48" t="n">
-        <v>7122926</v>
+        <v>7122760</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126917785</v>
+        <v>126919790</v>
       </c>
       <c r="B49" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655776</v>
+        <v>655973</v>
       </c>
       <c r="R49" t="n">
-        <v>7122760</v>
+        <v>7122926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5638,7 +5638,7 @@
         <v>126918406</v>
       </c>
       <c r="B50" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126918397</v>
+        <v>126919778</v>
       </c>
       <c r="B51" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655892</v>
+        <v>655919</v>
       </c>
       <c r="R51" t="n">
-        <v>7122986</v>
+        <v>7122981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5840,7 +5840,7 @@
         <v>126910294</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126919778</v>
+        <v>126920128</v>
       </c>
       <c r="B53" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655919</v>
+        <v>655942</v>
       </c>
       <c r="R53" t="n">
-        <v>7122981</v>
+        <v>7122804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126920128</v>
+        <v>126915088</v>
       </c>
       <c r="B54" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6070,14 +6070,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655942</v>
+        <v>655950</v>
       </c>
       <c r="R54" t="n">
-        <v>7122804</v>
+        <v>7122893</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915088</v>
+        <v>126918672</v>
       </c>
       <c r="B55" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,14 +6171,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655950</v>
+        <v>655882</v>
       </c>
       <c r="R55" t="n">
-        <v>7122893</v>
+        <v>7122787</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918672</v>
+        <v>126918397</v>
       </c>
       <c r="B56" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655882</v>
+        <v>655892</v>
       </c>
       <c r="R56" t="n">
-        <v>7122787</v>
+        <v>7122986</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6345,7 +6345,7 @@
         <v>126917762</v>
       </c>
       <c r="B57" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>126918043</v>
       </c>
       <c r="B58" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>126917803</v>
       </c>
       <c r="B59" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>126917763</v>
       </c>
       <c r="B60" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918041</v>
+        <v>126917791</v>
       </c>
       <c r="B61" t="n">
-        <v>92802</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,34 +6772,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655965</v>
+        <v>656327</v>
       </c>
       <c r="R61" t="n">
-        <v>7122890</v>
+        <v>7122772</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,30 +6843,15 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,10 +6862,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916745</v>
+        <v>126916274</v>
       </c>
       <c r="B62" t="n">
-        <v>78678</v>
+        <v>79603</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6888,21 +6873,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6897,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655840</v>
+        <v>656012</v>
       </c>
       <c r="R62" t="n">
-        <v>7122839</v>
+        <v>7122821</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,57 +6947,61 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916312</v>
+        <v>126918045</v>
       </c>
       <c r="B63" t="n">
-        <v>92609</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656104</v>
+        <v>656177</v>
       </c>
       <c r="R63" t="n">
-        <v>7122796</v>
+        <v>7122815</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7056,15 +7045,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7075,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918047</v>
+        <v>126919808</v>
       </c>
       <c r="B64" t="n">
-        <v>78678</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,34 +7090,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656203</v>
+        <v>655921</v>
       </c>
       <c r="R64" t="n">
-        <v>7122806</v>
+        <v>7122999</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7157,30 +7161,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7194,7 +7183,7 @@
         <v>126915955</v>
       </c>
       <c r="B65" t="n">
-        <v>92635</v>
+        <v>92641</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7296,32 +7285,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126916274</v>
+        <v>126916312</v>
       </c>
       <c r="B66" t="n">
-        <v>79600</v>
+        <v>92615</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7331,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656012</v>
+        <v>656104</v>
       </c>
       <c r="R66" t="n">
-        <v>7122821</v>
+        <v>7122796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7397,10 +7386,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917791</v>
+        <v>126918041</v>
       </c>
       <c r="B67" t="n">
-        <v>78770</v>
+        <v>92808</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,34 +7397,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656327</v>
+        <v>655965</v>
       </c>
       <c r="R67" t="n">
-        <v>7122772</v>
+        <v>7122890</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7479,15 +7468,30 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7498,10 +7502,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918045</v>
+        <v>126918047</v>
       </c>
       <c r="B68" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,21 +7513,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7537,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656177</v>
+        <v>656203</v>
       </c>
       <c r="R68" t="n">
-        <v>7122815</v>
+        <v>7122806</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126919808</v>
+        <v>126916745</v>
       </c>
       <c r="B69" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7625,21 +7629,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7649,10 +7653,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>655921</v>
+        <v>655840</v>
       </c>
       <c r="R69" t="n">
-        <v>7122999</v>
+        <v>7122839</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7699,26 +7703,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>126918443</v>
       </c>
       <c r="B70" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7831,32 +7831,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126916315</v>
+        <v>126918422</v>
       </c>
       <c r="B71" t="n">
-        <v>92609</v>
+        <v>91486</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655879</v>
+        <v>655890</v>
       </c>
       <c r="R71" t="n">
-        <v>7122817</v>
+        <v>7122888</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,12 +7916,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,32 +7932,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918422</v>
+        <v>126918650</v>
       </c>
       <c r="B72" t="n">
-        <v>91480</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655890</v>
+        <v>656291</v>
       </c>
       <c r="R72" t="n">
-        <v>7122888</v>
+        <v>7122816</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,10 +8033,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126917789</v>
+        <v>126918042</v>
       </c>
       <c r="B73" t="n">
-        <v>78770</v>
+        <v>78420</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8044,34 +8044,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655760</v>
+        <v>655954</v>
       </c>
       <c r="R73" t="n">
-        <v>7122811</v>
+        <v>7122886</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8115,15 +8115,30 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,10 +8149,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918042</v>
+        <v>126917789</v>
       </c>
       <c r="B74" t="n">
-        <v>78417</v>
+        <v>78773</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8145,34 +8160,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655954</v>
+        <v>655760</v>
       </c>
       <c r="R74" t="n">
-        <v>7122886</v>
+        <v>7122811</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,30 +8231,15 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,10 +8250,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918650</v>
+        <v>126916315</v>
       </c>
       <c r="B75" t="n">
-        <v>80143</v>
+        <v>92615</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8261,21 +8261,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656291</v>
+        <v>655879</v>
       </c>
       <c r="R75" t="n">
-        <v>7122816</v>
+        <v>7122817</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,45 +8351,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126918050</v>
+        <v>126916729</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656266</v>
+        <v>655892</v>
       </c>
       <c r="R76" t="n">
-        <v>7122789</v>
+        <v>7122748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,6 +8424,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8432,31 +8437,16 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8470,7 +8460,7 @@
         <v>126915970</v>
       </c>
       <c r="B77" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8571,7 +8561,7 @@
         <v>126915964</v>
       </c>
       <c r="B78" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8672,7 +8662,7 @@
         <v>126917772</v>
       </c>
       <c r="B79" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8770,45 +8760,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916729</v>
+        <v>126918050</v>
       </c>
       <c r="B80" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655892</v>
+        <v>656266</v>
       </c>
       <c r="R80" t="n">
-        <v>7122748</v>
+        <v>7122789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,11 +8833,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8856,16 +8841,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8879,7 +8879,7 @@
         <v>126919806</v>
       </c>
       <c r="B81" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8977,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915963</v>
+        <v>126918404</v>
       </c>
       <c r="B82" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655813</v>
+        <v>655901</v>
       </c>
       <c r="R82" t="n">
-        <v>7122846</v>
+        <v>7122844</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,10 +9078,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126916286</v>
+        <v>126915963</v>
       </c>
       <c r="B83" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655866</v>
+        <v>655813</v>
       </c>
       <c r="R83" t="n">
-        <v>7122779</v>
+        <v>7122846</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9163,12 +9163,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126918404</v>
+        <v>126916286</v>
       </c>
       <c r="B84" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655901</v>
+        <v>655866</v>
       </c>
       <c r="R84" t="n">
-        <v>7122844</v>
+        <v>7122779</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>126918104</v>
       </c>
       <c r="B85" t="n">
-        <v>92603</v>
+        <v>92609</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918677</v>
+        <v>126915959</v>
       </c>
       <c r="B86" t="n">
-        <v>78770</v>
+        <v>92808</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,21 +9392,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655893</v>
+        <v>655849</v>
       </c>
       <c r="R86" t="n">
-        <v>7122814</v>
+        <v>7122806</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9466,12 +9466,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,10 +9482,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915959</v>
+        <v>126918040</v>
       </c>
       <c r="B87" t="n">
-        <v>92802</v>
+        <v>78681</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9493,37 +9493,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655849</v>
+        <v>655945</v>
       </c>
       <c r="R87" t="n">
-        <v>7122806</v>
+        <v>7122909</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9563,16 +9563,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9583,10 +9598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126918040</v>
+        <v>126916394</v>
       </c>
       <c r="B88" t="n">
-        <v>78678</v>
+        <v>78772</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9594,37 +9609,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655945</v>
+        <v>655798</v>
       </c>
       <c r="R88" t="n">
-        <v>7122909</v>
+        <v>7122934</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9662,33 +9677,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9699,10 +9700,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126916394</v>
+        <v>126918677</v>
       </c>
       <c r="B89" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9710,21 +9711,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9734,13 +9735,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655798</v>
+        <v>655893</v>
       </c>
       <c r="R89" t="n">
-        <v>7122934</v>
+        <v>7122814</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9778,19 +9779,18 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918423</v>
+        <v>126918711</v>
       </c>
       <c r="B90" t="n">
-        <v>92802</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655881</v>
+        <v>655898</v>
       </c>
       <c r="R90" t="n">
-        <v>7122919</v>
+        <v>7122802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9905,7 +9905,7 @@
         <v>126918038</v>
       </c>
       <c r="B91" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10018,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918711</v>
+        <v>126918100</v>
       </c>
       <c r="B92" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,37 +10029,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655898</v>
+        <v>655957</v>
       </c>
       <c r="R92" t="n">
-        <v>7122802</v>
+        <v>7122879</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10103,12 +10103,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,10 +10119,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918100</v>
+        <v>126917788</v>
       </c>
       <c r="B93" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10150,17 +10150,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655957</v>
+        <v>655780</v>
       </c>
       <c r="R93" t="n">
-        <v>7122879</v>
+        <v>7122780</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10204,12 +10204,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126917788</v>
+        <v>126918423</v>
       </c>
       <c r="B94" t="n">
-        <v>78770</v>
+        <v>92808</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655780</v>
+        <v>655881</v>
       </c>
       <c r="R94" t="n">
-        <v>7122780</v>
+        <v>7122919</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10324,7 +10324,7 @@
         <v>126916313</v>
       </c>
       <c r="B95" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>126918713</v>
       </c>
       <c r="B96" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>126918681</v>
       </c>
       <c r="B97" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>126918395</v>
       </c>
       <c r="B98" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10725,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126916276</v>
+        <v>126915962</v>
       </c>
       <c r="B99" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10736,21 +10736,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655925</v>
+        <v>655854</v>
       </c>
       <c r="R99" t="n">
-        <v>7122825</v>
+        <v>7122777</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10810,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,10 +10826,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126914201</v>
+        <v>126916276</v>
       </c>
       <c r="B100" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10857,17 +10857,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655947</v>
+        <v>655925</v>
       </c>
       <c r="R100" t="n">
-        <v>7122837</v>
+        <v>7122825</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10894,19 +10894,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10911,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10927,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915962</v>
+        <v>126914201</v>
       </c>
       <c r="B101" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,37 +10938,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655854</v>
+        <v>655947</v>
       </c>
       <c r="R101" t="n">
-        <v>7122777</v>
+        <v>7122837</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11005,9 +10995,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918407</v>
+        <v>126918715</v>
       </c>
       <c r="B102" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>655901</v>
+        <v>656372</v>
       </c>
       <c r="R102" t="n">
-        <v>7122844</v>
+        <v>7122721</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,12 +11123,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11139,10 +11139,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918715</v>
+        <v>126918407</v>
       </c>
       <c r="B103" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11150,21 +11150,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11174,10 +11174,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656372</v>
+        <v>655901</v>
       </c>
       <c r="R103" t="n">
-        <v>7122721</v>
+        <v>7122844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11224,12 +11224,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11240,50 +11240,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R104" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11327,30 +11322,15 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11361,45 +11341,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B105" t="n">
-        <v>79600</v>
+        <v>8447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R105" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,15 +11428,30 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126919802</v>
+        <v>126916298</v>
       </c>
       <c r="B106" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>656007</v>
+        <v>655900</v>
       </c>
       <c r="R106" t="n">
-        <v>7122964</v>
+        <v>7122796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126920127</v>
+        <v>126918657</v>
       </c>
       <c r="B107" t="n">
-        <v>78770</v>
+        <v>58087</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656146</v>
+        <v>655908</v>
       </c>
       <c r="R107" t="n">
-        <v>7122791</v>
+        <v>7122774</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11642,19 +11642,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11665,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126916298</v>
+        <v>126919802</v>
       </c>
       <c r="B108" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11676,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11700,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655900</v>
+        <v>656007</v>
       </c>
       <c r="R108" t="n">
-        <v>7122796</v>
+        <v>7122964</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11750,12 +11749,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11769,7 +11768,7 @@
         <v>126916275</v>
       </c>
       <c r="B109" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11867,10 +11866,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126918657</v>
+        <v>126920127</v>
       </c>
       <c r="B110" t="n">
-        <v>58087</v>
+        <v>78773</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11878,21 +11877,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11902,10 +11901,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>655908</v>
+        <v>656146</v>
       </c>
       <c r="R110" t="n">
-        <v>7122774</v>
+        <v>7122791</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11946,18 +11945,19 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11971,7 +11971,7 @@
         <v>126920120</v>
       </c>
       <c r="B111" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126914202</v>
+        <v>126914200</v>
       </c>
       <c r="B112" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12080,21 +12080,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>655932</v>
+        <v>655892</v>
       </c>
       <c r="R112" t="n">
-        <v>7122830</v>
+        <v>7122864</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12180,10 +12180,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918410</v>
+        <v>126916733</v>
       </c>
       <c r="B113" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12191,21 +12191,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12215,10 +12215,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>655904</v>
+        <v>655793</v>
       </c>
       <c r="R113" t="n">
-        <v>7122985</v>
+        <v>7122849</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12265,12 +12265,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12281,10 +12281,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126914200</v>
+        <v>126914202</v>
       </c>
       <c r="B114" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12316,13 +12316,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655892</v>
+        <v>655932</v>
       </c>
       <c r="R114" t="n">
-        <v>7122864</v>
+        <v>7122830</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12392,10 +12392,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126916733</v>
+        <v>126918410</v>
       </c>
       <c r="B115" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12403,21 +12403,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12427,10 +12427,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>655793</v>
+        <v>655904</v>
       </c>
       <c r="R115" t="n">
-        <v>7122849</v>
+        <v>7122985</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12477,12 +12477,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12496,7 +12496,7 @@
         <v>126950497</v>
       </c>
       <c r="B116" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>126950494</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>126950495</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>126950493</v>
       </c>
       <c r="B119" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>126950496</v>
       </c>
       <c r="B120" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>126950482</v>
       </c>
       <c r="B121" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>126950498</v>
       </c>
       <c r="B122" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -888,45 +888,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126916842</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655948</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,9 +961,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,12 +988,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918405</v>
+        <v>126916285</v>
       </c>
       <c r="B5" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655901</v>
+        <v>655855</v>
       </c>
       <c r="R5" t="n">
-        <v>7122844</v>
+        <v>7122774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1089,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,53 +1105,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916842</v>
+        <v>126914199</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655948</v>
+        <v>655888</v>
       </c>
       <c r="R6" t="n">
-        <v>7122908</v>
+        <v>7122973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1175,7 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1200,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916285</v>
+        <v>126916284</v>
       </c>
       <c r="B7" t="n">
         <v>78773</v>
@@ -1241,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655855</v>
+        <v>655943</v>
       </c>
       <c r="R7" t="n">
-        <v>7122774</v>
+        <v>7122816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126914199</v>
+        <v>126910130</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655888</v>
+        <v>655841</v>
       </c>
       <c r="R8" t="n">
-        <v>7122973</v>
+        <v>7122800</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,19 +1385,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,12 +1402,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126916284</v>
+        <v>126918405</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655943</v>
+        <v>655901</v>
       </c>
       <c r="R9" t="n">
-        <v>7122816</v>
+        <v>7122844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Peder Winding, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126910130</v>
+        <v>126910394</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655841</v>
+        <v>655885</v>
       </c>
       <c r="R10" t="n">
-        <v>7122800</v>
+        <v>7122738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918421</v>
+        <v>126916306</v>
       </c>
       <c r="B11" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655890</v>
+        <v>655956</v>
       </c>
       <c r="R11" t="n">
-        <v>7122888</v>
+        <v>7122866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,12 +1705,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916306</v>
+        <v>126916316</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>92615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655956</v>
+        <v>655863</v>
       </c>
       <c r="R12" t="n">
-        <v>7122866</v>
+        <v>7122755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916299</v>
+        <v>126918044</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655995</v>
+        <v>656088</v>
       </c>
       <c r="R13" t="n">
-        <v>7122921</v>
+        <v>7122850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,15 +1904,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916844</v>
+        <v>126916299</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655905</v>
+        <v>655995</v>
       </c>
       <c r="R14" t="n">
-        <v>7122985</v>
+        <v>7122921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,21 +2006,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2014,36 +2019,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2054,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916278</v>
+        <v>126916844</v>
       </c>
       <c r="B15" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655957</v>
+        <v>655905</v>
       </c>
       <c r="R15" t="n">
-        <v>7122864</v>
+        <v>7122985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2107,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2135,16 +2130,36 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2155,32 +2170,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126917770</v>
+        <v>126919792</v>
       </c>
       <c r="B16" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655852</v>
+        <v>655919</v>
       </c>
       <c r="R16" t="n">
-        <v>7122942</v>
+        <v>7122887</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,6 +2243,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2240,12 +2260,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2256,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126909344</v>
+        <v>126918421</v>
       </c>
       <c r="B17" t="n">
-        <v>79603</v>
+        <v>92808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2294,7 +2314,7 @@
         <v>655890</v>
       </c>
       <c r="R17" t="n">
-        <v>7122814</v>
+        <v>7122888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,12 +2361,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, kristina stenmarck, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2357,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126919792</v>
+        <v>126918646</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655919</v>
+        <v>656298</v>
       </c>
       <c r="R18" t="n">
-        <v>7122887</v>
+        <v>7122812</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2430,11 +2450,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2447,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2463,32 +2478,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916316</v>
+        <v>126916278</v>
       </c>
       <c r="B19" t="n">
-        <v>92615</v>
+        <v>79603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2498,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655863</v>
+        <v>655957</v>
       </c>
       <c r="R19" t="n">
-        <v>7122755</v>
+        <v>7122864</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918044</v>
+        <v>126917770</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,34 +2590,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656088</v>
+        <v>655852</v>
       </c>
       <c r="R20" t="n">
-        <v>7122850</v>
+        <v>7122942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,30 +2661,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918646</v>
+        <v>126909344</v>
       </c>
       <c r="B21" t="n">
-        <v>57817</v>
+        <v>79603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656298</v>
+        <v>655890</v>
       </c>
       <c r="R21" t="n">
-        <v>7122812</v>
+        <v>7122814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126916397</v>
+        <v>126917813</v>
       </c>
       <c r="B27" t="n">
-        <v>92615</v>
+        <v>78772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655893</v>
+        <v>655710</v>
       </c>
       <c r="R27" t="n">
-        <v>7122752</v>
+        <v>7122853</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126910403</v>
+        <v>126918424</v>
       </c>
       <c r="B28" t="n">
-        <v>79603</v>
+        <v>92808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655885</v>
+        <v>655961</v>
       </c>
       <c r="R28" t="n">
-        <v>7122738</v>
+        <v>7122865</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918424</v>
+        <v>126916397</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>92615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655961</v>
+        <v>655893</v>
       </c>
       <c r="R29" t="n">
-        <v>7122865</v>
+        <v>7122752</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126917813</v>
+        <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655710</v>
+        <v>655885</v>
       </c>
       <c r="R30" t="n">
-        <v>7122853</v>
+        <v>7122738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918450</v>
+        <v>126916289</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655906</v>
+        <v>655996</v>
       </c>
       <c r="R31" t="n">
-        <v>7122852</v>
+        <v>7122934</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B32" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R32" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916289</v>
+        <v>126916288</v>
       </c>
       <c r="B33" t="n">
         <v>78773</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655996</v>
+        <v>655965</v>
       </c>
       <c r="R33" t="n">
-        <v>7122934</v>
+        <v>7122873</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126917804</v>
+        <v>126916746</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>91899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655834</v>
+        <v>655785</v>
       </c>
       <c r="R34" t="n">
-        <v>7122923</v>
+        <v>7122898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,19 +4093,15 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4311,32 +4307,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126916746</v>
+        <v>126917804</v>
       </c>
       <c r="B37" t="n">
-        <v>91899</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4346,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655785</v>
+        <v>655834</v>
       </c>
       <c r="R37" t="n">
-        <v>7122898</v>
+        <v>7122923</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,15 +4392,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126916741</v>
+        <v>126917825</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655895</v>
+        <v>655749</v>
       </c>
       <c r="R45" t="n">
-        <v>7122747</v>
+        <v>7122779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126917825</v>
+        <v>126916741</v>
       </c>
       <c r="B46" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655749</v>
+        <v>655895</v>
       </c>
       <c r="R46" t="n">
-        <v>7122779</v>
+        <v>7122747</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126920128</v>
+        <v>126918397</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655942</v>
+        <v>655892</v>
       </c>
       <c r="R53" t="n">
-        <v>7122804</v>
+        <v>7122986</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126915088</v>
+        <v>126920128</v>
       </c>
       <c r="B54" t="n">
         <v>78773</v>
@@ -6070,14 +6070,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655950</v>
+        <v>655942</v>
       </c>
       <c r="R54" t="n">
-        <v>7122893</v>
+        <v>7122804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,7 +6140,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918672</v>
+        <v>126915088</v>
       </c>
       <c r="B55" t="n">
         <v>78773</v>
@@ -6171,14 +6171,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655882</v>
+        <v>655950</v>
       </c>
       <c r="R55" t="n">
-        <v>7122787</v>
+        <v>7122893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918397</v>
+        <v>126918672</v>
       </c>
       <c r="B56" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655892</v>
+        <v>655882</v>
       </c>
       <c r="R56" t="n">
-        <v>7122986</v>
+        <v>7122787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R57" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,15 +6424,30 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6443,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B58" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6454,34 +6469,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R58" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6525,30 +6540,15 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126917803</v>
+        <v>126916312</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>92615</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655792</v>
+        <v>656104</v>
       </c>
       <c r="R59" t="n">
-        <v>7122889</v>
+        <v>7122796</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,12 +6644,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126917763</v>
+        <v>126917803</v>
       </c>
       <c r="B60" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656241</v>
+        <v>655792</v>
       </c>
       <c r="R60" t="n">
-        <v>7122853</v>
+        <v>7122889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917791</v>
+        <v>126915955</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>92641</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,37 +6772,40 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>5448</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656327</v>
+        <v>655885</v>
       </c>
       <c r="R61" t="n">
-        <v>7122772</v>
+        <v>7122754</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,18 +6843,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6862,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916274</v>
+        <v>126916745</v>
       </c>
       <c r="B62" t="n">
-        <v>79603</v>
+        <v>78681</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6873,21 +6877,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6897,10 +6901,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656012</v>
+        <v>655840</v>
       </c>
       <c r="R62" t="n">
-        <v>7122821</v>
+        <v>7122839</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,26 +6951,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918045</v>
+        <v>126918047</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6974,21 +6974,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656177</v>
+        <v>656203</v>
       </c>
       <c r="R63" t="n">
-        <v>7122815</v>
+        <v>7122806</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7079,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126919808</v>
+        <v>126918041</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>92808</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7090,34 +7090,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655921</v>
+        <v>655965</v>
       </c>
       <c r="R64" t="n">
-        <v>7122999</v>
+        <v>7122890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,15 +7161,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7180,10 +7195,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126915955</v>
+        <v>126917763</v>
       </c>
       <c r="B65" t="n">
-        <v>92641</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,40 +7206,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>655885</v>
+        <v>656241</v>
       </c>
       <c r="R65" t="n">
-        <v>7122754</v>
+        <v>7122853</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7262,19 +7274,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7285,32 +7296,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126916312</v>
+        <v>126917791</v>
       </c>
       <c r="B66" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7320,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656104</v>
+        <v>656327</v>
       </c>
       <c r="R66" t="n">
-        <v>7122796</v>
+        <v>7122772</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,12 +7381,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7386,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126918041</v>
+        <v>126919808</v>
       </c>
       <c r="B67" t="n">
-        <v>92808</v>
+        <v>78773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7397,34 +7408,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>655965</v>
+        <v>655921</v>
       </c>
       <c r="R67" t="n">
-        <v>7122890</v>
+        <v>7122999</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7468,30 +7479,15 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7502,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918047</v>
+        <v>126916274</v>
       </c>
       <c r="B68" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7513,34 +7509,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656203</v>
+        <v>656012</v>
       </c>
       <c r="R68" t="n">
-        <v>7122806</v>
+        <v>7122821</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,30 +7580,15 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7618,10 +7599,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126916745</v>
+        <v>126918045</v>
       </c>
       <c r="B69" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7629,34 +7610,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>655840</v>
+        <v>656177</v>
       </c>
       <c r="R69" t="n">
-        <v>7122839</v>
+        <v>7122815</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,47 +7681,66 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918443</v>
+        <v>126918422</v>
       </c>
       <c r="B70" t="n">
-        <v>80989</v>
+        <v>91486</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655875</v>
+        <v>655890</v>
       </c>
       <c r="R70" t="n">
-        <v>7122959</v>
+        <v>7122888</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7796,21 +7796,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7831,32 +7816,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918422</v>
+        <v>126918443</v>
       </c>
       <c r="B71" t="n">
-        <v>91486</v>
+        <v>80989</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7866,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655890</v>
+        <v>655875</v>
       </c>
       <c r="R71" t="n">
-        <v>7122888</v>
+        <v>7122959</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,6 +7897,21 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -7932,10 +7932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918650</v>
+        <v>126916315</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>92615</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7943,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656291</v>
+        <v>655879</v>
       </c>
       <c r="R72" t="n">
-        <v>7122816</v>
+        <v>7122817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,45 +8033,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918042</v>
+        <v>126918650</v>
       </c>
       <c r="B73" t="n">
-        <v>78420</v>
+        <v>80146</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655954</v>
+        <v>656291</v>
       </c>
       <c r="R73" t="n">
-        <v>7122886</v>
+        <v>7122816</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8115,30 +8115,15 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8149,10 +8134,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126917789</v>
+        <v>126918042</v>
       </c>
       <c r="B74" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8160,34 +8145,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655760</v>
+        <v>655954</v>
       </c>
       <c r="R74" t="n">
-        <v>7122811</v>
+        <v>7122886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8231,15 +8216,30 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916315</v>
+        <v>126917789</v>
       </c>
       <c r="B75" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655879</v>
+        <v>655760</v>
       </c>
       <c r="R75" t="n">
-        <v>7122817</v>
+        <v>7122811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,32 +8351,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916729</v>
+        <v>126915964</v>
       </c>
       <c r="B76" t="n">
-        <v>56849</v>
+        <v>80117</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655892</v>
+        <v>655800</v>
       </c>
       <c r="R76" t="n">
-        <v>7122748</v>
+        <v>7122929</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8422,11 +8422,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8441,12 +8436,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8457,32 +8452,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915970</v>
+        <v>126917772</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8492,13 +8487,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655778</v>
+        <v>655768</v>
       </c>
       <c r="R77" t="n">
-        <v>7122904</v>
+        <v>7122903</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8542,12 +8537,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8558,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915964</v>
+        <v>126918050</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8569,37 +8564,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655800</v>
+        <v>656266</v>
       </c>
       <c r="R78" t="n">
-        <v>7122929</v>
+        <v>7122789</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8639,16 +8634,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8659,32 +8669,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126917772</v>
+        <v>126915970</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,13 +8704,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655768</v>
+        <v>655778</v>
       </c>
       <c r="R79" t="n">
-        <v>7122903</v>
+        <v>7122904</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8744,12 +8754,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8760,10 +8770,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918050</v>
+        <v>126919806</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8771,34 +8781,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656266</v>
+        <v>655917</v>
       </c>
       <c r="R80" t="n">
-        <v>7122789</v>
+        <v>7122874</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8842,30 +8852,15 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8876,10 +8871,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126919806</v>
+        <v>126918404</v>
       </c>
       <c r="B81" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8887,21 +8882,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8911,10 +8906,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655917</v>
+        <v>655901</v>
       </c>
       <c r="R81" t="n">
-        <v>7122874</v>
+        <v>7122844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8961,12 +8956,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918404</v>
+        <v>126915963</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8983,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,13 +9007,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655901</v>
+        <v>655813</v>
       </c>
       <c r="R82" t="n">
-        <v>7122844</v>
+        <v>7122846</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9057,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,7 +9073,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915963</v>
+        <v>126916286</v>
       </c>
       <c r="B83" t="n">
         <v>78773</v>
@@ -9113,13 +9108,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655813</v>
+        <v>655866</v>
       </c>
       <c r="R83" t="n">
-        <v>7122846</v>
+        <v>7122779</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9163,12 +9158,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,32 +9174,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916286</v>
+        <v>126916729</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655866</v>
+        <v>655892</v>
       </c>
       <c r="R84" t="n">
-        <v>7122779</v>
+        <v>7122748</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9252,6 +9247,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126915959</v>
+        <v>126918040</v>
       </c>
       <c r="B86" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655849</v>
+        <v>655945</v>
       </c>
       <c r="R86" t="n">
-        <v>7122806</v>
+        <v>7122909</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9462,16 +9462,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,10 +9497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126918040</v>
+        <v>126916394</v>
       </c>
       <c r="B87" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9493,37 +9508,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655945</v>
+        <v>655798</v>
       </c>
       <c r="R87" t="n">
-        <v>7122909</v>
+        <v>7122934</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9561,33 +9576,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9598,10 +9599,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126916394</v>
+        <v>126915959</v>
       </c>
       <c r="B88" t="n">
-        <v>78772</v>
+        <v>92808</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9609,21 +9610,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9633,10 +9634,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655798</v>
+        <v>655849</v>
       </c>
       <c r="R88" t="n">
-        <v>7122934</v>
+        <v>7122806</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9677,7 +9678,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10018,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918100</v>
+        <v>126918711</v>
       </c>
       <c r="B92" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,37 +10029,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655957</v>
+        <v>655898</v>
       </c>
       <c r="R92" t="n">
-        <v>7122879</v>
+        <v>7122802</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10103,12 +10103,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,7 +10119,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126917788</v>
+        <v>126918100</v>
       </c>
       <c r="B93" t="n">
         <v>78773</v>
@@ -10150,17 +10150,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655780</v>
+        <v>655957</v>
       </c>
       <c r="R93" t="n">
-        <v>7122780</v>
+        <v>7122879</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10204,12 +10204,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918423</v>
+        <v>126917788</v>
       </c>
       <c r="B94" t="n">
-        <v>92808</v>
+        <v>78773</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655881</v>
+        <v>655780</v>
       </c>
       <c r="R94" t="n">
-        <v>7122919</v>
+        <v>7122780</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10321,32 +10321,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126916313</v>
+        <v>126918681</v>
       </c>
       <c r="B95" t="n">
-        <v>92615</v>
+        <v>80117</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656087</v>
+        <v>656291</v>
       </c>
       <c r="R95" t="n">
-        <v>7122806</v>
+        <v>7122808</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918681</v>
+        <v>126918395</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>79632</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,21 +10534,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656291</v>
+        <v>655892</v>
       </c>
       <c r="R97" t="n">
-        <v>7122808</v>
+        <v>7122986</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10608,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918395</v>
+        <v>126915962</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10635,21 +10635,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,13 +10659,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655892</v>
+        <v>655854</v>
       </c>
       <c r="R98" t="n">
-        <v>7122986</v>
+        <v>7122777</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10709,12 +10709,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915962</v>
+        <v>126916276</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10736,21 +10736,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655854</v>
+        <v>655925</v>
       </c>
       <c r="R99" t="n">
-        <v>7122777</v>
+        <v>7122825</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10810,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,7 +10826,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126916276</v>
+        <v>126914201</v>
       </c>
       <c r="B100" t="n">
         <v>79603</v>
@@ -10857,17 +10857,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655925</v>
+        <v>655947</v>
       </c>
       <c r="R100" t="n">
-        <v>7122825</v>
+        <v>7122837</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10894,9 +10894,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10911,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10927,48 +10937,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126914201</v>
+        <v>126916313</v>
       </c>
       <c r="B101" t="n">
-        <v>79603</v>
+        <v>92615</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655947</v>
+        <v>656087</v>
       </c>
       <c r="R101" t="n">
-        <v>7122837</v>
+        <v>7122806</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10995,19 +11005,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11240,45 +11240,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B104" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R104" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11322,15 +11327,30 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11341,50 +11361,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B105" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R105" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11428,30 +11443,15 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916314</v>
+        <v>126910130</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>79603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655893</v>
+        <v>655841</v>
       </c>
       <c r="R3" t="n">
-        <v>7122779</v>
+        <v>7122800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916842</v>
+        <v>126916314</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>92615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,39 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655948</v>
+        <v>655893</v>
       </c>
       <c r="R4" t="n">
-        <v>7122908</v>
+        <v>7122779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,19 +956,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916285</v>
+        <v>126910394</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655855</v>
+        <v>655885</v>
       </c>
       <c r="R5" t="n">
-        <v>7122774</v>
+        <v>7122738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1105,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126914199</v>
+        <v>126918405</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,37 +1101,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655888</v>
+        <v>655901</v>
       </c>
       <c r="R6" t="n">
-        <v>7122973</v>
+        <v>7122844</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1158,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,12 +1175,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Peder Winding, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1216,45 +1191,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916284</v>
+        <v>126916842</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655943</v>
+        <v>655948</v>
       </c>
       <c r="R7" t="n">
-        <v>7122816</v>
+        <v>7122908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,9 +1264,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126910130</v>
+        <v>126916285</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655841</v>
+        <v>655855</v>
       </c>
       <c r="R8" t="n">
-        <v>7122800</v>
+        <v>7122774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,12 +1392,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918405</v>
+        <v>126914199</v>
       </c>
       <c r="B9" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,37 +1419,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655901</v>
+        <v>655888</v>
       </c>
       <c r="R9" t="n">
-        <v>7122844</v>
+        <v>7122973</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,9 +1476,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Peder Winding, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126910394</v>
+        <v>126916284</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655885</v>
+        <v>655943</v>
       </c>
       <c r="R10" t="n">
-        <v>7122738</v>
+        <v>7122816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126916289</v>
+        <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655996</v>
+        <v>655906</v>
       </c>
       <c r="R31" t="n">
-        <v>7122934</v>
+        <v>7122852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B32" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R32" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916288</v>
+        <v>126916289</v>
       </c>
       <c r="B33" t="n">
         <v>78773</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655965</v>
+        <v>655996</v>
       </c>
       <c r="R33" t="n">
-        <v>7122873</v>
+        <v>7122934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -8351,32 +8351,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126915964</v>
+        <v>126916729</v>
       </c>
       <c r="B76" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655800</v>
+        <v>655892</v>
       </c>
       <c r="R76" t="n">
-        <v>7122929</v>
+        <v>7122748</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8422,6 +8422,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8436,12 +8441,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8452,32 +8457,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126917772</v>
+        <v>126915964</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,13 +8492,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655768</v>
+        <v>655800</v>
       </c>
       <c r="R77" t="n">
-        <v>7122903</v>
+        <v>7122929</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8537,12 +8542,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8553,45 +8558,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126918050</v>
+        <v>126917772</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656266</v>
+        <v>655768</v>
       </c>
       <c r="R78" t="n">
-        <v>7122789</v>
+        <v>7122903</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8635,30 +8640,15 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8669,10 +8659,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915970</v>
+        <v>126918050</v>
       </c>
       <c r="B79" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8680,37 +8670,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655778</v>
+        <v>656266</v>
       </c>
       <c r="R79" t="n">
-        <v>7122904</v>
+        <v>7122789</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8750,16 +8740,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8770,10 +8775,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126919806</v>
+        <v>126915970</v>
       </c>
       <c r="B80" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,21 +8786,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,13 +8810,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655917</v>
+        <v>655778</v>
       </c>
       <c r="R80" t="n">
-        <v>7122874</v>
+        <v>7122904</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8855,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8871,10 +8876,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918404</v>
+        <v>126919806</v>
       </c>
       <c r="B81" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8882,21 +8887,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8906,10 +8911,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655901</v>
+        <v>655917</v>
       </c>
       <c r="R81" t="n">
-        <v>7122844</v>
+        <v>7122874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8956,12 +8961,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, Peder Winding</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8972,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915963</v>
+        <v>126918404</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8983,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9007,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655813</v>
+        <v>655901</v>
       </c>
       <c r="R82" t="n">
-        <v>7122846</v>
+        <v>7122844</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9057,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9073,7 +9078,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126916286</v>
+        <v>126915963</v>
       </c>
       <c r="B83" t="n">
         <v>78773</v>
@@ -9108,13 +9113,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655866</v>
+        <v>655813</v>
       </c>
       <c r="R83" t="n">
-        <v>7122779</v>
+        <v>7122846</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9158,12 +9163,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9174,32 +9179,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916729</v>
+        <v>126916286</v>
       </c>
       <c r="B84" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9209,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655892</v>
+        <v>655866</v>
       </c>
       <c r="R84" t="n">
-        <v>7122748</v>
+        <v>7122779</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9247,11 +9252,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918681</v>
+        <v>126915962</v>
       </c>
       <c r="B95" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656291</v>
+        <v>655854</v>
       </c>
       <c r="R95" t="n">
-        <v>7122808</v>
+        <v>7122777</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918713</v>
+        <v>126916276</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656004</v>
+        <v>655925</v>
       </c>
       <c r="R96" t="n">
-        <v>7122974</v>
+        <v>7122825</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918395</v>
+        <v>126914201</v>
       </c>
       <c r="B97" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,37 +10534,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655892</v>
+        <v>655947</v>
       </c>
       <c r="R97" t="n">
-        <v>7122986</v>
+        <v>7122837</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,9 +10591,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10608,12 +10618,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,32 +10634,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126915962</v>
+        <v>126916313</v>
       </c>
       <c r="B98" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,13 +10669,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655854</v>
+        <v>656087</v>
       </c>
       <c r="R98" t="n">
-        <v>7122777</v>
+        <v>7122806</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10709,12 +10719,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126916276</v>
+        <v>126918713</v>
       </c>
       <c r="B99" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10736,21 +10746,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,10 +10770,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655925</v>
+        <v>656004</v>
       </c>
       <c r="R99" t="n">
-        <v>7122825</v>
+        <v>7122974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10810,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,10 +10836,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126914201</v>
+        <v>126918395</v>
       </c>
       <c r="B100" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10837,37 +10847,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655947</v>
+        <v>655892</v>
       </c>
       <c r="R100" t="n">
-        <v>7122837</v>
+        <v>7122986</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10894,19 +10904,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,32 +10937,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126916313</v>
+        <v>126918681</v>
       </c>
       <c r="B101" t="n">
-        <v>92615</v>
+        <v>80117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656087</v>
+        <v>656291</v>
       </c>
       <c r="R101" t="n">
-        <v>7122806</v>
+        <v>7122808</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126910130</v>
+        <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>79603</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655841</v>
+        <v>655893</v>
       </c>
       <c r="R3" t="n">
-        <v>7122800</v>
+        <v>7122779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,32 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916314</v>
+        <v>126918405</v>
       </c>
       <c r="B4" t="n">
-        <v>92615</v>
+        <v>77992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655893</v>
+        <v>655901</v>
       </c>
       <c r="R4" t="n">
-        <v>7122779</v>
+        <v>7122844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126910394</v>
+        <v>126916285</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655885</v>
+        <v>655855</v>
       </c>
       <c r="R5" t="n">
-        <v>7122738</v>
+        <v>7122774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918405</v>
+        <v>126914199</v>
       </c>
       <c r="B6" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,37 +1101,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655901</v>
+        <v>655888</v>
       </c>
       <c r="R6" t="n">
-        <v>7122844</v>
+        <v>7122973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,9 +1158,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,12 +1185,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Peder Winding, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1191,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916842</v>
+        <v>126916284</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655948</v>
+        <v>655943</v>
       </c>
       <c r="R7" t="n">
-        <v>7122908</v>
+        <v>7122816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,19 +1269,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,12 +1286,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126916285</v>
+        <v>126910130</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655855</v>
+        <v>655841</v>
       </c>
       <c r="R8" t="n">
-        <v>7122774</v>
+        <v>7122800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1387,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1408,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126914199</v>
+        <v>126910394</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,37 +1414,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655888</v>
+        <v>655885</v>
       </c>
       <c r="R9" t="n">
-        <v>7122973</v>
+        <v>7122738</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1476,19 +1471,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,45 +1504,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916284</v>
+        <v>126916842</v>
       </c>
       <c r="B10" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655943</v>
+        <v>655948</v>
       </c>
       <c r="R10" t="n">
-        <v>7122816</v>
+        <v>7122908</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,9 +1577,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1724,7 +1724,7 @@
         <v>126916316</v>
       </c>
       <c r="B12" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918044</v>
+        <v>126918421</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656088</v>
+        <v>655890</v>
       </c>
       <c r="R13" t="n">
-        <v>7122850</v>
+        <v>7122888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,30 +1904,15 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1938,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126918044</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,34 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>656088</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,15 +2005,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916844</v>
+        <v>126916299</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655905</v>
+        <v>655995</v>
       </c>
       <c r="R15" t="n">
-        <v>7122985</v>
+        <v>7122921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,21 +2107,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2130,36 +2120,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,32 +2140,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126919792</v>
+        <v>126916844</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655919</v>
+        <v>655905</v>
       </c>
       <c r="R16" t="n">
-        <v>7122887</v>
+        <v>7122985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,14 +2208,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spilning</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,16 +2231,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2276,32 +2271,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918421</v>
+        <v>126919792</v>
       </c>
       <c r="B17" t="n">
-        <v>92808</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655890</v>
+        <v>655919</v>
       </c>
       <c r="R17" t="n">
-        <v>7122888</v>
+        <v>7122887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,6 +2344,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2361,12 +2361,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peder Winding, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, kristina stenmarck, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126918712</v>
+        <v>126918424</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655899</v>
+        <v>655961</v>
       </c>
       <c r="R26" t="n">
-        <v>7122835</v>
+        <v>7122865</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917813</v>
+        <v>126918712</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655710</v>
+        <v>655899</v>
       </c>
       <c r="R27" t="n">
-        <v>7122853</v>
+        <v>7122835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918424</v>
+        <v>126910403</v>
       </c>
       <c r="B28" t="n">
-        <v>92808</v>
+        <v>79603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655961</v>
+        <v>655885</v>
       </c>
       <c r="R28" t="n">
-        <v>7122865</v>
+        <v>7122738</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3506,7 +3506,7 @@
         <v>126916397</v>
       </c>
       <c r="B29" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126910403</v>
+        <v>126917813</v>
       </c>
       <c r="B30" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655885</v>
+        <v>655710</v>
       </c>
       <c r="R30" t="n">
-        <v>7122738</v>
+        <v>7122853</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4011,7 +4011,7 @@
         <v>126916746</v>
       </c>
       <c r="B34" t="n">
-        <v>91899</v>
+        <v>91900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918458</v>
+        <v>126920137</v>
       </c>
       <c r="B35" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4116,21 +4116,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655914</v>
+        <v>655990</v>
       </c>
       <c r="R35" t="n">
-        <v>7122985</v>
+        <v>7122926</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,12 +4190,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126920137</v>
+        <v>126918458</v>
       </c>
       <c r="B36" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655990</v>
+        <v>655914</v>
       </c>
       <c r="R36" t="n">
-        <v>7122926</v>
+        <v>7122985</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,12 +4291,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917825</v>
+        <v>126916741</v>
       </c>
       <c r="B45" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655749</v>
+        <v>655895</v>
       </c>
       <c r="R45" t="n">
-        <v>7122779</v>
+        <v>7122747</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916741</v>
+        <v>126916272</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655895</v>
+        <v>655957</v>
       </c>
       <c r="R46" t="n">
-        <v>7122747</v>
+        <v>7122864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126916272</v>
+        <v>126917825</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>77992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655957</v>
+        <v>655749</v>
       </c>
       <c r="R47" t="n">
-        <v>7122864</v>
+        <v>7122779</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919778</v>
+        <v>126918397</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655919</v>
+        <v>655892</v>
       </c>
       <c r="R51" t="n">
-        <v>7122981</v>
+        <v>7122986</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126918397</v>
+        <v>126919778</v>
       </c>
       <c r="B53" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655892</v>
+        <v>655919</v>
       </c>
       <c r="R53" t="n">
-        <v>7122986</v>
+        <v>7122981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R57" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,30 +6424,15 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6458,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B58" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6469,34 +6454,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R58" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,15 +6525,30 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126916312</v>
+        <v>126917791</v>
       </c>
       <c r="B59" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656104</v>
+        <v>656327</v>
       </c>
       <c r="R59" t="n">
-        <v>7122796</v>
+        <v>7122772</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,12 +6644,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126917803</v>
+        <v>126916274</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>79603</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655792</v>
+        <v>656012</v>
       </c>
       <c r="R60" t="n">
-        <v>7122889</v>
+        <v>7122821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6745,12 +6745,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6761,10 +6761,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126915955</v>
+        <v>126918045</v>
       </c>
       <c r="B61" t="n">
-        <v>92641</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,40 +6772,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655885</v>
+        <v>656177</v>
       </c>
       <c r="R61" t="n">
-        <v>7122754</v>
+        <v>7122815</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6843,19 +6840,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6866,10 +6877,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916745</v>
+        <v>126919808</v>
       </c>
       <c r="B62" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6877,21 +6888,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6901,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655840</v>
+        <v>655921</v>
       </c>
       <c r="R62" t="n">
-        <v>7122839</v>
+        <v>7122999</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,19 +6962,23 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Peder Winding, Anders Heggestad, Lisa Requin, Lise Mortensen, Mattias Dalkvist, Nicklas Gustavsson, Miriam Schenk, Jennica Andersson, Beke Regelin, Torbjörn Söderquist, Elin Kannerby, Carl Jansson, kristina stenmarck</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918047</v>
+        <v>126916745</v>
       </c>
       <c r="B63" t="n">
         <v>78681</v>
@@ -6994,14 +7009,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656203</v>
+        <v>655840</v>
       </c>
       <c r="R63" t="n">
-        <v>7122806</v>
+        <v>7122839</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7045,44 +7060,25 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918041</v>
+        <v>126918047</v>
       </c>
       <c r="B64" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7090,21 +7086,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7114,10 +7110,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655965</v>
+        <v>656203</v>
       </c>
       <c r="R64" t="n">
-        <v>7122890</v>
+        <v>7122806</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7195,10 +7191,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126917763</v>
+        <v>126918041</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,34 +7202,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656241</v>
+        <v>655965</v>
       </c>
       <c r="R65" t="n">
-        <v>7122853</v>
+        <v>7122890</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,15 +7273,30 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7296,32 +7307,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917791</v>
+        <v>126916312</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7331,10 +7342,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656327</v>
+        <v>656104</v>
       </c>
       <c r="R66" t="n">
-        <v>7122772</v>
+        <v>7122796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7381,12 +7392,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7397,10 +7408,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126919808</v>
+        <v>126915955</v>
       </c>
       <c r="B67" t="n">
-        <v>78773</v>
+        <v>92642</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,37 +7419,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>5448</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>655921</v>
+        <v>655885</v>
       </c>
       <c r="R67" t="n">
-        <v>7122999</v>
+        <v>7122754</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7476,18 +7490,19 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7498,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126916274</v>
+        <v>126917763</v>
       </c>
       <c r="B68" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,21 +7524,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7548,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656012</v>
+        <v>656241</v>
       </c>
       <c r="R68" t="n">
-        <v>7122821</v>
+        <v>7122853</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7583,12 +7598,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7599,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126918045</v>
+        <v>126917803</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,34 +7625,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>656177</v>
+        <v>655792</v>
       </c>
       <c r="R69" t="n">
-        <v>7122815</v>
+        <v>7122889</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,30 +7696,15 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7715,32 +7715,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918422</v>
+        <v>126918443</v>
       </c>
       <c r="B70" t="n">
-        <v>91486</v>
+        <v>80989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655890</v>
+        <v>655875</v>
       </c>
       <c r="R70" t="n">
-        <v>7122888</v>
+        <v>7122959</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7796,6 +7796,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -7816,32 +7831,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918443</v>
+        <v>126916315</v>
       </c>
       <c r="B71" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7851,10 +7866,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655875</v>
+        <v>655879</v>
       </c>
       <c r="R71" t="n">
-        <v>7122959</v>
+        <v>7122817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7898,30 +7913,15 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,32 +7932,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126916315</v>
+        <v>126918422</v>
       </c>
       <c r="B72" t="n">
-        <v>92615</v>
+        <v>91487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655879</v>
+        <v>655890</v>
       </c>
       <c r="R72" t="n">
-        <v>7122817</v>
+        <v>7122888</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,45 +8033,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918650</v>
+        <v>126918042</v>
       </c>
       <c r="B73" t="n">
-        <v>80146</v>
+        <v>78420</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656291</v>
+        <v>655954</v>
       </c>
       <c r="R73" t="n">
-        <v>7122816</v>
+        <v>7122886</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8115,15 +8115,30 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,10 +8149,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918042</v>
+        <v>126917789</v>
       </c>
       <c r="B74" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8145,34 +8160,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655954</v>
+        <v>655760</v>
       </c>
       <c r="R74" t="n">
-        <v>7122886</v>
+        <v>7122811</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,30 +8231,15 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917789</v>
+        <v>126918650</v>
       </c>
       <c r="B75" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655760</v>
+        <v>656291</v>
       </c>
       <c r="R75" t="n">
-        <v>7122811</v>
+        <v>7122816</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,45 +8351,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916729</v>
+        <v>126918050</v>
       </c>
       <c r="B76" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655892</v>
+        <v>656266</v>
       </c>
       <c r="R76" t="n">
-        <v>7122748</v>
+        <v>7122789</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,11 +8424,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8437,16 +8432,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8457,10 +8467,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915964</v>
+        <v>126915970</v>
       </c>
       <c r="B77" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8468,21 +8478,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8492,10 +8502,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655800</v>
+        <v>655778</v>
       </c>
       <c r="R77" t="n">
-        <v>7122929</v>
+        <v>7122904</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8558,32 +8568,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126917772</v>
+        <v>126915964</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8593,13 +8603,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655768</v>
+        <v>655800</v>
       </c>
       <c r="R78" t="n">
-        <v>7122903</v>
+        <v>7122929</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8643,12 +8653,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8659,45 +8669,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918050</v>
+        <v>126917772</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656266</v>
+        <v>655768</v>
       </c>
       <c r="R79" t="n">
-        <v>7122789</v>
+        <v>7122903</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8741,30 +8751,15 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8775,32 +8770,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126915970</v>
+        <v>126916729</v>
       </c>
       <c r="B80" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8810,13 +8805,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655778</v>
+        <v>655892</v>
       </c>
       <c r="R80" t="n">
-        <v>7122904</v>
+        <v>7122748</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8846,6 +8841,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8860,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>126918104</v>
       </c>
       <c r="B85" t="n">
-        <v>92609</v>
+        <v>92610</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918040</v>
+        <v>126915959</v>
       </c>
       <c r="B86" t="n">
-        <v>78681</v>
+        <v>92809</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655945</v>
+        <v>655849</v>
       </c>
       <c r="R86" t="n">
-        <v>7122909</v>
+        <v>7122806</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9462,31 +9462,16 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9599,10 +9584,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126915959</v>
+        <v>126918040</v>
       </c>
       <c r="B88" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9610,37 +9595,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655849</v>
+        <v>655945</v>
       </c>
       <c r="R88" t="n">
-        <v>7122806</v>
+        <v>7122909</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9680,16 +9665,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9804,7 +9804,7 @@
         <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918038</v>
+        <v>126918711</v>
       </c>
       <c r="B91" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,34 +9913,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655904</v>
+        <v>655898</v>
       </c>
       <c r="R91" t="n">
-        <v>7122984</v>
+        <v>7122802</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,30 +9984,15 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10018,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918711</v>
+        <v>126918038</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,34 +10014,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655898</v>
+        <v>655904</v>
       </c>
       <c r="R92" t="n">
-        <v>7122802</v>
+        <v>7122984</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10100,15 +10085,30 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126915962</v>
+        <v>126918713</v>
       </c>
       <c r="B95" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>655854</v>
+        <v>656004</v>
       </c>
       <c r="R95" t="n">
-        <v>7122777</v>
+        <v>7122974</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126916276</v>
+        <v>126918681</v>
       </c>
       <c r="B96" t="n">
-        <v>79603</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655925</v>
+        <v>656291</v>
       </c>
       <c r="R96" t="n">
-        <v>7122825</v>
+        <v>7122808</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126914201</v>
+        <v>126915962</v>
       </c>
       <c r="B97" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,37 +10534,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655947</v>
+        <v>655854</v>
       </c>
       <c r="R97" t="n">
-        <v>7122837</v>
+        <v>7122777</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,19 +10591,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10618,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10634,32 +10624,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126916313</v>
+        <v>126916276</v>
       </c>
       <c r="B98" t="n">
-        <v>92615</v>
+        <v>79603</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10669,10 +10659,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656087</v>
+        <v>655925</v>
       </c>
       <c r="R98" t="n">
-        <v>7122806</v>
+        <v>7122825</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10735,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918713</v>
+        <v>126914201</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10746,37 +10736,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656004</v>
+        <v>655947</v>
       </c>
       <c r="R99" t="n">
-        <v>7122974</v>
+        <v>7122837</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10803,9 +10793,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10820,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,32 +10836,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918395</v>
+        <v>126916313</v>
       </c>
       <c r="B100" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655892</v>
+        <v>656087</v>
       </c>
       <c r="R100" t="n">
-        <v>7122986</v>
+        <v>7122806</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918681</v>
+        <v>126918395</v>
       </c>
       <c r="B101" t="n">
-        <v>80117</v>
+        <v>79632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,21 +10948,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656291</v>
+        <v>655892</v>
       </c>
       <c r="R101" t="n">
-        <v>7122808</v>
+        <v>7122986</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11139,45 +11139,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918407</v>
+        <v>126918049</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655901</v>
+        <v>656225</v>
       </c>
       <c r="R103" t="n">
-        <v>7122844</v>
+        <v>7122794</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11221,15 +11226,30 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11240,50 +11260,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R104" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11327,30 +11342,15 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11361,10 +11361,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126916277</v>
+        <v>126918407</v>
       </c>
       <c r="B105" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11372,21 +11372,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655921</v>
+        <v>655901</v>
       </c>
       <c r="R105" t="n">
-        <v>7122873</v>
+        <v>7122844</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,12 +11446,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126918657</v>
+        <v>126919802</v>
       </c>
       <c r="B107" t="n">
-        <v>58087</v>
+        <v>78773</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655908</v>
+        <v>656007</v>
       </c>
       <c r="R107" t="n">
-        <v>7122774</v>
+        <v>7122964</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126919802</v>
+        <v>126916275</v>
       </c>
       <c r="B108" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656007</v>
+        <v>655900</v>
       </c>
       <c r="R108" t="n">
-        <v>7122964</v>
+        <v>7122800</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,12 +11749,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,10 +11765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126916275</v>
+        <v>126920127</v>
       </c>
       <c r="B109" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,21 +11776,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>655900</v>
+        <v>656146</v>
       </c>
       <c r="R109" t="n">
-        <v>7122800</v>
+        <v>7122791</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,18 +11844,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11866,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920127</v>
+        <v>126920120</v>
       </c>
       <c r="B110" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11877,21 +11878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11901,10 +11902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656146</v>
+        <v>655982</v>
       </c>
       <c r="R110" t="n">
-        <v>7122791</v>
+        <v>7122865</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11945,7 +11946,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126920120</v>
+        <v>126918657</v>
       </c>
       <c r="B111" t="n">
-        <v>79603</v>
+        <v>58087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655982</v>
+        <v>655908</v>
       </c>
       <c r="R111" t="n">
-        <v>7122865</v>
+        <v>7122774</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918405</v>
+        <v>126910394</v>
       </c>
       <c r="B4" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655901</v>
+        <v>655885</v>
       </c>
       <c r="R4" t="n">
-        <v>7122844</v>
+        <v>7122738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916285</v>
+        <v>126918405</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655855</v>
+        <v>655901</v>
       </c>
       <c r="R5" t="n">
-        <v>7122774</v>
+        <v>7122844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,48 +1090,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126914199</v>
+        <v>126916842</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655888</v>
+        <v>655948</v>
       </c>
       <c r="R6" t="n">
-        <v>7122973</v>
+        <v>7122908</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1170,7 +1175,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1201,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916284</v>
+        <v>126916285</v>
       </c>
       <c r="B7" t="n">
         <v>78773</v>
@@ -1236,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655943</v>
+        <v>655855</v>
       </c>
       <c r="R7" t="n">
-        <v>7122816</v>
+        <v>7122774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126910130</v>
+        <v>126914199</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655841</v>
+        <v>655888</v>
       </c>
       <c r="R8" t="n">
-        <v>7122800</v>
+        <v>7122973</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,9 +1375,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,12 +1402,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1403,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126910394</v>
+        <v>126916284</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655885</v>
+        <v>655943</v>
       </c>
       <c r="R9" t="n">
-        <v>7122738</v>
+        <v>7122816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1504,50 +1519,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916842</v>
+        <v>126910130</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655948</v>
+        <v>655841</v>
       </c>
       <c r="R10" t="n">
-        <v>7122908</v>
+        <v>7122800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,19 +1587,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,32 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916306</v>
+        <v>126916316</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655956</v>
+        <v>655863</v>
       </c>
       <c r="R11" t="n">
-        <v>7122866</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916316</v>
+        <v>126918421</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655863</v>
+        <v>655890</v>
       </c>
       <c r="R12" t="n">
-        <v>7122755</v>
+        <v>7122888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918421</v>
+        <v>126918044</v>
       </c>
       <c r="B13" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655890</v>
+        <v>656088</v>
       </c>
       <c r="R13" t="n">
-        <v>7122888</v>
+        <v>7122850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,15 +1904,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918044</v>
+        <v>126916299</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1949,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656088</v>
+        <v>655995</v>
       </c>
       <c r="R14" t="n">
-        <v>7122850</v>
+        <v>7122921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,30 +2020,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916299</v>
+        <v>126916844</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655995</v>
+        <v>655905</v>
       </c>
       <c r="R15" t="n">
-        <v>7122921</v>
+        <v>7122985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,11 +2107,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2120,16 +2130,36 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916844</v>
+        <v>126918646</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655905</v>
+        <v>656298</v>
       </c>
       <c r="R16" t="n">
-        <v>7122985</v>
+        <v>7122812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,21 +2238,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2231,36 +2251,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,32 +2271,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126919792</v>
+        <v>126916278</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655919</v>
+        <v>655957</v>
       </c>
       <c r="R17" t="n">
-        <v>7122887</v>
+        <v>7122864</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,11 +2344,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2361,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918646</v>
+        <v>126917770</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>79603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656298</v>
+        <v>655852</v>
       </c>
       <c r="R18" t="n">
-        <v>7122812</v>
+        <v>7122942</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,7 +2473,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916278</v>
+        <v>126909344</v>
       </c>
       <c r="B19" t="n">
         <v>79603</v>
@@ -2513,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655957</v>
+        <v>655890</v>
       </c>
       <c r="R19" t="n">
-        <v>7122864</v>
+        <v>7122814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,12 +2558,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2579,10 +2574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917770</v>
+        <v>126916306</v>
       </c>
       <c r="B20" t="n">
-        <v>79603</v>
+        <v>78681</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,21 +2585,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655852</v>
+        <v>655956</v>
       </c>
       <c r="R20" t="n">
-        <v>7122942</v>
+        <v>7122866</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2659,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,32 +2675,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126909344</v>
+        <v>126919792</v>
       </c>
       <c r="B21" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655890</v>
+        <v>655919</v>
       </c>
       <c r="R21" t="n">
-        <v>7122814</v>
+        <v>7122887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,6 +2748,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126918424</v>
+        <v>126918712</v>
       </c>
       <c r="B26" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655961</v>
+        <v>655899</v>
       </c>
       <c r="R26" t="n">
-        <v>7122865</v>
+        <v>7122835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918712</v>
+        <v>126918424</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655899</v>
+        <v>655961</v>
       </c>
       <c r="R27" t="n">
-        <v>7122835</v>
+        <v>7122865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,32 +3402,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126910403</v>
+        <v>126916397</v>
       </c>
       <c r="B28" t="n">
-        <v>79603</v>
+        <v>92616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655885</v>
+        <v>655893</v>
       </c>
       <c r="R28" t="n">
-        <v>7122738</v>
+        <v>7122752</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126916397</v>
+        <v>126917813</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655893</v>
+        <v>655710</v>
       </c>
       <c r="R29" t="n">
-        <v>7122752</v>
+        <v>7122853</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126917813</v>
+        <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655710</v>
+        <v>655885</v>
       </c>
       <c r="R30" t="n">
-        <v>7122853</v>
+        <v>7122738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R31" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916288</v>
+        <v>126916289</v>
       </c>
       <c r="B32" t="n">
         <v>78773</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655965</v>
+        <v>655996</v>
       </c>
       <c r="R32" t="n">
-        <v>7122873</v>
+        <v>7122934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916289</v>
+        <v>126918450</v>
       </c>
       <c r="B33" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655996</v>
+        <v>655906</v>
       </c>
       <c r="R33" t="n">
-        <v>7122934</v>
+        <v>7122852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918458</v>
+        <v>126918438</v>
       </c>
       <c r="B36" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655914</v>
+        <v>655882</v>
       </c>
       <c r="R36" t="n">
-        <v>7122985</v>
+        <v>7122978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126917804</v>
+        <v>126919804</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655834</v>
+        <v>655989</v>
       </c>
       <c r="R37" t="n">
-        <v>7122923</v>
+        <v>7122922</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4408,10 +4408,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126918438</v>
+        <v>126918037</v>
       </c>
       <c r="B38" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,34 +4419,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655882</v>
+        <v>655903</v>
       </c>
       <c r="R38" t="n">
-        <v>7122978</v>
+        <v>7122984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,15 +4490,30 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4509,7 +4524,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919804</v>
+        <v>126916287</v>
       </c>
       <c r="B39" t="n">
         <v>78773</v>
@@ -4544,10 +4559,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655989</v>
+        <v>655900</v>
       </c>
       <c r="R39" t="n">
-        <v>7122922</v>
+        <v>7122798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,12 +4609,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4610,10 +4625,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918037</v>
+        <v>126918458</v>
       </c>
       <c r="B40" t="n">
-        <v>79603</v>
+        <v>78420</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,34 +4636,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655903</v>
+        <v>655914</v>
       </c>
       <c r="R40" t="n">
-        <v>7122984</v>
+        <v>7122985</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,30 +4707,15 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126916287</v>
+        <v>126917804</v>
       </c>
       <c r="B41" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655900</v>
+        <v>655834</v>
       </c>
       <c r="R41" t="n">
-        <v>7122798</v>
+        <v>7122923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126916304</v>
+        <v>126917830</v>
       </c>
       <c r="B42" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655978</v>
+        <v>655749</v>
       </c>
       <c r="R42" t="n">
-        <v>7122825</v>
+        <v>7122779</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4928,7 +4928,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126920136</v>
+        <v>126916304</v>
       </c>
       <c r="B43" t="n">
         <v>78681</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655941</v>
+        <v>655978</v>
       </c>
       <c r="R43" t="n">
-        <v>7122804</v>
+        <v>7122825</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,12 +5013,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126917830</v>
+        <v>126920136</v>
       </c>
       <c r="B44" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655749</v>
+        <v>655941</v>
       </c>
       <c r="R44" t="n">
-        <v>7122779</v>
+        <v>7122804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126918397</v>
+        <v>126920128</v>
       </c>
       <c r="B51" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655892</v>
+        <v>655942</v>
       </c>
       <c r="R51" t="n">
-        <v>7122986</v>
+        <v>7122804</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126910294</v>
+        <v>126915088</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655845</v>
+        <v>655950</v>
       </c>
       <c r="R52" t="n">
-        <v>7122750</v>
+        <v>7122893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126919778</v>
+        <v>126918672</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655919</v>
+        <v>655882</v>
       </c>
       <c r="R53" t="n">
-        <v>7122981</v>
+        <v>7122787</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126920128</v>
+        <v>126918397</v>
       </c>
       <c r="B54" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655942</v>
+        <v>655892</v>
       </c>
       <c r="R54" t="n">
-        <v>7122804</v>
+        <v>7122986</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915088</v>
+        <v>126910294</v>
       </c>
       <c r="B55" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655950</v>
+        <v>655845</v>
       </c>
       <c r="R55" t="n">
-        <v>7122893</v>
+        <v>7122750</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918672</v>
+        <v>126919778</v>
       </c>
       <c r="B56" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655882</v>
+        <v>655919</v>
       </c>
       <c r="R56" t="n">
-        <v>7122787</v>
+        <v>7122981</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -8149,32 +8149,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126917789</v>
+        <v>126918650</v>
       </c>
       <c r="B74" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655760</v>
+        <v>656291</v>
       </c>
       <c r="R74" t="n">
-        <v>7122811</v>
+        <v>7122816</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8234,12 +8234,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918650</v>
+        <v>126917789</v>
       </c>
       <c r="B75" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656291</v>
+        <v>655760</v>
       </c>
       <c r="R75" t="n">
-        <v>7122816</v>
+        <v>7122811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126918050</v>
+        <v>126915964</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,37 +8362,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656266</v>
+        <v>655800</v>
       </c>
       <c r="R76" t="n">
-        <v>7122789</v>
+        <v>7122929</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8432,31 +8432,16 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8467,32 +8452,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915970</v>
+        <v>126917772</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8502,13 +8487,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655778</v>
+        <v>655768</v>
       </c>
       <c r="R77" t="n">
-        <v>7122904</v>
+        <v>7122903</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8552,12 +8537,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8568,32 +8553,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915964</v>
+        <v>126916729</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>56849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8603,13 +8588,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655800</v>
+        <v>655892</v>
       </c>
       <c r="R78" t="n">
-        <v>7122929</v>
+        <v>7122748</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8639,6 +8624,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8653,12 +8643,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8669,32 +8659,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126917772</v>
+        <v>126919806</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655768</v>
+        <v>655917</v>
       </c>
       <c r="R79" t="n">
-        <v>7122903</v>
+        <v>7122874</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8754,12 +8744,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8770,32 +8760,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916729</v>
+        <v>126918404</v>
       </c>
       <c r="B80" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,10 +8795,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655892</v>
+        <v>655901</v>
       </c>
       <c r="R80" t="n">
-        <v>7122748</v>
+        <v>7122844</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,11 +8833,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8860,12 +8845,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8876,7 +8861,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126919806</v>
+        <v>126915963</v>
       </c>
       <c r="B81" t="n">
         <v>78773</v>
@@ -8911,13 +8896,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655917</v>
+        <v>655813</v>
       </c>
       <c r="R81" t="n">
-        <v>7122874</v>
+        <v>7122846</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8961,12 +8946,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8962,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918404</v>
+        <v>126916286</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8973,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,10 +8997,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655901</v>
+        <v>655866</v>
       </c>
       <c r="R82" t="n">
-        <v>7122844</v>
+        <v>7122779</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9062,12 +9047,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,10 +9063,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915963</v>
+        <v>126918050</v>
       </c>
       <c r="B83" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9089,37 +9074,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655813</v>
+        <v>656266</v>
       </c>
       <c r="R83" t="n">
-        <v>7122846</v>
+        <v>7122789</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9159,16 +9144,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916286</v>
+        <v>126915970</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,13 +9214,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655866</v>
+        <v>655778</v>
       </c>
       <c r="R84" t="n">
-        <v>7122779</v>
+        <v>7122904</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126915959</v>
+        <v>126918040</v>
       </c>
       <c r="B86" t="n">
-        <v>92809</v>
+        <v>78681</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655849</v>
+        <v>655945</v>
       </c>
       <c r="R86" t="n">
-        <v>7122806</v>
+        <v>7122909</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9462,16 +9462,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,10 +9497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126916394</v>
+        <v>126915959</v>
       </c>
       <c r="B87" t="n">
-        <v>78772</v>
+        <v>92809</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9493,21 +9508,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9517,10 +9532,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655798</v>
+        <v>655849</v>
       </c>
       <c r="R87" t="n">
-        <v>7122934</v>
+        <v>7122806</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9561,7 +9576,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9573,7 +9587,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9584,10 +9598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126918040</v>
+        <v>126916394</v>
       </c>
       <c r="B88" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9595,37 +9609,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655945</v>
+        <v>655798</v>
       </c>
       <c r="R88" t="n">
-        <v>7122909</v>
+        <v>7122934</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9663,33 +9677,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918423</v>
+        <v>126918711</v>
       </c>
       <c r="B90" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655881</v>
+        <v>655898</v>
       </c>
       <c r="R90" t="n">
-        <v>7122919</v>
+        <v>7122802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918711</v>
+        <v>126918038</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,34 +9913,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655898</v>
+        <v>655904</v>
       </c>
       <c r="R91" t="n">
-        <v>7122802</v>
+        <v>7122984</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,15 +9984,30 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10003,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918038</v>
+        <v>126918100</v>
       </c>
       <c r="B92" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10014,37 +10029,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655904</v>
+        <v>655957</v>
       </c>
       <c r="R92" t="n">
-        <v>7122984</v>
+        <v>7122879</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10084,31 +10099,16 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,7 +10119,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918100</v>
+        <v>126917788</v>
       </c>
       <c r="B93" t="n">
         <v>78773</v>
@@ -10150,17 +10150,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655957</v>
+        <v>655780</v>
       </c>
       <c r="R93" t="n">
-        <v>7122879</v>
+        <v>7122780</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10204,12 +10204,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126917788</v>
+        <v>126918423</v>
       </c>
       <c r="B94" t="n">
-        <v>78773</v>
+        <v>92809</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655780</v>
+        <v>655881</v>
       </c>
       <c r="R94" t="n">
-        <v>7122780</v>
+        <v>7122919</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916314</v>
+        <v>126916842</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655893</v>
+        <v>655948</v>
       </c>
       <c r="R3" t="n">
-        <v>7122779</v>
+        <v>7122908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,9 +860,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126916314</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655893</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +988,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918405</v>
+        <v>126910394</v>
       </c>
       <c r="B5" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655901</v>
+        <v>655885</v>
       </c>
       <c r="R5" t="n">
-        <v>7122844</v>
+        <v>7122738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1089,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,50 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916842</v>
+        <v>126918405</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>77992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655948</v>
+        <v>655901</v>
       </c>
       <c r="R6" t="n">
-        <v>7122908</v>
+        <v>7122844</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,19 +1173,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1620,32 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916316</v>
+        <v>126916306</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655863</v>
+        <v>655956</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918421</v>
+        <v>126916316</v>
       </c>
       <c r="B12" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655890</v>
+        <v>655863</v>
       </c>
       <c r="R12" t="n">
-        <v>7122888</v>
+        <v>7122755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918044</v>
+        <v>126918421</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656088</v>
+        <v>655890</v>
       </c>
       <c r="R13" t="n">
-        <v>7122850</v>
+        <v>7122888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,30 +1904,15 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1938,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126918044</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,34 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>656088</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,15 +2005,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916844</v>
+        <v>126916299</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655905</v>
+        <v>655995</v>
       </c>
       <c r="R15" t="n">
-        <v>7122985</v>
+        <v>7122921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,21 +2107,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2130,36 +2120,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918646</v>
+        <v>126916844</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656298</v>
+        <v>655905</v>
       </c>
       <c r="R16" t="n">
-        <v>7122812</v>
+        <v>7122985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,11 +2208,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2251,16 +2231,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916278</v>
+        <v>126918646</v>
       </c>
       <c r="B17" t="n">
-        <v>79603</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655957</v>
+        <v>656298</v>
       </c>
       <c r="R17" t="n">
-        <v>7122864</v>
+        <v>7122812</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,32 +2372,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917770</v>
+        <v>126919792</v>
       </c>
       <c r="B18" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655852</v>
+        <v>655919</v>
       </c>
       <c r="R18" t="n">
-        <v>7122942</v>
+        <v>7122887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,6 +2445,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2457,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2473,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126909344</v>
+        <v>126916278</v>
       </c>
       <c r="B19" t="n">
         <v>79603</v>
@@ -2508,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655890</v>
+        <v>655957</v>
       </c>
       <c r="R19" t="n">
-        <v>7122814</v>
+        <v>7122864</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,12 +2563,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2574,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126916306</v>
+        <v>126917770</v>
       </c>
       <c r="B20" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2585,21 +2590,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655956</v>
+        <v>655852</v>
       </c>
       <c r="R20" t="n">
-        <v>7122866</v>
+        <v>7122942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2675,32 +2680,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126919792</v>
+        <v>126909344</v>
       </c>
       <c r="B21" t="n">
-        <v>56849</v>
+        <v>79603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655919</v>
+        <v>655890</v>
       </c>
       <c r="R21" t="n">
-        <v>7122887</v>
+        <v>7122814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,11 +2753,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918424</v>
+        <v>126917813</v>
       </c>
       <c r="B27" t="n">
-        <v>92809</v>
+        <v>78772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655961</v>
+        <v>655710</v>
       </c>
       <c r="R27" t="n">
-        <v>7122865</v>
+        <v>7122853</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917813</v>
+        <v>126918424</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>92809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655710</v>
+        <v>655961</v>
       </c>
       <c r="R29" t="n">
-        <v>7122853</v>
+        <v>7122865</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918438</v>
+        <v>126917804</v>
       </c>
       <c r="B36" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655882</v>
+        <v>655834</v>
       </c>
       <c r="R36" t="n">
-        <v>7122978</v>
+        <v>7122923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,12 +4291,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4307,7 +4307,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919804</v>
+        <v>126918438</v>
       </c>
       <c r="B37" t="n">
         <v>78773</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655989</v>
+        <v>655882</v>
       </c>
       <c r="R37" t="n">
-        <v>7122922</v>
+        <v>7122978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4408,10 +4408,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126918037</v>
+        <v>126919804</v>
       </c>
       <c r="B38" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,34 +4419,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655903</v>
+        <v>655989</v>
       </c>
       <c r="R38" t="n">
-        <v>7122984</v>
+        <v>7122922</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,30 +4490,15 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4524,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126916287</v>
+        <v>126918037</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4535,34 +4520,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655900</v>
+        <v>655903</v>
       </c>
       <c r="R39" t="n">
-        <v>7122798</v>
+        <v>7122984</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,15 +4591,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918458</v>
+        <v>126916287</v>
       </c>
       <c r="B40" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4636,21 +4636,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655914</v>
+        <v>655900</v>
       </c>
       <c r="R40" t="n">
-        <v>7122985</v>
+        <v>7122798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,12 +4710,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917804</v>
+        <v>126918458</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>78420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655834</v>
+        <v>655914</v>
       </c>
       <c r="R41" t="n">
-        <v>7122923</v>
+        <v>7122985</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126917830</v>
+        <v>126916304</v>
       </c>
       <c r="B42" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655749</v>
+        <v>655978</v>
       </c>
       <c r="R42" t="n">
-        <v>7122779</v>
+        <v>7122825</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4928,7 +4928,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126916304</v>
+        <v>126920136</v>
       </c>
       <c r="B43" t="n">
         <v>78681</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655978</v>
+        <v>655941</v>
       </c>
       <c r="R43" t="n">
-        <v>7122825</v>
+        <v>7122804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,12 +5013,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126920136</v>
+        <v>126917830</v>
       </c>
       <c r="B44" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655941</v>
+        <v>655749</v>
       </c>
       <c r="R44" t="n">
-        <v>7122804</v>
+        <v>7122779</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126916741</v>
+        <v>126917825</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655895</v>
+        <v>655749</v>
       </c>
       <c r="R45" t="n">
-        <v>7122747</v>
+        <v>7122779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126917825</v>
+        <v>126916741</v>
       </c>
       <c r="B47" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655749</v>
+        <v>655895</v>
       </c>
       <c r="R47" t="n">
-        <v>7122779</v>
+        <v>7122747</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126920128</v>
+        <v>126918397</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655942</v>
+        <v>655892</v>
       </c>
       <c r="R51" t="n">
-        <v>7122804</v>
+        <v>7122986</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,7 +5837,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126915088</v>
+        <v>126920128</v>
       </c>
       <c r="B52" t="n">
         <v>78773</v>
@@ -5868,14 +5868,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655950</v>
+        <v>655942</v>
       </c>
       <c r="R52" t="n">
-        <v>7122893</v>
+        <v>7122804</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,7 +5938,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126918672</v>
+        <v>126915088</v>
       </c>
       <c r="B53" t="n">
         <v>78773</v>
@@ -5969,14 +5969,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655882</v>
+        <v>655950</v>
       </c>
       <c r="R53" t="n">
-        <v>7122787</v>
+        <v>7122893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918397</v>
+        <v>126918672</v>
       </c>
       <c r="B54" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655892</v>
+        <v>655882</v>
       </c>
       <c r="R54" t="n">
-        <v>7122986</v>
+        <v>7122787</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126910294</v>
+        <v>126919778</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,21 +6151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655845</v>
+        <v>655919</v>
       </c>
       <c r="R55" t="n">
-        <v>7122750</v>
+        <v>7122981</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919778</v>
+        <v>126910294</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655919</v>
+        <v>655845</v>
       </c>
       <c r="R56" t="n">
-        <v>7122981</v>
+        <v>7122750</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126917791</v>
+        <v>126916312</v>
       </c>
       <c r="B59" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656327</v>
+        <v>656104</v>
       </c>
       <c r="R59" t="n">
-        <v>7122772</v>
+        <v>7122796</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,12 +6644,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126916274</v>
+        <v>126918041</v>
       </c>
       <c r="B60" t="n">
-        <v>79603</v>
+        <v>92809</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,34 +6671,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656012</v>
+        <v>655965</v>
       </c>
       <c r="R60" t="n">
-        <v>7122821</v>
+        <v>7122890</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6742,15 +6742,30 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6761,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918045</v>
+        <v>126917803</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,34 +6787,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656177</v>
+        <v>655792</v>
       </c>
       <c r="R61" t="n">
-        <v>7122815</v>
+        <v>7122889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,30 +6858,15 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,10 +6877,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919808</v>
+        <v>126917763</v>
       </c>
       <c r="B62" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6888,21 +6888,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655921</v>
+        <v>656241</v>
       </c>
       <c r="R62" t="n">
-        <v>7122999</v>
+        <v>7122853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,12 +6962,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7191,10 +7191,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918041</v>
+        <v>126915955</v>
       </c>
       <c r="B65" t="n">
-        <v>92809</v>
+        <v>92642</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7202,37 +7202,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>655965</v>
+        <v>655885</v>
       </c>
       <c r="R65" t="n">
-        <v>7122890</v>
+        <v>7122754</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7270,33 +7273,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7307,32 +7296,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126916312</v>
+        <v>126917791</v>
       </c>
       <c r="B66" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7342,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656104</v>
+        <v>656327</v>
       </c>
       <c r="R66" t="n">
-        <v>7122796</v>
+        <v>7122772</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,12 +7381,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7408,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126915955</v>
+        <v>126916274</v>
       </c>
       <c r="B67" t="n">
-        <v>92642</v>
+        <v>79603</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7419,40 +7408,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5448</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>655885</v>
+        <v>656012</v>
       </c>
       <c r="R67" t="n">
-        <v>7122754</v>
+        <v>7122821</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7490,19 +7476,18 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7513,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917763</v>
+        <v>126918045</v>
       </c>
       <c r="B68" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7524,34 +7509,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656241</v>
+        <v>656177</v>
       </c>
       <c r="R68" t="n">
-        <v>7122853</v>
+        <v>7122815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7595,15 +7580,30 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7614,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126917803</v>
+        <v>126919808</v>
       </c>
       <c r="B69" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>655792</v>
+        <v>655921</v>
       </c>
       <c r="R69" t="n">
-        <v>7122889</v>
+        <v>7122999</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7699,12 +7699,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7831,10 +7831,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126916315</v>
+        <v>126918650</v>
       </c>
       <c r="B71" t="n">
-        <v>92616</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655879</v>
+        <v>656291</v>
       </c>
       <c r="R71" t="n">
-        <v>7122817</v>
+        <v>7122816</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,12 +7916,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,32 +7932,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918422</v>
+        <v>126916315</v>
       </c>
       <c r="B72" t="n">
-        <v>91487</v>
+        <v>92616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655890</v>
+        <v>655879</v>
       </c>
       <c r="R72" t="n">
-        <v>7122888</v>
+        <v>7122817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,45 +8033,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918042</v>
+        <v>126918422</v>
       </c>
       <c r="B73" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655954</v>
+        <v>655890</v>
       </c>
       <c r="R73" t="n">
-        <v>7122886</v>
+        <v>7122888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8115,30 +8115,15 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8149,45 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918650</v>
+        <v>126918042</v>
       </c>
       <c r="B74" t="n">
-        <v>80146</v>
+        <v>78420</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656291</v>
+        <v>655954</v>
       </c>
       <c r="R74" t="n">
-        <v>7122816</v>
+        <v>7122886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8231,15 +8216,30 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126915964</v>
+        <v>126918050</v>
       </c>
       <c r="B76" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,37 +8362,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655800</v>
+        <v>656266</v>
       </c>
       <c r="R76" t="n">
-        <v>7122929</v>
+        <v>7122789</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8432,16 +8432,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8452,32 +8467,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126917772</v>
+        <v>126915970</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,13 +8502,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655768</v>
+        <v>655778</v>
       </c>
       <c r="R77" t="n">
-        <v>7122903</v>
+        <v>7122904</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8537,12 +8552,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8553,32 +8568,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126916729</v>
+        <v>126915964</v>
       </c>
       <c r="B78" t="n">
-        <v>56849</v>
+        <v>80117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8588,13 +8603,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655892</v>
+        <v>655800</v>
       </c>
       <c r="R78" t="n">
-        <v>7122748</v>
+        <v>7122929</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8624,11 +8639,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8643,12 +8653,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8659,32 +8669,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126919806</v>
+        <v>126917772</v>
       </c>
       <c r="B79" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,10 +8704,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655917</v>
+        <v>655768</v>
       </c>
       <c r="R79" t="n">
-        <v>7122874</v>
+        <v>7122903</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8744,12 +8754,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8760,32 +8770,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918404</v>
+        <v>126916729</v>
       </c>
       <c r="B80" t="n">
-        <v>79603</v>
+        <v>56849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8795,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655901</v>
+        <v>655892</v>
       </c>
       <c r="R80" t="n">
-        <v>7122844</v>
+        <v>7122748</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8833,6 +8843,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8845,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8861,7 +8876,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126915963</v>
+        <v>126919806</v>
       </c>
       <c r="B81" t="n">
         <v>78773</v>
@@ -8896,13 +8911,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655813</v>
+        <v>655917</v>
       </c>
       <c r="R81" t="n">
-        <v>7122846</v>
+        <v>7122874</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8946,12 +8961,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8962,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126916286</v>
+        <v>126918404</v>
       </c>
       <c r="B82" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8973,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8997,10 +9012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655866</v>
+        <v>655901</v>
       </c>
       <c r="R82" t="n">
-        <v>7122779</v>
+        <v>7122844</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9047,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9063,10 +9078,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126918050</v>
+        <v>126915963</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9074,37 +9089,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>656266</v>
+        <v>655813</v>
       </c>
       <c r="R83" t="n">
-        <v>7122789</v>
+        <v>7122846</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9144,31 +9159,16 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126915970</v>
+        <v>126916286</v>
       </c>
       <c r="B84" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,13 +9214,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655778</v>
+        <v>655866</v>
       </c>
       <c r="R84" t="n">
-        <v>7122904</v>
+        <v>7122779</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9497,10 +9497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915959</v>
+        <v>126916394</v>
       </c>
       <c r="B87" t="n">
-        <v>92809</v>
+        <v>78772</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655849</v>
+        <v>655798</v>
       </c>
       <c r="R87" t="n">
-        <v>7122806</v>
+        <v>7122934</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9576,6 +9576,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9587,7 +9588,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9598,10 +9599,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126916394</v>
+        <v>126915959</v>
       </c>
       <c r="B88" t="n">
-        <v>78772</v>
+        <v>92809</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9609,21 +9610,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9633,10 +9634,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655798</v>
+        <v>655849</v>
       </c>
       <c r="R88" t="n">
-        <v>7122934</v>
+        <v>7122806</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9677,7 +9678,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10018,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918100</v>
+        <v>126918711</v>
       </c>
       <c r="B92" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,37 +10029,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655957</v>
+        <v>655898</v>
       </c>
       <c r="R92" t="n">
-        <v>7122879</v>
+        <v>7122802</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10103,12 +10103,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,7 +10119,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126917788</v>
+        <v>126918100</v>
       </c>
       <c r="B93" t="n">
         <v>78773</v>
@@ -10150,17 +10150,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655780</v>
+        <v>655957</v>
       </c>
       <c r="R93" t="n">
-        <v>7122780</v>
+        <v>7122879</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10204,12 +10204,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918423</v>
+        <v>126917788</v>
       </c>
       <c r="B94" t="n">
-        <v>92809</v>
+        <v>78773</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655881</v>
+        <v>655780</v>
       </c>
       <c r="R94" t="n">
-        <v>7122919</v>
+        <v>7122780</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10321,32 +10321,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918713</v>
+        <v>126916313</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656004</v>
+        <v>656087</v>
       </c>
       <c r="R95" t="n">
-        <v>7122974</v>
+        <v>7122806</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918681</v>
+        <v>126918713</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656291</v>
+        <v>656004</v>
       </c>
       <c r="R96" t="n">
-        <v>7122808</v>
+        <v>7122974</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126915962</v>
+        <v>126918681</v>
       </c>
       <c r="B97" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,21 +10534,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10558,13 +10558,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655854</v>
+        <v>656291</v>
       </c>
       <c r="R97" t="n">
-        <v>7122777</v>
+        <v>7122808</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10608,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126916276</v>
+        <v>126918395</v>
       </c>
       <c r="B98" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10635,21 +10635,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655925</v>
+        <v>655892</v>
       </c>
       <c r="R98" t="n">
-        <v>7122825</v>
+        <v>7122986</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10709,12 +10709,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,7 +10725,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126914201</v>
+        <v>126916276</v>
       </c>
       <c r="B99" t="n">
         <v>79603</v>
@@ -10756,17 +10756,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655947</v>
+        <v>655925</v>
       </c>
       <c r="R99" t="n">
-        <v>7122837</v>
+        <v>7122825</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10793,19 +10793,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10820,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,48 +10826,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126916313</v>
+        <v>126914201</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>79603</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656087</v>
+        <v>655947</v>
       </c>
       <c r="R100" t="n">
-        <v>7122806</v>
+        <v>7122837</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10904,9 +10894,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918395</v>
+        <v>126915962</v>
       </c>
       <c r="B101" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,21 +10948,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,13 +10972,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655892</v>
+        <v>655854</v>
       </c>
       <c r="R101" t="n">
-        <v>7122986</v>
+        <v>7122777</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918715</v>
+        <v>126918407</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656372</v>
+        <v>655901</v>
       </c>
       <c r="R102" t="n">
-        <v>7122721</v>
+        <v>7122844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,12 +11123,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11260,10 +11260,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126916277</v>
+        <v>126918715</v>
       </c>
       <c r="B104" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11271,21 +11271,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>655921</v>
+        <v>656372</v>
       </c>
       <c r="R104" t="n">
-        <v>7122873</v>
+        <v>7122721</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11345,12 +11345,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11361,10 +11361,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918407</v>
+        <v>126916277</v>
       </c>
       <c r="B105" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11372,21 +11372,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655901</v>
+        <v>655921</v>
       </c>
       <c r="R105" t="n">
-        <v>7122844</v>
+        <v>7122873</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,12 +11446,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126916298</v>
+        <v>126918657</v>
       </c>
       <c r="B106" t="n">
-        <v>78772</v>
+        <v>58087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R106" t="n">
-        <v>7122796</v>
+        <v>7122774</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B111" t="n">
-        <v>58087</v>
+        <v>78772</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R111" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916842</v>
+        <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>92616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655948</v>
+        <v>655893</v>
       </c>
       <c r="R3" t="n">
-        <v>7122908</v>
+        <v>7122779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +855,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -903,32 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916314</v>
+        <v>126910394</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655893</v>
+        <v>655885</v>
       </c>
       <c r="R4" t="n">
-        <v>7122779</v>
+        <v>7122738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126910394</v>
+        <v>126918405</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655885</v>
+        <v>655901</v>
       </c>
       <c r="R5" t="n">
-        <v>7122738</v>
+        <v>7122844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1105,45 +1090,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918405</v>
+        <v>126916842</v>
       </c>
       <c r="B6" t="n">
-        <v>77992</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655901</v>
+        <v>655948</v>
       </c>
       <c r="R6" t="n">
-        <v>7122844</v>
+        <v>7122908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,9 +1163,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916306</v>
+        <v>126916299</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655956</v>
+        <v>655995</v>
       </c>
       <c r="R11" t="n">
-        <v>7122866</v>
+        <v>7122921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916316</v>
+        <v>126916844</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655863</v>
+        <v>655905</v>
       </c>
       <c r="R12" t="n">
-        <v>7122755</v>
+        <v>7122985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,11 +1789,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1802,16 +1812,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918421</v>
+        <v>126918646</v>
       </c>
       <c r="B13" t="n">
-        <v>92809</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655890</v>
+        <v>656298</v>
       </c>
       <c r="R13" t="n">
-        <v>7122888</v>
+        <v>7122812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,12 +1937,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918044</v>
+        <v>126916306</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1964,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656088</v>
+        <v>655956</v>
       </c>
       <c r="R14" t="n">
-        <v>7122850</v>
+        <v>7122866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,30 +2035,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,32 +2054,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916299</v>
+        <v>126916316</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655995</v>
+        <v>655863</v>
       </c>
       <c r="R15" t="n">
-        <v>7122921</v>
+        <v>7122755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916844</v>
+        <v>126918421</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655905</v>
+        <v>655890</v>
       </c>
       <c r="R16" t="n">
-        <v>7122985</v>
+        <v>7122888</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,21 +2223,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2231,36 +2236,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918646</v>
+        <v>126918044</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,34 +2267,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656298</v>
+        <v>656088</v>
       </c>
       <c r="R17" t="n">
-        <v>7122812</v>
+        <v>7122850</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,15 +2338,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R31" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916289</v>
+        <v>126916288</v>
       </c>
       <c r="B32" t="n">
         <v>78773</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655996</v>
+        <v>655965</v>
       </c>
       <c r="R32" t="n">
-        <v>7122934</v>
+        <v>7122873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126918450</v>
+        <v>126916289</v>
       </c>
       <c r="B33" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655906</v>
+        <v>655996</v>
       </c>
       <c r="R33" t="n">
-        <v>7122852</v>
+        <v>7122934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126916746</v>
+        <v>126918438</v>
       </c>
       <c r="B34" t="n">
-        <v>91900</v>
+        <v>78773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655785</v>
+        <v>655882</v>
       </c>
       <c r="R34" t="n">
-        <v>7122898</v>
+        <v>7122978</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,22 +4093,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126920137</v>
+        <v>126919804</v>
       </c>
       <c r="B35" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4116,21 +4120,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4140,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655990</v>
+        <v>655989</v>
       </c>
       <c r="R35" t="n">
-        <v>7122926</v>
+        <v>7122922</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4190,12 +4194,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4206,10 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126917804</v>
+        <v>126918037</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>79603</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,34 +4221,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655834</v>
+        <v>655903</v>
       </c>
       <c r="R36" t="n">
-        <v>7122923</v>
+        <v>7122984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,15 +4292,30 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4307,7 +4326,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126918438</v>
+        <v>126916287</v>
       </c>
       <c r="B37" t="n">
         <v>78773</v>
@@ -4342,10 +4361,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655882</v>
+        <v>655900</v>
       </c>
       <c r="R37" t="n">
-        <v>7122978</v>
+        <v>7122798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4411,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4408,10 +4427,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919804</v>
+        <v>126920137</v>
       </c>
       <c r="B38" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,21 +4438,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4443,10 +4462,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655989</v>
+        <v>655990</v>
       </c>
       <c r="R38" t="n">
-        <v>7122922</v>
+        <v>7122926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,12 +4512,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4509,45 +4528,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126918037</v>
+        <v>126916746</v>
       </c>
       <c r="B39" t="n">
-        <v>79603</v>
+        <v>91900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655903</v>
+        <v>655785</v>
       </c>
       <c r="R39" t="n">
-        <v>7122984</v>
+        <v>7122898</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,44 +4610,25 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126916287</v>
+        <v>126918458</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4636,21 +4636,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655900</v>
+        <v>655914</v>
       </c>
       <c r="R40" t="n">
-        <v>7122798</v>
+        <v>7122985</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,12 +4710,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126918458</v>
+        <v>126917804</v>
       </c>
       <c r="B41" t="n">
-        <v>78420</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655914</v>
+        <v>655834</v>
       </c>
       <c r="R41" t="n">
-        <v>7122985</v>
+        <v>7122923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917825</v>
+        <v>126917785</v>
       </c>
       <c r="B45" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655749</v>
+        <v>655776</v>
       </c>
       <c r="R45" t="n">
-        <v>7122779</v>
+        <v>7122760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916272</v>
+        <v>126919790</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655957</v>
+        <v>655973</v>
       </c>
       <c r="R46" t="n">
-        <v>7122864</v>
+        <v>7122926</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126916741</v>
+        <v>126918406</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655895</v>
+        <v>655901</v>
       </c>
       <c r="R47" t="n">
-        <v>7122747</v>
+        <v>7122844</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126917785</v>
+        <v>126917825</v>
       </c>
       <c r="B48" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655776</v>
+        <v>655749</v>
       </c>
       <c r="R48" t="n">
-        <v>7122760</v>
+        <v>7122779</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919790</v>
+        <v>126916272</v>
       </c>
       <c r="B49" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655973</v>
+        <v>655957</v>
       </c>
       <c r="R49" t="n">
-        <v>7122926</v>
+        <v>7122864</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918406</v>
+        <v>126916741</v>
       </c>
       <c r="B50" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655901</v>
+        <v>655895</v>
       </c>
       <c r="R50" t="n">
-        <v>7122844</v>
+        <v>7122747</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126920128</v>
+        <v>126919778</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655942</v>
+        <v>655919</v>
       </c>
       <c r="R52" t="n">
-        <v>7122804</v>
+        <v>7122981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915088</v>
+        <v>126910294</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,34 +5949,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655950</v>
+        <v>655845</v>
       </c>
       <c r="R53" t="n">
-        <v>7122893</v>
+        <v>7122750</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918672</v>
+        <v>126920128</v>
       </c>
       <c r="B54" t="n">
         <v>78773</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655882</v>
+        <v>655942</v>
       </c>
       <c r="R54" t="n">
-        <v>7122787</v>
+        <v>7122804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919778</v>
+        <v>126915088</v>
       </c>
       <c r="B55" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655919</v>
+        <v>655950</v>
       </c>
       <c r="R55" t="n">
-        <v>7122981</v>
+        <v>7122893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126910294</v>
+        <v>126918672</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655845</v>
+        <v>655882</v>
       </c>
       <c r="R56" t="n">
-        <v>7122750</v>
+        <v>7122787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7715,10 +7715,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918443</v>
+        <v>126917789</v>
       </c>
       <c r="B70" t="n">
-        <v>80989</v>
+        <v>78773</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655875</v>
+        <v>655760</v>
       </c>
       <c r="R70" t="n">
-        <v>7122959</v>
+        <v>7122811</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,30 +7797,15 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7831,32 +7816,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918650</v>
+        <v>126918443</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>80989</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7866,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>656291</v>
+        <v>655875</v>
       </c>
       <c r="R71" t="n">
-        <v>7122816</v>
+        <v>7122959</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7913,15 +7898,30 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,10 +7932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126916315</v>
+        <v>126918650</v>
       </c>
       <c r="B72" t="n">
-        <v>92616</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7943,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655879</v>
+        <v>656291</v>
       </c>
       <c r="R72" t="n">
-        <v>7122817</v>
+        <v>7122816</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,32 +8033,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918422</v>
+        <v>126916315</v>
       </c>
       <c r="B73" t="n">
-        <v>91487</v>
+        <v>92616</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655890</v>
+        <v>655879</v>
       </c>
       <c r="R73" t="n">
-        <v>7122888</v>
+        <v>7122817</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,12 +8118,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,45 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918042</v>
+        <v>126918422</v>
       </c>
       <c r="B74" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655954</v>
+        <v>655890</v>
       </c>
       <c r="R74" t="n">
-        <v>7122886</v>
+        <v>7122888</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,30 +8216,15 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917789</v>
+        <v>126918042</v>
       </c>
       <c r="B75" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8261,34 +8246,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655760</v>
+        <v>655954</v>
       </c>
       <c r="R75" t="n">
-        <v>7122811</v>
+        <v>7122886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8332,15 +8317,30 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916314</v>
+        <v>126916842</v>
       </c>
       <c r="B3" t="n">
-        <v>92616</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655893</v>
+        <v>655948</v>
       </c>
       <c r="R3" t="n">
-        <v>7122779</v>
+        <v>7122908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,9 +860,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126916314</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655893</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +988,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918405</v>
+        <v>126910394</v>
       </c>
       <c r="B5" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655901</v>
+        <v>655885</v>
       </c>
       <c r="R5" t="n">
-        <v>7122844</v>
+        <v>7122738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1089,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,50 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916842</v>
+        <v>126918405</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>77992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655948</v>
+        <v>655901</v>
       </c>
       <c r="R6" t="n">
-        <v>7122908</v>
+        <v>7122844</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,19 +1173,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916299</v>
+        <v>126916306</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655995</v>
+        <v>655956</v>
       </c>
       <c r="R11" t="n">
-        <v>7122921</v>
+        <v>7122866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916844</v>
+        <v>126916316</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655905</v>
+        <v>655863</v>
       </c>
       <c r="R12" t="n">
-        <v>7122985</v>
+        <v>7122755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,21 +1789,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1812,36 +1802,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1852,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918646</v>
+        <v>126918421</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>92809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656298</v>
+        <v>655890</v>
       </c>
       <c r="R13" t="n">
-        <v>7122812</v>
+        <v>7122888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,12 +1907,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1953,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916306</v>
+        <v>126918044</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,34 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655956</v>
+        <v>656088</v>
       </c>
       <c r="R14" t="n">
-        <v>7122866</v>
+        <v>7122850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,15 +2005,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2054,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916316</v>
+        <v>126916299</v>
       </c>
       <c r="B15" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655863</v>
+        <v>655995</v>
       </c>
       <c r="R15" t="n">
-        <v>7122755</v>
+        <v>7122921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918421</v>
+        <v>126916844</v>
       </c>
       <c r="B16" t="n">
-        <v>92809</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2190,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655890</v>
+        <v>655905</v>
       </c>
       <c r="R16" t="n">
-        <v>7122888</v>
+        <v>7122985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,11 +2208,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2236,16 +2231,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2256,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918044</v>
+        <v>126918646</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,34 +2282,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656088</v>
+        <v>656298</v>
       </c>
       <c r="R17" t="n">
-        <v>7122850</v>
+        <v>7122812</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,30 +2353,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3200,32 +3200,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126918712</v>
+        <v>126916397</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655899</v>
+        <v>655893</v>
       </c>
       <c r="R26" t="n">
-        <v>7122835</v>
+        <v>7122752</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917813</v>
+        <v>126918424</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>92809</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655710</v>
+        <v>655961</v>
       </c>
       <c r="R27" t="n">
-        <v>7122853</v>
+        <v>7122865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,32 +3402,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126916397</v>
+        <v>126918712</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,13 +3437,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655893</v>
+        <v>655899</v>
       </c>
       <c r="R28" t="n">
-        <v>7122752</v>
+        <v>7122835</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918424</v>
+        <v>126917813</v>
       </c>
       <c r="B29" t="n">
-        <v>92809</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655961</v>
+        <v>655710</v>
       </c>
       <c r="R29" t="n">
-        <v>7122865</v>
+        <v>7122853</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B31" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R31" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916288</v>
+        <v>126916289</v>
       </c>
       <c r="B32" t="n">
         <v>78773</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655965</v>
+        <v>655996</v>
       </c>
       <c r="R32" t="n">
-        <v>7122873</v>
+        <v>7122934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916289</v>
+        <v>126918450</v>
       </c>
       <c r="B33" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655996</v>
+        <v>655906</v>
       </c>
       <c r="R33" t="n">
-        <v>7122934</v>
+        <v>7122852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126916312</v>
+        <v>126916745</v>
       </c>
       <c r="B59" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656104</v>
+        <v>655840</v>
       </c>
       <c r="R59" t="n">
-        <v>7122796</v>
+        <v>7122839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,26 +6644,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918041</v>
+        <v>126918047</v>
       </c>
       <c r="B60" t="n">
-        <v>92809</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,21 +6667,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6695,10 +6691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655965</v>
+        <v>656203</v>
       </c>
       <c r="R60" t="n">
-        <v>7122890</v>
+        <v>7122806</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,32 +6772,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917803</v>
+        <v>126916312</v>
       </c>
       <c r="B61" t="n">
-        <v>80117</v>
+        <v>92616</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655792</v>
+        <v>656104</v>
       </c>
       <c r="R61" t="n">
-        <v>7122889</v>
+        <v>7122796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6861,12 +6857,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,10 +6873,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126917763</v>
+        <v>126918041</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6888,34 +6884,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656241</v>
+        <v>655965</v>
       </c>
       <c r="R62" t="n">
-        <v>7122853</v>
+        <v>7122890</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6959,15 +6955,30 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6978,10 +6989,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916745</v>
+        <v>126917803</v>
       </c>
       <c r="B63" t="n">
-        <v>78681</v>
+        <v>80117</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6989,21 +7000,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7024,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>655840</v>
+        <v>655792</v>
       </c>
       <c r="R63" t="n">
-        <v>7122839</v>
+        <v>7122889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7063,22 +7074,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918047</v>
+        <v>126917763</v>
       </c>
       <c r="B64" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,34 +7101,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656203</v>
+        <v>656241</v>
       </c>
       <c r="R64" t="n">
-        <v>7122806</v>
+        <v>7122853</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7157,30 +7172,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7932,10 +7932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918650</v>
+        <v>126916315</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>92616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7943,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656291</v>
+        <v>655879</v>
       </c>
       <c r="R72" t="n">
-        <v>7122816</v>
+        <v>7122817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8017,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,32 +8033,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126916315</v>
+        <v>126918422</v>
       </c>
       <c r="B73" t="n">
-        <v>92616</v>
+        <v>91487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655879</v>
+        <v>655890</v>
       </c>
       <c r="R73" t="n">
-        <v>7122817</v>
+        <v>7122888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,12 +8118,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,45 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918422</v>
+        <v>126918042</v>
       </c>
       <c r="B74" t="n">
-        <v>91487</v>
+        <v>78420</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655890</v>
+        <v>655954</v>
       </c>
       <c r="R74" t="n">
-        <v>7122888</v>
+        <v>7122886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,15 +8216,30 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8235,45 +8250,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918042</v>
+        <v>126918650</v>
       </c>
       <c r="B75" t="n">
-        <v>78420</v>
+        <v>80146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655954</v>
+        <v>656291</v>
       </c>
       <c r="R75" t="n">
-        <v>7122886</v>
+        <v>7122816</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,30 +8332,15 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126918050</v>
+        <v>126919806</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,34 +8362,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656266</v>
+        <v>655917</v>
       </c>
       <c r="R76" t="n">
-        <v>7122789</v>
+        <v>7122874</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8433,30 +8433,15 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8467,10 +8452,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915970</v>
+        <v>126918404</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8478,21 +8463,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8502,13 +8487,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655778</v>
+        <v>655901</v>
       </c>
       <c r="R77" t="n">
-        <v>7122904</v>
+        <v>7122844</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8552,12 +8537,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8568,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915964</v>
+        <v>126915963</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8579,21 +8564,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8603,10 +8588,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655800</v>
+        <v>655813</v>
       </c>
       <c r="R78" t="n">
-        <v>7122929</v>
+        <v>7122846</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8669,32 +8654,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126917772</v>
+        <v>126916286</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,10 +8689,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655768</v>
+        <v>655866</v>
       </c>
       <c r="R79" t="n">
-        <v>7122903</v>
+        <v>7122779</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8754,12 +8739,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8770,45 +8755,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916729</v>
+        <v>126918050</v>
       </c>
       <c r="B80" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655892</v>
+        <v>656266</v>
       </c>
       <c r="R80" t="n">
-        <v>7122748</v>
+        <v>7122789</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,11 +8828,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8856,16 +8836,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8876,10 +8871,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126919806</v>
+        <v>126915970</v>
       </c>
       <c r="B81" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8887,21 +8882,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8911,13 +8906,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655917</v>
+        <v>655778</v>
       </c>
       <c r="R81" t="n">
-        <v>7122874</v>
+        <v>7122904</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8961,12 +8956,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918404</v>
+        <v>126915964</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>80117</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8983,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,13 +9007,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655901</v>
+        <v>655800</v>
       </c>
       <c r="R82" t="n">
-        <v>7122844</v>
+        <v>7122929</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9057,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,32 +9073,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915963</v>
+        <v>126917772</v>
       </c>
       <c r="B83" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,13 +9108,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655813</v>
+        <v>655768</v>
       </c>
       <c r="R83" t="n">
-        <v>7122846</v>
+        <v>7122903</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9163,12 +9158,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9179,32 +9174,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916286</v>
+        <v>126916729</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655866</v>
+        <v>655892</v>
       </c>
       <c r="R84" t="n">
-        <v>7122779</v>
+        <v>7122748</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9252,6 +9247,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918423</v>
+        <v>126918038</v>
       </c>
       <c r="B90" t="n">
-        <v>92809</v>
+        <v>78420</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,34 +9812,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655881</v>
+        <v>655904</v>
       </c>
       <c r="R90" t="n">
-        <v>7122919</v>
+        <v>7122984</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9883,15 +9883,30 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9917,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918038</v>
+        <v>126918711</v>
       </c>
       <c r="B91" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,34 +9928,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655904</v>
+        <v>655898</v>
       </c>
       <c r="R91" t="n">
-        <v>7122984</v>
+        <v>7122802</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,30 +9999,15 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10018,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,21 +10029,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R92" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10103,12 +10103,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10321,32 +10321,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126916313</v>
+        <v>126918713</v>
       </c>
       <c r="B95" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10356,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656087</v>
+        <v>656004</v>
       </c>
       <c r="R95" t="n">
-        <v>7122806</v>
+        <v>7122974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,32 +10422,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918713</v>
+        <v>126916313</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656004</v>
+        <v>656087</v>
       </c>
       <c r="R96" t="n">
-        <v>7122974</v>
+        <v>7122806</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10725,7 +10725,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126916276</v>
+        <v>126914201</v>
       </c>
       <c r="B99" t="n">
         <v>79603</v>
@@ -10756,17 +10756,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655925</v>
+        <v>655947</v>
       </c>
       <c r="R99" t="n">
-        <v>7122825</v>
+        <v>7122837</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10793,9 +10793,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10810,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,10 +10836,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126914201</v>
+        <v>126915962</v>
       </c>
       <c r="B100" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10837,37 +10847,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655947</v>
+        <v>655854</v>
       </c>
       <c r="R100" t="n">
-        <v>7122837</v>
+        <v>7122777</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10894,19 +10904,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915962</v>
+        <v>126916276</v>
       </c>
       <c r="B101" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,21 +10948,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,13 +10972,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655854</v>
+        <v>655925</v>
       </c>
       <c r="R101" t="n">
-        <v>7122777</v>
+        <v>7122825</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918407</v>
+        <v>126918715</v>
       </c>
       <c r="B102" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>655901</v>
+        <v>656372</v>
       </c>
       <c r="R102" t="n">
-        <v>7122844</v>
+        <v>7122721</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,12 +11123,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11139,50 +11139,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918049</v>
+        <v>126918407</v>
       </c>
       <c r="B103" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656225</v>
+        <v>655901</v>
       </c>
       <c r="R103" t="n">
-        <v>7122794</v>
+        <v>7122844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11226,30 +11221,15 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11260,45 +11240,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918715</v>
+        <v>126918049</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656372</v>
+        <v>656225</v>
       </c>
       <c r="R104" t="n">
-        <v>7122721</v>
+        <v>7122794</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11342,15 +11327,30 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126919802</v>
+        <v>126916298</v>
       </c>
       <c r="B107" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656007</v>
+        <v>655900</v>
       </c>
       <c r="R107" t="n">
-        <v>7122964</v>
+        <v>7122796</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126916275</v>
+        <v>126919802</v>
       </c>
       <c r="B108" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655900</v>
+        <v>656007</v>
       </c>
       <c r="R108" t="n">
-        <v>7122800</v>
+        <v>7122964</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,12 +11749,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,10 +11765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126920127</v>
+        <v>126916275</v>
       </c>
       <c r="B109" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,21 +11776,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>656146</v>
+        <v>655900</v>
       </c>
       <c r="R109" t="n">
-        <v>7122791</v>
+        <v>7122800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,19 +11844,18 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11867,10 +11866,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920120</v>
+        <v>126920127</v>
       </c>
       <c r="B110" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11878,21 +11877,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11902,10 +11901,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>655982</v>
+        <v>656146</v>
       </c>
       <c r="R110" t="n">
-        <v>7122865</v>
+        <v>7122791</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11946,6 +11945,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126916298</v>
+        <v>126920120</v>
       </c>
       <c r="B111" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655900</v>
+        <v>655982</v>
       </c>
       <c r="R111" t="n">
-        <v>7122796</v>
+        <v>7122865</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>126916842</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,32 +903,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916314</v>
+        <v>126916285</v>
       </c>
       <c r="B4" t="n">
-        <v>92616</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655893</v>
+        <v>655855</v>
       </c>
       <c r="R4" t="n">
-        <v>7122779</v>
+        <v>7122774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126910394</v>
+        <v>126914199</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,37 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655885</v>
+        <v>655888</v>
       </c>
       <c r="R5" t="n">
-        <v>7122738</v>
+        <v>7122973</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,9 +1072,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,12 +1099,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1105,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918405</v>
+        <v>126910130</v>
       </c>
       <c r="B6" t="n">
-        <v>77992</v>
+        <v>79607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655901</v>
+        <v>655841</v>
       </c>
       <c r="R6" t="n">
-        <v>7122844</v>
+        <v>7122800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,12 +1200,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916285</v>
+        <v>126910394</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>78776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655855</v>
+        <v>655885</v>
       </c>
       <c r="R7" t="n">
-        <v>7122774</v>
+        <v>7122738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,12 +1301,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126914199</v>
+        <v>126918405</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>77996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655888</v>
+        <v>655901</v>
       </c>
       <c r="R8" t="n">
-        <v>7122973</v>
+        <v>7122844</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,19 +1385,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,12 +1402,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,32 +1418,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126916284</v>
+        <v>126916314</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>92620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655943</v>
+        <v>655893</v>
       </c>
       <c r="R9" t="n">
-        <v>7122816</v>
+        <v>7122779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126910130</v>
+        <v>126916284</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655841</v>
+        <v>655943</v>
       </c>
       <c r="R10" t="n">
-        <v>7122800</v>
+        <v>7122816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916306</v>
+        <v>126918044</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,34 +1631,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655956</v>
+        <v>656088</v>
       </c>
       <c r="R11" t="n">
-        <v>7122866</v>
+        <v>7122850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,15 +1702,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1721,32 +1736,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916316</v>
+        <v>126916299</v>
       </c>
       <c r="B12" t="n">
-        <v>92616</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655863</v>
+        <v>655995</v>
       </c>
       <c r="R12" t="n">
-        <v>7122755</v>
+        <v>7122921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918421</v>
+        <v>126916844</v>
       </c>
       <c r="B13" t="n">
-        <v>92809</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655890</v>
+        <v>655905</v>
       </c>
       <c r="R13" t="n">
-        <v>7122888</v>
+        <v>7122985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,11 +1905,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1903,16 +1928,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,45 +1968,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918044</v>
+        <v>126916316</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656088</v>
+        <v>655863</v>
       </c>
       <c r="R14" t="n">
-        <v>7122850</v>
+        <v>7122755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,30 +2050,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916299</v>
+        <v>126918421</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>92813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655995</v>
+        <v>655890</v>
       </c>
       <c r="R15" t="n">
-        <v>7122921</v>
+        <v>7122888</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,12 +2154,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916844</v>
+        <v>126916306</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655905</v>
+        <v>655956</v>
       </c>
       <c r="R16" t="n">
-        <v>7122985</v>
+        <v>7122866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,21 +2238,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2231,36 +2251,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,32 +2271,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918646</v>
+        <v>126919792</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>56853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656298</v>
+        <v>655919</v>
       </c>
       <c r="R17" t="n">
-        <v>7122812</v>
+        <v>7122887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,6 +2344,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2356,12 +2361,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126919792</v>
+        <v>126918646</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655919</v>
+        <v>656298</v>
       </c>
       <c r="R18" t="n">
-        <v>7122887</v>
+        <v>7122812</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,11 +2450,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2462,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>126916278</v>
       </c>
       <c r="B19" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>126917770</v>
       </c>
       <c r="B20" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>126909344</v>
       </c>
       <c r="B21" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>126918439</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>126910226</v>
       </c>
       <c r="B23" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>126917790</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>126918039</v>
       </c>
       <c r="B25" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,32 +3200,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126916397</v>
+        <v>126917813</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>78776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655893</v>
+        <v>655710</v>
       </c>
       <c r="R26" t="n">
-        <v>7122752</v>
+        <v>7122853</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918424</v>
+        <v>126918712</v>
       </c>
       <c r="B27" t="n">
-        <v>92809</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655961</v>
+        <v>655899</v>
       </c>
       <c r="R27" t="n">
-        <v>7122865</v>
+        <v>7122835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918712</v>
+        <v>126918424</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>92813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655899</v>
+        <v>655961</v>
       </c>
       <c r="R28" t="n">
-        <v>7122835</v>
+        <v>7122865</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917813</v>
+        <v>126916397</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655710</v>
+        <v>655893</v>
       </c>
       <c r="R29" t="n">
-        <v>7122853</v>
+        <v>7122752</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3607,7 +3607,7 @@
         <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78773</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R31" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916289</v>
+        <v>126916288</v>
       </c>
       <c r="B32" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655996</v>
+        <v>655965</v>
       </c>
       <c r="R32" t="n">
-        <v>7122934</v>
+        <v>7122873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126918450</v>
+        <v>126916289</v>
       </c>
       <c r="B33" t="n">
-        <v>78681</v>
+        <v>78777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655906</v>
+        <v>655996</v>
       </c>
       <c r="R33" t="n">
-        <v>7122852</v>
+        <v>7122934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918438</v>
+        <v>126917804</v>
       </c>
       <c r="B34" t="n">
-        <v>78773</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,21 +4019,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655882</v>
+        <v>655834</v>
       </c>
       <c r="R34" t="n">
-        <v>7122978</v>
+        <v>7122923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126919804</v>
+        <v>126918458</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>78424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655989</v>
+        <v>655914</v>
       </c>
       <c r="R35" t="n">
-        <v>7122922</v>
+        <v>7122985</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,12 +4194,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4210,10 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918037</v>
+        <v>126918438</v>
       </c>
       <c r="B36" t="n">
-        <v>79603</v>
+        <v>78777</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655903</v>
+        <v>655882</v>
       </c>
       <c r="R36" t="n">
-        <v>7122984</v>
+        <v>7122978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4292,30 +4292,15 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4326,10 +4311,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126916287</v>
+        <v>126919804</v>
       </c>
       <c r="B37" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,10 +4346,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655900</v>
+        <v>655989</v>
       </c>
       <c r="R37" t="n">
-        <v>7122798</v>
+        <v>7122922</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,12 +4396,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4427,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126920137</v>
+        <v>126918037</v>
       </c>
       <c r="B38" t="n">
-        <v>78681</v>
+        <v>79607</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4438,34 +4423,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655990</v>
+        <v>655903</v>
       </c>
       <c r="R38" t="n">
-        <v>7122926</v>
+        <v>7122984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4509,15 +4494,30 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4528,32 +4528,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126916746</v>
+        <v>126916287</v>
       </c>
       <c r="B39" t="n">
-        <v>91900</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655785</v>
+        <v>655900</v>
       </c>
       <c r="R39" t="n">
-        <v>7122898</v>
+        <v>7122798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4613,44 +4613,48 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918458</v>
+        <v>126916746</v>
       </c>
       <c r="B40" t="n">
-        <v>78420</v>
+        <v>91904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>760</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4660,10 +4664,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655914</v>
+        <v>655785</v>
       </c>
       <c r="R40" t="n">
-        <v>7122985</v>
+        <v>7122898</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,26 +4714,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917804</v>
+        <v>126920137</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>78685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655834</v>
+        <v>655990</v>
       </c>
       <c r="R41" t="n">
-        <v>7122923</v>
+        <v>7122926</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126916304</v>
+        <v>126917830</v>
       </c>
       <c r="B42" t="n">
-        <v>78681</v>
+        <v>78424</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655978</v>
+        <v>655749</v>
       </c>
       <c r="R42" t="n">
-        <v>7122825</v>
+        <v>7122779</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126920136</v>
+        <v>126916304</v>
       </c>
       <c r="B43" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655941</v>
+        <v>655978</v>
       </c>
       <c r="R43" t="n">
-        <v>7122804</v>
+        <v>7122825</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,12 +5013,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126917830</v>
+        <v>126920136</v>
       </c>
       <c r="B44" t="n">
-        <v>78420</v>
+        <v>78685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655749</v>
+        <v>655941</v>
       </c>
       <c r="R44" t="n">
-        <v>7122779</v>
+        <v>7122804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v>126917785</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>126919790</v>
       </c>
       <c r="B46" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5335,7 +5335,7 @@
         <v>126918406</v>
       </c>
       <c r="B47" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126917825</v>
+        <v>126916741</v>
       </c>
       <c r="B48" t="n">
-        <v>77992</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655749</v>
+        <v>655895</v>
       </c>
       <c r="R48" t="n">
-        <v>7122779</v>
+        <v>7122747</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126916272</v>
+        <v>126917825</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>77996</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655957</v>
+        <v>655749</v>
       </c>
       <c r="R49" t="n">
-        <v>7122864</v>
+        <v>7122779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126916741</v>
+        <v>126916272</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655895</v>
+        <v>655957</v>
       </c>
       <c r="R50" t="n">
-        <v>7122747</v>
+        <v>7122864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126918397</v>
+        <v>126919778</v>
       </c>
       <c r="B51" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655892</v>
+        <v>655919</v>
       </c>
       <c r="R51" t="n">
-        <v>7122986</v>
+        <v>7122981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919778</v>
+        <v>126910294</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655919</v>
+        <v>655845</v>
       </c>
       <c r="R52" t="n">
-        <v>7122981</v>
+        <v>7122750</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126910294</v>
+        <v>126920128</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655845</v>
+        <v>655942</v>
       </c>
       <c r="R53" t="n">
-        <v>7122750</v>
+        <v>7122804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126920128</v>
+        <v>126915088</v>
       </c>
       <c r="B54" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6070,14 +6070,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655942</v>
+        <v>655950</v>
       </c>
       <c r="R54" t="n">
-        <v>7122804</v>
+        <v>7122893</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915088</v>
+        <v>126918672</v>
       </c>
       <c r="B55" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,14 +6171,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655950</v>
+        <v>655882</v>
       </c>
       <c r="R55" t="n">
-        <v>7122893</v>
+        <v>7122787</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918672</v>
+        <v>126918397</v>
       </c>
       <c r="B56" t="n">
-        <v>78773</v>
+        <v>78685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655882</v>
+        <v>655892</v>
       </c>
       <c r="R56" t="n">
-        <v>7122787</v>
+        <v>7122986</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R57" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,15 +6424,30 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6443,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B58" t="n">
-        <v>78773</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6454,34 +6469,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R58" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6525,30 +6540,15 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126916745</v>
+        <v>126917803</v>
       </c>
       <c r="B59" t="n">
-        <v>78681</v>
+        <v>80121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,21 +6570,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655840</v>
+        <v>655792</v>
       </c>
       <c r="R59" t="n">
-        <v>7122839</v>
+        <v>7122889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,22 +6644,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918047</v>
+        <v>126917763</v>
       </c>
       <c r="B60" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6667,34 +6671,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656203</v>
+        <v>656241</v>
       </c>
       <c r="R60" t="n">
-        <v>7122806</v>
+        <v>7122853</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6738,30 +6742,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6772,45 +6761,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126916312</v>
+        <v>126918041</v>
       </c>
       <c r="B61" t="n">
-        <v>92616</v>
+        <v>92813</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656104</v>
+        <v>655965</v>
       </c>
       <c r="R61" t="n">
-        <v>7122796</v>
+        <v>7122890</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6854,15 +6843,30 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6873,10 +6877,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918041</v>
+        <v>126915955</v>
       </c>
       <c r="B62" t="n">
-        <v>92809</v>
+        <v>92646</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6884,37 +6888,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655965</v>
+        <v>655885</v>
       </c>
       <c r="R62" t="n">
-        <v>7122890</v>
+        <v>7122754</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6952,33 +6959,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6989,32 +6982,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126917803</v>
+        <v>126916312</v>
       </c>
       <c r="B63" t="n">
-        <v>80117</v>
+        <v>92620</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7017,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>655792</v>
+        <v>656104</v>
       </c>
       <c r="R63" t="n">
-        <v>7122889</v>
+        <v>7122796</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7074,12 +7067,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7090,10 +7083,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126917763</v>
+        <v>126916745</v>
       </c>
       <c r="B64" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7101,21 +7094,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7125,10 +7118,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656241</v>
+        <v>655840</v>
       </c>
       <c r="R64" t="n">
-        <v>7122853</v>
+        <v>7122839</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7175,26 +7168,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126915955</v>
+        <v>126918047</v>
       </c>
       <c r="B65" t="n">
-        <v>92642</v>
+        <v>78685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7202,40 +7191,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>655885</v>
+        <v>656203</v>
       </c>
       <c r="R65" t="n">
-        <v>7122754</v>
+        <v>7122806</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7273,19 +7259,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7299,7 +7299,7 @@
         <v>126917791</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>126916274</v>
       </c>
       <c r="B67" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>126918045</v>
       </c>
       <c r="B68" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>126919808</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7715,32 +7715,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126917789</v>
+        <v>126918650</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655760</v>
+        <v>656291</v>
       </c>
       <c r="R70" t="n">
-        <v>7122811</v>
+        <v>7122816</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,12 +7800,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918443</v>
+        <v>126918042</v>
       </c>
       <c r="B71" t="n">
-        <v>80989</v>
+        <v>78424</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7827,34 +7827,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655875</v>
+        <v>655954</v>
       </c>
       <c r="R71" t="n">
-        <v>7122959</v>
+        <v>7122886</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,12 +7916,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7935,7 +7935,7 @@
         <v>126916315</v>
       </c>
       <c r="B72" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8033,32 +8033,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918422</v>
+        <v>126918443</v>
       </c>
       <c r="B73" t="n">
-        <v>91487</v>
+        <v>80993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655890</v>
+        <v>655875</v>
       </c>
       <c r="R73" t="n">
-        <v>7122888</v>
+        <v>7122959</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8114,6 +8114,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8134,45 +8149,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918042</v>
+        <v>126918422</v>
       </c>
       <c r="B74" t="n">
-        <v>78420</v>
+        <v>91491</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655954</v>
+        <v>655890</v>
       </c>
       <c r="R74" t="n">
-        <v>7122886</v>
+        <v>7122888</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,30 +8231,15 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918650</v>
+        <v>126917789</v>
       </c>
       <c r="B75" t="n">
-        <v>80146</v>
+        <v>78777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656291</v>
+        <v>655760</v>
       </c>
       <c r="R75" t="n">
-        <v>7122816</v>
+        <v>7122811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,10 +8351,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126919806</v>
+        <v>126918050</v>
       </c>
       <c r="B76" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8362,34 +8362,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655917</v>
+        <v>656266</v>
       </c>
       <c r="R76" t="n">
-        <v>7122874</v>
+        <v>7122789</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8433,15 +8433,30 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8452,10 +8467,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126918404</v>
+        <v>126915970</v>
       </c>
       <c r="B77" t="n">
-        <v>79603</v>
+        <v>78776</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8463,21 +8478,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,13 +8502,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655901</v>
+        <v>655778</v>
       </c>
       <c r="R77" t="n">
-        <v>7122844</v>
+        <v>7122904</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8537,12 +8552,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8553,10 +8568,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915963</v>
+        <v>126915964</v>
       </c>
       <c r="B78" t="n">
-        <v>78773</v>
+        <v>80121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8564,21 +8579,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8588,10 +8603,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655813</v>
+        <v>655800</v>
       </c>
       <c r="R78" t="n">
-        <v>7122846</v>
+        <v>7122929</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8654,32 +8669,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126916286</v>
+        <v>126917772</v>
       </c>
       <c r="B79" t="n">
-        <v>78773</v>
+        <v>80150</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8689,10 +8704,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655866</v>
+        <v>655768</v>
       </c>
       <c r="R79" t="n">
-        <v>7122779</v>
+        <v>7122903</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8739,12 +8754,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8755,10 +8770,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918050</v>
+        <v>126919806</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8766,34 +8781,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656266</v>
+        <v>655917</v>
       </c>
       <c r="R80" t="n">
-        <v>7122789</v>
+        <v>7122874</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,30 +8852,15 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8871,10 +8871,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126915970</v>
+        <v>126918404</v>
       </c>
       <c r="B81" t="n">
-        <v>78772</v>
+        <v>79607</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8882,21 +8882,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655778</v>
+        <v>655901</v>
       </c>
       <c r="R81" t="n">
-        <v>7122904</v>
+        <v>7122844</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8956,12 +8956,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8972,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915964</v>
+        <v>126915963</v>
       </c>
       <c r="B82" t="n">
-        <v>80117</v>
+        <v>78777</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8983,21 +8983,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655800</v>
+        <v>655813</v>
       </c>
       <c r="R82" t="n">
-        <v>7122929</v>
+        <v>7122846</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9073,32 +9073,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126917772</v>
+        <v>126916286</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>78777</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655768</v>
+        <v>655866</v>
       </c>
       <c r="R83" t="n">
-        <v>7122903</v>
+        <v>7122779</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,12 +9158,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9177,7 +9177,7 @@
         <v>126916729</v>
       </c>
       <c r="B84" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>126918104</v>
       </c>
       <c r="B85" t="n">
-        <v>92610</v>
+        <v>92614</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918040</v>
+        <v>126916394</v>
       </c>
       <c r="B86" t="n">
-        <v>78681</v>
+        <v>78776</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655945</v>
+        <v>655798</v>
       </c>
       <c r="R86" t="n">
-        <v>7122909</v>
+        <v>7122934</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9460,33 +9460,19 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9497,10 +9483,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126916394</v>
+        <v>126915959</v>
       </c>
       <c r="B87" t="n">
-        <v>78772</v>
+        <v>92813</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9508,21 +9494,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9532,10 +9518,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655798</v>
+        <v>655849</v>
       </c>
       <c r="R87" t="n">
-        <v>7122934</v>
+        <v>7122806</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
@@ -9576,7 +9562,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9588,7 +9573,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9599,10 +9584,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126915959</v>
+        <v>126918677</v>
       </c>
       <c r="B88" t="n">
-        <v>92809</v>
+        <v>78777</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9610,21 +9595,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9634,13 +9619,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655849</v>
+        <v>655893</v>
       </c>
       <c r="R88" t="n">
-        <v>7122806</v>
+        <v>7122814</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9684,12 +9669,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9700,10 +9685,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126918677</v>
+        <v>126918040</v>
       </c>
       <c r="B89" t="n">
-        <v>78773</v>
+        <v>78685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9711,34 +9696,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655893</v>
+        <v>655945</v>
       </c>
       <c r="R89" t="n">
-        <v>7122814</v>
+        <v>7122909</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9782,15 +9767,30 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9804,7 +9804,7 @@
         <v>126918038</v>
       </c>
       <c r="B90" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>126918711</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>126918423</v>
       </c>
       <c r="B92" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>126918100</v>
       </c>
       <c r="B93" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>126917788</v>
       </c>
       <c r="B94" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>126918713</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10422,32 +10422,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126916313</v>
+        <v>126918681</v>
       </c>
       <c r="B96" t="n">
-        <v>92616</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656087</v>
+        <v>656291</v>
       </c>
       <c r="R96" t="n">
-        <v>7122806</v>
+        <v>7122808</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918681</v>
+        <v>126918395</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>79636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,21 +10534,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656291</v>
+        <v>655892</v>
       </c>
       <c r="R97" t="n">
-        <v>7122808</v>
+        <v>7122986</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10608,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918395</v>
+        <v>126915962</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10635,21 +10635,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,13 +10659,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655892</v>
+        <v>655854</v>
       </c>
       <c r="R98" t="n">
-        <v>7122986</v>
+        <v>7122777</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10709,12 +10709,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126914201</v>
+        <v>126916276</v>
       </c>
       <c r="B99" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10756,17 +10756,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655947</v>
+        <v>655925</v>
       </c>
       <c r="R99" t="n">
-        <v>7122837</v>
+        <v>7122825</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10793,19 +10793,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10820,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,10 +10826,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126915962</v>
+        <v>126914201</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>79607</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10847,37 +10837,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655854</v>
+        <v>655947</v>
       </c>
       <c r="R100" t="n">
-        <v>7122777</v>
+        <v>7122837</v>
       </c>
       <c r="S100" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10904,9 +10894,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,32 +10937,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126916276</v>
+        <v>126916313</v>
       </c>
       <c r="B101" t="n">
-        <v>79603</v>
+        <v>92620</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655925</v>
+        <v>656087</v>
       </c>
       <c r="R101" t="n">
-        <v>7122825</v>
+        <v>7122806</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918715</v>
+        <v>126916277</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>79607</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11049,21 +11049,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656372</v>
+        <v>655921</v>
       </c>
       <c r="R102" t="n">
-        <v>7122721</v>
+        <v>7122873</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11123,12 +11123,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11142,7 +11142,7 @@
         <v>126918407</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11240,50 +11240,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918049</v>
+        <v>126918715</v>
       </c>
       <c r="B104" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656225</v>
+        <v>656372</v>
       </c>
       <c r="R104" t="n">
-        <v>7122794</v>
+        <v>7122721</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11327,30 +11322,15 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11361,45 +11341,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B105" t="n">
-        <v>79603</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R105" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,15 +11428,30 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B106" t="n">
-        <v>58087</v>
+        <v>78776</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R106" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126916298</v>
+        <v>126918657</v>
       </c>
       <c r="B107" t="n">
-        <v>78772</v>
+        <v>58091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R107" t="n">
-        <v>7122796</v>
+        <v>7122774</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11667,7 +11667,7 @@
         <v>126919802</v>
       </c>
       <c r="B108" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>126916275</v>
       </c>
       <c r="B109" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>126920127</v>
       </c>
       <c r="B110" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>126920120</v>
       </c>
       <c r="B111" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>126914200</v>
       </c>
       <c r="B112" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>126916733</v>
       </c>
       <c r="B113" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>126914202</v>
       </c>
       <c r="B114" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>126918410</v>
       </c>
       <c r="B115" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>126950497</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>126950494</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>126950495</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>126950493</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>126950496</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>126950482</v>
       </c>
       <c r="B121" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>126950498</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916842</v>
+        <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>92620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655948</v>
+        <v>655893</v>
       </c>
       <c r="R3" t="n">
-        <v>7122908</v>
+        <v>7122779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +855,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -903,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916285</v>
+        <v>126910394</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655855</v>
+        <v>655885</v>
       </c>
       <c r="R4" t="n">
-        <v>7122774</v>
+        <v>7122738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126914199</v>
+        <v>126918405</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>77996</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,37 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655888</v>
+        <v>655901</v>
       </c>
       <c r="R5" t="n">
-        <v>7122973</v>
+        <v>7122844</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,19 +1057,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1115,45 +1090,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126910130</v>
+        <v>126916842</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655841</v>
+        <v>655948</v>
       </c>
       <c r="R6" t="n">
-        <v>7122800</v>
+        <v>7122908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,9 +1163,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1216,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126910394</v>
+        <v>126916285</v>
       </c>
       <c r="B7" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655885</v>
+        <v>655855</v>
       </c>
       <c r="R7" t="n">
-        <v>7122738</v>
+        <v>7122774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126918405</v>
+        <v>126914199</v>
       </c>
       <c r="B8" t="n">
-        <v>77996</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655901</v>
+        <v>655888</v>
       </c>
       <c r="R8" t="n">
-        <v>7122844</v>
+        <v>7122973</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,9 +1375,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,12 +1402,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,32 +1418,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126916314</v>
+        <v>126916284</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655893</v>
+        <v>655943</v>
       </c>
       <c r="R9" t="n">
-        <v>7122779</v>
+        <v>7122816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916284</v>
+        <v>126910130</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655943</v>
+        <v>655841</v>
       </c>
       <c r="R10" t="n">
-        <v>7122816</v>
+        <v>7122800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918044</v>
+        <v>126916278</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,34 +1631,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656088</v>
+        <v>655957</v>
       </c>
       <c r="R11" t="n">
-        <v>7122850</v>
+        <v>7122864</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,30 +1702,15 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1736,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916299</v>
+        <v>126917770</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>79607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655995</v>
+        <v>655852</v>
       </c>
       <c r="R12" t="n">
-        <v>7122921</v>
+        <v>7122942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1837,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916844</v>
+        <v>126909344</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655905</v>
+        <v>655890</v>
       </c>
       <c r="R13" t="n">
-        <v>7122985</v>
+        <v>7122814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,21 +1890,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1928,36 +1903,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1968,32 +1923,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916316</v>
+        <v>126918646</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655863</v>
+        <v>656298</v>
       </c>
       <c r="R14" t="n">
-        <v>7122755</v>
+        <v>7122812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,12 +2008,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2069,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918421</v>
+        <v>126918044</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,34 +2035,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655890</v>
+        <v>656088</v>
       </c>
       <c r="R15" t="n">
-        <v>7122888</v>
+        <v>7122850</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,15 +2106,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916306</v>
+        <v>126916299</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655956</v>
+        <v>655995</v>
       </c>
       <c r="R16" t="n">
-        <v>7122866</v>
+        <v>7122921</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,32 +2241,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126919792</v>
+        <v>126916844</v>
       </c>
       <c r="B17" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655919</v>
+        <v>655905</v>
       </c>
       <c r="R17" t="n">
-        <v>7122887</v>
+        <v>7122985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,14 +2309,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spilning</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,16 +2332,36 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918646</v>
+        <v>126916306</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>78685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656298</v>
+        <v>655956</v>
       </c>
       <c r="R18" t="n">
-        <v>7122812</v>
+        <v>7122866</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,12 +2457,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2478,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916278</v>
+        <v>126918421</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>92813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,21 +2484,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655957</v>
+        <v>655890</v>
       </c>
       <c r="R19" t="n">
-        <v>7122864</v>
+        <v>7122888</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,12 +2558,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2579,32 +2574,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917770</v>
+        <v>126916316</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655852</v>
+        <v>655863</v>
       </c>
       <c r="R20" t="n">
-        <v>7122942</v>
+        <v>7122755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2659,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,32 +2675,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126909344</v>
+        <v>126919792</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>56853</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655890</v>
+        <v>655919</v>
       </c>
       <c r="R21" t="n">
-        <v>7122814</v>
+        <v>7122887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,6 +2748,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126917813</v>
+        <v>126918424</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>92813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655710</v>
+        <v>655961</v>
       </c>
       <c r="R26" t="n">
-        <v>7122853</v>
+        <v>7122865</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918712</v>
+        <v>126916397</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655899</v>
+        <v>655893</v>
       </c>
       <c r="R27" t="n">
-        <v>7122835</v>
+        <v>7122752</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918424</v>
+        <v>126918712</v>
       </c>
       <c r="B28" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655961</v>
+        <v>655899</v>
       </c>
       <c r="R28" t="n">
-        <v>7122865</v>
+        <v>7122835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126916397</v>
+        <v>126917813</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655893</v>
+        <v>655710</v>
       </c>
       <c r="R29" t="n">
-        <v>7122752</v>
+        <v>7122853</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R31" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916288</v>
+        <v>126916289</v>
       </c>
       <c r="B32" t="n">
         <v>78777</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655965</v>
+        <v>655996</v>
       </c>
       <c r="R32" t="n">
-        <v>7122873</v>
+        <v>7122934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916289</v>
+        <v>126918450</v>
       </c>
       <c r="B33" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655996</v>
+        <v>655906</v>
       </c>
       <c r="R33" t="n">
-        <v>7122934</v>
+        <v>7122852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126917804</v>
+        <v>126920137</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>78685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,21 +4019,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655834</v>
+        <v>655990</v>
       </c>
       <c r="R34" t="n">
-        <v>7122923</v>
+        <v>7122926</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,32 +4109,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918458</v>
+        <v>126916746</v>
       </c>
       <c r="B35" t="n">
-        <v>78424</v>
+        <v>91904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655914</v>
+        <v>655785</v>
       </c>
       <c r="R35" t="n">
-        <v>7122985</v>
+        <v>7122898</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,19 +4194,15 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4629,32 +4625,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126916746</v>
+        <v>126917804</v>
       </c>
       <c r="B40" t="n">
-        <v>91904</v>
+        <v>80121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4664,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655785</v>
+        <v>655834</v>
       </c>
       <c r="R40" t="n">
-        <v>7122898</v>
+        <v>7122923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,22 +4710,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126920137</v>
+        <v>126918458</v>
       </c>
       <c r="B41" t="n">
-        <v>78685</v>
+        <v>78424</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655990</v>
+        <v>655914</v>
       </c>
       <c r="R41" t="n">
-        <v>7122926</v>
+        <v>7122985</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126917830</v>
+        <v>126916304</v>
       </c>
       <c r="B42" t="n">
-        <v>78424</v>
+        <v>78685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655749</v>
+        <v>655978</v>
       </c>
       <c r="R42" t="n">
-        <v>7122779</v>
+        <v>7122825</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4928,7 +4928,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126916304</v>
+        <v>126920136</v>
       </c>
       <c r="B43" t="n">
         <v>78685</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655978</v>
+        <v>655941</v>
       </c>
       <c r="R43" t="n">
-        <v>7122825</v>
+        <v>7122804</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,12 +5013,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126920136</v>
+        <v>126917830</v>
       </c>
       <c r="B44" t="n">
-        <v>78685</v>
+        <v>78424</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655941</v>
+        <v>655749</v>
       </c>
       <c r="R44" t="n">
-        <v>7122804</v>
+        <v>7122779</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917785</v>
+        <v>126916741</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655776</v>
+        <v>655895</v>
       </c>
       <c r="R45" t="n">
-        <v>7122760</v>
+        <v>7122747</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919790</v>
+        <v>126917825</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>77996</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655973</v>
+        <v>655749</v>
       </c>
       <c r="R46" t="n">
-        <v>7122926</v>
+        <v>7122779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126918406</v>
+        <v>126916272</v>
       </c>
       <c r="B47" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655901</v>
+        <v>655957</v>
       </c>
       <c r="R47" t="n">
-        <v>7122844</v>
+        <v>7122864</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126916741</v>
+        <v>126917785</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655895</v>
+        <v>655776</v>
       </c>
       <c r="R48" t="n">
-        <v>7122747</v>
+        <v>7122760</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126917825</v>
+        <v>126919790</v>
       </c>
       <c r="B49" t="n">
-        <v>77996</v>
+        <v>79607</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655749</v>
+        <v>655973</v>
       </c>
       <c r="R49" t="n">
-        <v>7122779</v>
+        <v>7122926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126916272</v>
+        <v>126918406</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655957</v>
+        <v>655901</v>
       </c>
       <c r="R50" t="n">
-        <v>7122864</v>
+        <v>7122844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126910294</v>
+        <v>126920128</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655845</v>
+        <v>655942</v>
       </c>
       <c r="R52" t="n">
-        <v>7122750</v>
+        <v>7122804</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,7 +5938,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126920128</v>
+        <v>126915088</v>
       </c>
       <c r="B53" t="n">
         <v>78777</v>
@@ -5969,14 +5969,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655942</v>
+        <v>655950</v>
       </c>
       <c r="R53" t="n">
-        <v>7122804</v>
+        <v>7122893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126915088</v>
+        <v>126918672</v>
       </c>
       <c r="B54" t="n">
         <v>78777</v>
@@ -6070,14 +6070,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655950</v>
+        <v>655882</v>
       </c>
       <c r="R54" t="n">
-        <v>7122893</v>
+        <v>7122787</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918672</v>
+        <v>126910294</v>
       </c>
       <c r="B55" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,21 +6151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655882</v>
+        <v>655845</v>
       </c>
       <c r="R55" t="n">
-        <v>7122787</v>
+        <v>7122750</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B57" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R57" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,30 +6424,15 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6458,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6469,34 +6454,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R58" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,15 +6525,30 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126917803</v>
+        <v>126916312</v>
       </c>
       <c r="B59" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655792</v>
+        <v>656104</v>
       </c>
       <c r="R59" t="n">
-        <v>7122889</v>
+        <v>7122796</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,12 +6644,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126917763</v>
+        <v>126917803</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,21 +6671,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656241</v>
+        <v>655792</v>
       </c>
       <c r="R60" t="n">
-        <v>7122853</v>
+        <v>7122889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6761,10 +6761,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918041</v>
+        <v>126917763</v>
       </c>
       <c r="B61" t="n">
-        <v>92813</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,34 +6772,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655965</v>
+        <v>656241</v>
       </c>
       <c r="R61" t="n">
-        <v>7122890</v>
+        <v>7122853</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,30 +6843,15 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,10 +6862,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126915955</v>
+        <v>126916745</v>
       </c>
       <c r="B62" t="n">
-        <v>92646</v>
+        <v>78685</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6888,40 +6873,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655885</v>
+        <v>655840</v>
       </c>
       <c r="R62" t="n">
-        <v>7122754</v>
+        <v>7122839</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6959,68 +6941,63 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916312</v>
+        <v>126918047</v>
       </c>
       <c r="B63" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656104</v>
+        <v>656203</v>
       </c>
       <c r="R63" t="n">
-        <v>7122796</v>
+        <v>7122806</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,15 +7041,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7083,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126916745</v>
+        <v>126918041</v>
       </c>
       <c r="B64" t="n">
-        <v>78685</v>
+        <v>92813</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7094,34 +7086,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655840</v>
+        <v>655965</v>
       </c>
       <c r="R64" t="n">
-        <v>7122839</v>
+        <v>7122890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,25 +7157,44 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918047</v>
+        <v>126915955</v>
       </c>
       <c r="B65" t="n">
-        <v>78685</v>
+        <v>92646</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,37 +7202,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656203</v>
+        <v>655885</v>
       </c>
       <c r="R65" t="n">
-        <v>7122806</v>
+        <v>7122754</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7259,33 +7273,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7715,32 +7715,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918650</v>
+        <v>126917789</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>656291</v>
+        <v>655760</v>
       </c>
       <c r="R70" t="n">
-        <v>7122816</v>
+        <v>7122811</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,12 +7800,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7816,45 +7816,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918042</v>
+        <v>126916315</v>
       </c>
       <c r="B71" t="n">
-        <v>78424</v>
+        <v>92620</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655954</v>
+        <v>655879</v>
       </c>
       <c r="R71" t="n">
-        <v>7122886</v>
+        <v>7122817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7898,30 +7898,15 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7932,10 +7917,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126916315</v>
+        <v>126918650</v>
       </c>
       <c r="B72" t="n">
-        <v>92620</v>
+        <v>80150</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7943,21 +7928,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7952,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>655879</v>
+        <v>656291</v>
       </c>
       <c r="R72" t="n">
-        <v>7122817</v>
+        <v>7122816</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,12 +8002,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8033,10 +8018,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918443</v>
+        <v>126918042</v>
       </c>
       <c r="B73" t="n">
-        <v>80993</v>
+        <v>78424</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8044,34 +8029,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655875</v>
+        <v>655954</v>
       </c>
       <c r="R73" t="n">
-        <v>7122959</v>
+        <v>7122886</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8133,12 +8118,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8149,32 +8134,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918422</v>
+        <v>126918443</v>
       </c>
       <c r="B74" t="n">
-        <v>91491</v>
+        <v>80993</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8184,10 +8169,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655890</v>
+        <v>655875</v>
       </c>
       <c r="R74" t="n">
-        <v>7122888</v>
+        <v>7122959</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8230,6 +8215,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917789</v>
+        <v>126918422</v>
       </c>
       <c r="B75" t="n">
-        <v>78777</v>
+        <v>91491</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655760</v>
+        <v>655890</v>
       </c>
       <c r="R75" t="n">
-        <v>7122811</v>
+        <v>7122888</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8770,32 +8770,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126919806</v>
+        <v>126916729</v>
       </c>
       <c r="B80" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655917</v>
+        <v>655892</v>
       </c>
       <c r="R80" t="n">
-        <v>7122874</v>
+        <v>7122748</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,6 +8843,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8855,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8871,10 +8876,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918404</v>
+        <v>126919806</v>
       </c>
       <c r="B81" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8882,21 +8887,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8906,10 +8911,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655901</v>
+        <v>655917</v>
       </c>
       <c r="R81" t="n">
-        <v>7122844</v>
+        <v>7122874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8956,12 +8961,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8972,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915963</v>
+        <v>126918404</v>
       </c>
       <c r="B82" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8983,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9007,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655813</v>
+        <v>655901</v>
       </c>
       <c r="R82" t="n">
-        <v>7122846</v>
+        <v>7122844</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9057,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9073,7 +9078,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126916286</v>
+        <v>126915963</v>
       </c>
       <c r="B83" t="n">
         <v>78777</v>
@@ -9108,13 +9113,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655866</v>
+        <v>655813</v>
       </c>
       <c r="R83" t="n">
-        <v>7122779</v>
+        <v>7122846</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9158,12 +9163,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9174,32 +9179,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916729</v>
+        <v>126916286</v>
       </c>
       <c r="B84" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9209,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655892</v>
+        <v>655866</v>
       </c>
       <c r="R84" t="n">
-        <v>7122748</v>
+        <v>7122779</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9247,11 +9252,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126916394</v>
+        <v>126918040</v>
       </c>
       <c r="B86" t="n">
-        <v>78776</v>
+        <v>78685</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655798</v>
+        <v>655945</v>
       </c>
       <c r="R86" t="n">
-        <v>7122934</v>
+        <v>7122909</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9460,19 +9460,33 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9584,10 +9598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126918677</v>
+        <v>126916394</v>
       </c>
       <c r="B88" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9595,21 +9609,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9619,13 +9633,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655893</v>
+        <v>655798</v>
       </c>
       <c r="R88" t="n">
-        <v>7122814</v>
+        <v>7122934</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9663,18 +9677,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9685,10 +9700,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126918040</v>
+        <v>126918677</v>
       </c>
       <c r="B89" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9696,34 +9711,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655945</v>
+        <v>655893</v>
       </c>
       <c r="R89" t="n">
-        <v>7122909</v>
+        <v>7122814</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9767,30 +9782,15 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918038</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>78424</v>
+        <v>92813</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,34 +9812,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655904</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122984</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9883,30 +9883,15 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10018,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918423</v>
+        <v>126918038</v>
       </c>
       <c r="B92" t="n">
-        <v>92813</v>
+        <v>78424</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,34 +10014,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655881</v>
+        <v>655904</v>
       </c>
       <c r="R92" t="n">
-        <v>7122919</v>
+        <v>7122984</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10100,15 +10085,30 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918713</v>
+        <v>126915962</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656004</v>
+        <v>655854</v>
       </c>
       <c r="R95" t="n">
-        <v>7122974</v>
+        <v>7122777</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918681</v>
+        <v>126916276</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>79607</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656291</v>
+        <v>655925</v>
       </c>
       <c r="R96" t="n">
-        <v>7122808</v>
+        <v>7122825</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918395</v>
+        <v>126914201</v>
       </c>
       <c r="B97" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,37 +10534,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655892</v>
+        <v>655947</v>
       </c>
       <c r="R97" t="n">
-        <v>7122986</v>
+        <v>7122837</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,9 +10591,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10608,12 +10618,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,32 +10634,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126915962</v>
+        <v>126916313</v>
       </c>
       <c r="B98" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,13 +10669,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655854</v>
+        <v>656087</v>
       </c>
       <c r="R98" t="n">
-        <v>7122777</v>
+        <v>7122806</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10709,12 +10719,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126916276</v>
+        <v>126918713</v>
       </c>
       <c r="B99" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10736,21 +10746,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,10 +10770,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655925</v>
+        <v>656004</v>
       </c>
       <c r="R99" t="n">
-        <v>7122825</v>
+        <v>7122974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10810,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,10 +10836,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126914201</v>
+        <v>126918681</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>80121</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10837,37 +10847,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655947</v>
+        <v>656291</v>
       </c>
       <c r="R100" t="n">
-        <v>7122837</v>
+        <v>7122808</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10894,19 +10904,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,32 +10937,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126916313</v>
+        <v>126918395</v>
       </c>
       <c r="B101" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656087</v>
+        <v>655892</v>
       </c>
       <c r="R101" t="n">
-        <v>7122806</v>
+        <v>7122986</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,45 +11038,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R102" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11120,15 +11125,30 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11139,10 +11159,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918407</v>
+        <v>126916277</v>
       </c>
       <c r="B103" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11150,21 +11170,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11174,10 +11194,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655901</v>
+        <v>655921</v>
       </c>
       <c r="R103" t="n">
-        <v>7122844</v>
+        <v>7122873</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11224,12 +11244,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11341,50 +11361,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918049</v>
+        <v>126918407</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656225</v>
+        <v>655901</v>
       </c>
       <c r="R105" t="n">
-        <v>7122794</v>
+        <v>7122844</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11428,30 +11443,15 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126916298</v>
+        <v>126918657</v>
       </c>
       <c r="B106" t="n">
-        <v>78776</v>
+        <v>58091</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R106" t="n">
-        <v>7122796</v>
+        <v>7122774</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B107" t="n">
-        <v>58091</v>
+        <v>78776</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R107" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916278</v>
+        <v>126916306</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655957</v>
+        <v>655956</v>
       </c>
       <c r="R11" t="n">
-        <v>7122864</v>
+        <v>7122866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,32 +1721,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126917770</v>
+        <v>126916316</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655852</v>
+        <v>655863</v>
       </c>
       <c r="R12" t="n">
-        <v>7122942</v>
+        <v>7122755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126909344</v>
+        <v>126918044</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655890</v>
+        <v>656088</v>
       </c>
       <c r="R13" t="n">
-        <v>7122814</v>
+        <v>7122850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,15 +1904,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918646</v>
+        <v>126916299</v>
       </c>
       <c r="B14" t="n">
-        <v>57821</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656298</v>
+        <v>655995</v>
       </c>
       <c r="R14" t="n">
-        <v>7122812</v>
+        <v>7122921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,12 +2023,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2024,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918044</v>
+        <v>126916844</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,34 +2050,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656088</v>
+        <v>655905</v>
       </c>
       <c r="R15" t="n">
-        <v>7122850</v>
+        <v>7122985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,11 +2107,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2116,20 +2141,25 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Gammal tallved</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,32 +2170,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916299</v>
+        <v>126919792</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>56853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655995</v>
+        <v>655919</v>
       </c>
       <c r="R16" t="n">
-        <v>7122921</v>
+        <v>7122887</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,6 +2243,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2225,12 +2260,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2241,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916844</v>
+        <v>126916278</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655905</v>
+        <v>655957</v>
       </c>
       <c r="R17" t="n">
-        <v>7122985</v>
+        <v>7122864</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,21 +2344,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2332,36 +2357,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126916306</v>
+        <v>126917770</v>
       </c>
       <c r="B18" t="n">
-        <v>78685</v>
+        <v>79607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655956</v>
+        <v>655852</v>
       </c>
       <c r="R18" t="n">
-        <v>7122866</v>
+        <v>7122942</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2473,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918421</v>
+        <v>126909344</v>
       </c>
       <c r="B19" t="n">
-        <v>92813</v>
+        <v>79607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,7 +2516,7 @@
         <v>655890</v>
       </c>
       <c r="R19" t="n">
-        <v>7122888</v>
+        <v>7122814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,12 +2563,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2574,32 +2579,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126916316</v>
+        <v>126918646</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655863</v>
+        <v>656298</v>
       </c>
       <c r="R20" t="n">
-        <v>7122755</v>
+        <v>7122812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2675,32 +2680,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126919792</v>
+        <v>126918421</v>
       </c>
       <c r="B21" t="n">
-        <v>56853</v>
+        <v>92813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655919</v>
+        <v>655890</v>
       </c>
       <c r="R21" t="n">
-        <v>7122887</v>
+        <v>7122888</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,11 +2753,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126916741</v>
+        <v>126917785</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655895</v>
+        <v>655776</v>
       </c>
       <c r="R45" t="n">
-        <v>7122747</v>
+        <v>7122760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126917825</v>
+        <v>126919790</v>
       </c>
       <c r="B46" t="n">
-        <v>77996</v>
+        <v>79607</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655749</v>
+        <v>655973</v>
       </c>
       <c r="R46" t="n">
-        <v>7122779</v>
+        <v>7122926</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126916272</v>
+        <v>126918406</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655957</v>
+        <v>655901</v>
       </c>
       <c r="R47" t="n">
-        <v>7122864</v>
+        <v>7122844</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126917785</v>
+        <v>126916741</v>
       </c>
       <c r="B48" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655776</v>
+        <v>655895</v>
       </c>
       <c r="R48" t="n">
-        <v>7122760</v>
+        <v>7122747</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919790</v>
+        <v>126917825</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>77996</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655973</v>
+        <v>655749</v>
       </c>
       <c r="R49" t="n">
-        <v>7122926</v>
+        <v>7122779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918406</v>
+        <v>126916272</v>
       </c>
       <c r="B50" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655901</v>
+        <v>655957</v>
       </c>
       <c r="R50" t="n">
-        <v>7122844</v>
+        <v>7122864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919778</v>
+        <v>126918397</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655919</v>
+        <v>655892</v>
       </c>
       <c r="R51" t="n">
-        <v>7122981</v>
+        <v>7122986</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126920128</v>
+        <v>126919778</v>
       </c>
       <c r="B52" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655942</v>
+        <v>655919</v>
       </c>
       <c r="R52" t="n">
-        <v>7122804</v>
+        <v>7122981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915088</v>
+        <v>126910294</v>
       </c>
       <c r="B53" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,34 +5949,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655950</v>
+        <v>655845</v>
       </c>
       <c r="R53" t="n">
-        <v>7122893</v>
+        <v>7122750</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918672</v>
+        <v>126920128</v>
       </c>
       <c r="B54" t="n">
         <v>78777</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655882</v>
+        <v>655942</v>
       </c>
       <c r="R54" t="n">
-        <v>7122787</v>
+        <v>7122804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126910294</v>
+        <v>126915088</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655845</v>
+        <v>655950</v>
       </c>
       <c r="R55" t="n">
-        <v>7122750</v>
+        <v>7122893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918397</v>
+        <v>126918672</v>
       </c>
       <c r="B56" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655892</v>
+        <v>655882</v>
       </c>
       <c r="R56" t="n">
-        <v>7122986</v>
+        <v>7122787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126917803</v>
+        <v>126915955</v>
       </c>
       <c r="B60" t="n">
-        <v>80121</v>
+        <v>92646</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,37 +6671,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655792</v>
+        <v>655885</v>
       </c>
       <c r="R60" t="n">
-        <v>7122889</v>
+        <v>7122754</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6739,18 +6742,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6761,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917763</v>
+        <v>126917803</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6772,21 +6776,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6796,10 +6800,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656241</v>
+        <v>655792</v>
       </c>
       <c r="R61" t="n">
-        <v>7122853</v>
+        <v>7122889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6862,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916745</v>
+        <v>126917763</v>
       </c>
       <c r="B62" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6873,21 +6877,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6897,10 +6901,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655840</v>
+        <v>656241</v>
       </c>
       <c r="R62" t="n">
-        <v>7122839</v>
+        <v>7122853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,22 +6951,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918047</v>
+        <v>126917791</v>
       </c>
       <c r="B63" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6970,34 +6978,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656203</v>
+        <v>656327</v>
       </c>
       <c r="R63" t="n">
-        <v>7122806</v>
+        <v>7122772</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7041,30 +7049,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7075,10 +7068,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918041</v>
+        <v>126916274</v>
       </c>
       <c r="B64" t="n">
-        <v>92813</v>
+        <v>79607</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,34 +7079,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655965</v>
+        <v>656012</v>
       </c>
       <c r="R64" t="n">
-        <v>7122890</v>
+        <v>7122821</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7157,30 +7150,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7191,10 +7169,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126915955</v>
+        <v>126918045</v>
       </c>
       <c r="B65" t="n">
-        <v>92646</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7202,40 +7180,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>655885</v>
+        <v>656177</v>
       </c>
       <c r="R65" t="n">
-        <v>7122754</v>
+        <v>7122815</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7273,19 +7248,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7296,7 +7285,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917791</v>
+        <v>126919808</v>
       </c>
       <c r="B66" t="n">
         <v>78777</v>
@@ -7331,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656327</v>
+        <v>655921</v>
       </c>
       <c r="R66" t="n">
-        <v>7122772</v>
+        <v>7122999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7381,12 +7370,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7397,10 +7386,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126916274</v>
+        <v>126916745</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>78685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7408,21 +7397,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7432,10 +7421,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656012</v>
+        <v>655840</v>
       </c>
       <c r="R67" t="n">
-        <v>7122821</v>
+        <v>7122839</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,26 +7471,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918045</v>
+        <v>126918047</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,21 +7494,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656177</v>
+        <v>656203</v>
       </c>
       <c r="R68" t="n">
-        <v>7122815</v>
+        <v>7122806</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7614,10 +7599,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126919808</v>
+        <v>126918041</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>92813</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7625,34 +7610,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>655921</v>
+        <v>655965</v>
       </c>
       <c r="R69" t="n">
-        <v>7122999</v>
+        <v>7122890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7696,15 +7681,30 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8351,45 +8351,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126918050</v>
+        <v>126916729</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656266</v>
+        <v>655892</v>
       </c>
       <c r="R76" t="n">
-        <v>7122789</v>
+        <v>7122748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,6 +8424,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8432,31 +8437,16 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8467,10 +8457,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915970</v>
+        <v>126918050</v>
       </c>
       <c r="B77" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8478,37 +8468,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655778</v>
+        <v>656266</v>
       </c>
       <c r="R77" t="n">
-        <v>7122904</v>
+        <v>7122789</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8548,16 +8538,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8568,10 +8573,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915964</v>
+        <v>126915970</v>
       </c>
       <c r="B78" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8579,21 +8584,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8603,10 +8608,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655800</v>
+        <v>655778</v>
       </c>
       <c r="R78" t="n">
-        <v>7122929</v>
+        <v>7122904</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8669,32 +8674,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126917772</v>
+        <v>126915964</v>
       </c>
       <c r="B79" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,13 +8709,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655768</v>
+        <v>655800</v>
       </c>
       <c r="R79" t="n">
-        <v>7122903</v>
+        <v>7122929</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8754,12 +8759,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8770,10 +8775,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916729</v>
+        <v>126917772</v>
       </c>
       <c r="B80" t="n">
-        <v>56853</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,21 +8786,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,10 +8810,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655892</v>
+        <v>655768</v>
       </c>
       <c r="R80" t="n">
-        <v>7122748</v>
+        <v>7122903</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,11 +8848,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8860,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918423</v>
+        <v>126918711</v>
       </c>
       <c r="B90" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655881</v>
+        <v>655898</v>
       </c>
       <c r="R90" t="n">
-        <v>7122919</v>
+        <v>7122802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R91" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126915962</v>
+        <v>126918681</v>
       </c>
       <c r="B95" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>655854</v>
+        <v>656291</v>
       </c>
       <c r="R95" t="n">
-        <v>7122777</v>
+        <v>7122808</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126916276</v>
+        <v>126918395</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655925</v>
+        <v>655892</v>
       </c>
       <c r="R96" t="n">
-        <v>7122825</v>
+        <v>7122986</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,48 +10523,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126914201</v>
+        <v>126916313</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655947</v>
+        <v>656087</v>
       </c>
       <c r="R97" t="n">
-        <v>7122837</v>
+        <v>7122806</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,19 +10591,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10618,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10634,32 +10624,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126916313</v>
+        <v>126918713</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10669,10 +10659,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656087</v>
+        <v>656004</v>
       </c>
       <c r="R98" t="n">
-        <v>7122806</v>
+        <v>7122974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10719,12 +10709,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10735,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918713</v>
+        <v>126915962</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10746,21 +10736,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10770,13 +10760,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656004</v>
+        <v>655854</v>
       </c>
       <c r="R99" t="n">
-        <v>7122974</v>
+        <v>7122777</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10820,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,10 +10826,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918681</v>
+        <v>126916276</v>
       </c>
       <c r="B100" t="n">
-        <v>80121</v>
+        <v>79607</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10847,21 +10837,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10871,10 +10861,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656291</v>
+        <v>655925</v>
       </c>
       <c r="R100" t="n">
-        <v>7122808</v>
+        <v>7122825</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10921,12 +10911,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10927,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918395</v>
+        <v>126914201</v>
       </c>
       <c r="B101" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,37 +10938,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655892</v>
+        <v>655947</v>
       </c>
       <c r="R101" t="n">
-        <v>7122986</v>
+        <v>7122837</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11005,9 +10995,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126916298</v>
+        <v>126919802</v>
       </c>
       <c r="B107" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655900</v>
+        <v>656007</v>
       </c>
       <c r="R107" t="n">
-        <v>7122796</v>
+        <v>7122964</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126919802</v>
+        <v>126916275</v>
       </c>
       <c r="B108" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656007</v>
+        <v>655900</v>
       </c>
       <c r="R108" t="n">
-        <v>7122964</v>
+        <v>7122800</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,12 +11749,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,10 +11765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126916275</v>
+        <v>126920127</v>
       </c>
       <c r="B109" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,21 +11776,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>655900</v>
+        <v>656146</v>
       </c>
       <c r="R109" t="n">
-        <v>7122800</v>
+        <v>7122791</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,18 +11844,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11866,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920127</v>
+        <v>126920120</v>
       </c>
       <c r="B110" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11877,21 +11878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11901,10 +11902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656146</v>
+        <v>655982</v>
       </c>
       <c r="R110" t="n">
-        <v>7122791</v>
+        <v>7122865</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11945,7 +11946,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126920120</v>
+        <v>126916298</v>
       </c>
       <c r="B111" t="n">
-        <v>79607</v>
+        <v>78776</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655982</v>
+        <v>655900</v>
       </c>
       <c r="R111" t="n">
-        <v>7122865</v>
+        <v>7122796</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12281,7 +12281,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126914202</v>
+        <v>126918410</v>
       </c>
       <c r="B114" t="n">
         <v>79607</v>
@@ -12312,17 +12312,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655932</v>
+        <v>655904</v>
       </c>
       <c r="R114" t="n">
-        <v>7122830</v>
+        <v>7122985</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12349,19 +12349,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12376,12 +12366,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12392,10 +12382,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918410</v>
+        <v>126950497</v>
       </c>
       <c r="B115" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12403,21 +12393,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12427,10 +12417,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>655904</v>
+        <v>655994</v>
       </c>
       <c r="R115" t="n">
-        <v>7122985</v>
+        <v>7122976</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12477,12 +12467,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12493,7 +12483,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126950497</v>
+        <v>126950494</v>
       </c>
       <c r="B116" t="n">
         <v>79018</v>
@@ -12528,10 +12518,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>655994</v>
+        <v>655885</v>
       </c>
       <c r="R116" t="n">
-        <v>7122976</v>
+        <v>7122808</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12594,7 +12584,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126950494</v>
+        <v>126950495</v>
       </c>
       <c r="B117" t="n">
         <v>79018</v>
@@ -12629,10 +12619,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>655885</v>
+        <v>655825</v>
       </c>
       <c r="R117" t="n">
-        <v>7122808</v>
+        <v>7122842</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12695,7 +12685,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126950495</v>
+        <v>126950493</v>
       </c>
       <c r="B118" t="n">
         <v>79018</v>
@@ -12730,10 +12720,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>655825</v>
+        <v>655927</v>
       </c>
       <c r="R118" t="n">
-        <v>7122842</v>
+        <v>7122830</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12796,7 +12786,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126950493</v>
+        <v>126950496</v>
       </c>
       <c r="B119" t="n">
         <v>79018</v>
@@ -12831,10 +12821,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>655927</v>
+        <v>655752</v>
       </c>
       <c r="R119" t="n">
-        <v>7122830</v>
+        <v>7122831</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12897,10 +12887,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126950496</v>
+        <v>126950482</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12908,21 +12898,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12932,10 +12922,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>655752</v>
+        <v>656150</v>
       </c>
       <c r="R120" t="n">
-        <v>7122831</v>
+        <v>7122792</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12998,10 +12988,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126950482</v>
+        <v>126950498</v>
       </c>
       <c r="B121" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13009,21 +12999,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13033,10 +13023,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>656150</v>
+        <v>656073</v>
       </c>
       <c r="R121" t="n">
-        <v>7122792</v>
+        <v>7122877</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13099,10 +13089,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126950498</v>
+        <v>126914202</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13110,37 +13100,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>656073</v>
+        <v>655932</v>
       </c>
       <c r="R122" t="n">
-        <v>7122877</v>
+        <v>7122830</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13167,9 +13157,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13184,12 +13184,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126916397</v>
+        <v>126918712</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655893</v>
+        <v>655899</v>
       </c>
       <c r="R27" t="n">
-        <v>7122752</v>
+        <v>7122835</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918712</v>
+        <v>126917813</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655899</v>
+        <v>655710</v>
       </c>
       <c r="R28" t="n">
-        <v>7122835</v>
+        <v>7122853</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917813</v>
+        <v>126916397</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655710</v>
+        <v>655893</v>
       </c>
       <c r="R29" t="n">
-        <v>7122853</v>
+        <v>7122752</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918438</v>
+        <v>126917804</v>
       </c>
       <c r="B36" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655882</v>
+        <v>655834</v>
       </c>
       <c r="R36" t="n">
-        <v>7122978</v>
+        <v>7122923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,12 +4291,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4307,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919804</v>
+        <v>126918458</v>
       </c>
       <c r="B37" t="n">
-        <v>78777</v>
+        <v>78424</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655989</v>
+        <v>655914</v>
       </c>
       <c r="R37" t="n">
-        <v>7122922</v>
+        <v>7122985</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4408,10 +4408,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126918037</v>
+        <v>126918438</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,34 +4419,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655903</v>
+        <v>655882</v>
       </c>
       <c r="R38" t="n">
-        <v>7122984</v>
+        <v>7122978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,30 +4490,15 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4524,7 +4509,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126916287</v>
+        <v>126919804</v>
       </c>
       <c r="B39" t="n">
         <v>78777</v>
@@ -4559,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655900</v>
+        <v>655989</v>
       </c>
       <c r="R39" t="n">
-        <v>7122798</v>
+        <v>7122922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,12 +4594,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4625,10 +4610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126917804</v>
+        <v>126918037</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>79607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4636,34 +4621,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655834</v>
+        <v>655903</v>
       </c>
       <c r="R40" t="n">
-        <v>7122923</v>
+        <v>7122984</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,15 +4692,30 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126918458</v>
+        <v>126916287</v>
       </c>
       <c r="B41" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,21 +4737,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655914</v>
+        <v>655900</v>
       </c>
       <c r="R41" t="n">
-        <v>7122985</v>
+        <v>7122798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917785</v>
+        <v>126916741</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655776</v>
+        <v>655895</v>
       </c>
       <c r="R45" t="n">
-        <v>7122760</v>
+        <v>7122747</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919790</v>
+        <v>126917825</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>77996</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655973</v>
+        <v>655749</v>
       </c>
       <c r="R46" t="n">
-        <v>7122926</v>
+        <v>7122779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126918406</v>
+        <v>126916272</v>
       </c>
       <c r="B47" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655901</v>
+        <v>655957</v>
       </c>
       <c r="R47" t="n">
-        <v>7122844</v>
+        <v>7122864</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126916741</v>
+        <v>126917785</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655895</v>
+        <v>655776</v>
       </c>
       <c r="R48" t="n">
-        <v>7122747</v>
+        <v>7122760</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126917825</v>
+        <v>126919790</v>
       </c>
       <c r="B49" t="n">
-        <v>77996</v>
+        <v>79607</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655749</v>
+        <v>655973</v>
       </c>
       <c r="R49" t="n">
-        <v>7122779</v>
+        <v>7122926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126916272</v>
+        <v>126918406</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655957</v>
+        <v>655901</v>
       </c>
       <c r="R50" t="n">
-        <v>7122864</v>
+        <v>7122844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918423</v>
+        <v>126918711</v>
       </c>
       <c r="B91" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655881</v>
+        <v>655898</v>
       </c>
       <c r="R91" t="n">
-        <v>7122919</v>
+        <v>7122802</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918681</v>
+        <v>126915962</v>
       </c>
       <c r="B95" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656291</v>
+        <v>655854</v>
       </c>
       <c r="R95" t="n">
-        <v>7122808</v>
+        <v>7122777</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918395</v>
+        <v>126916276</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655892</v>
+        <v>655925</v>
       </c>
       <c r="R96" t="n">
-        <v>7122986</v>
+        <v>7122825</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,48 +10523,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126916313</v>
+        <v>126914201</v>
       </c>
       <c r="B97" t="n">
-        <v>92620</v>
+        <v>79607</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656087</v>
+        <v>655947</v>
       </c>
       <c r="R97" t="n">
-        <v>7122806</v>
+        <v>7122837</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,9 +10591,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10608,12 +10618,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,32 +10634,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918713</v>
+        <v>126916313</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10659,10 +10669,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656004</v>
+        <v>656087</v>
       </c>
       <c r="R98" t="n">
-        <v>7122974</v>
+        <v>7122806</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10709,12 +10719,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10725,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915962</v>
+        <v>126918713</v>
       </c>
       <c r="B99" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10736,21 +10746,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,13 +10770,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655854</v>
+        <v>656004</v>
       </c>
       <c r="R99" t="n">
-        <v>7122777</v>
+        <v>7122974</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10810,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10826,10 +10836,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126916276</v>
+        <v>126918681</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>80121</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10837,21 +10847,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10861,10 +10871,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>655925</v>
+        <v>656291</v>
       </c>
       <c r="R100" t="n">
-        <v>7122825</v>
+        <v>7122808</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10911,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10927,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126914201</v>
+        <v>126918395</v>
       </c>
       <c r="B101" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10938,37 +10948,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655947</v>
+        <v>655892</v>
       </c>
       <c r="R101" t="n">
-        <v>7122837</v>
+        <v>7122986</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10995,19 +11005,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126918405</v>
       </c>
       <c r="B4" t="n">
-        <v>78776</v>
+        <v>77996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655901</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,45 +989,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918405</v>
+        <v>126916842</v>
       </c>
       <c r="B5" t="n">
-        <v>77996</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655901</v>
+        <v>655948</v>
       </c>
       <c r="R5" t="n">
-        <v>7122844</v>
+        <v>7122908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,9 +1062,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,12 +1089,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,50 +1105,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916842</v>
+        <v>126916285</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655948</v>
+        <v>655855</v>
       </c>
       <c r="R6" t="n">
-        <v>7122908</v>
+        <v>7122774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,19 +1173,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916285</v>
+        <v>126916284</v>
       </c>
       <c r="B7" t="n">
         <v>78777</v>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655855</v>
+        <v>655943</v>
       </c>
       <c r="R7" t="n">
-        <v>7122774</v>
+        <v>7122816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126914199</v>
+        <v>126910130</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655888</v>
+        <v>655841</v>
       </c>
       <c r="R8" t="n">
-        <v>7122973</v>
+        <v>7122800</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,19 +1375,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,12 +1392,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1418,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126916284</v>
+        <v>126914199</v>
       </c>
       <c r="B9" t="n">
         <v>78777</v>
@@ -1449,17 +1439,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655943</v>
+        <v>655888</v>
       </c>
       <c r="R9" t="n">
-        <v>7122816</v>
+        <v>7122973</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,9 +1476,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1503,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126910130</v>
+        <v>126910394</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>78776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655841</v>
+        <v>655885</v>
       </c>
       <c r="R10" t="n">
-        <v>7122800</v>
+        <v>7122738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,32 +1620,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916306</v>
+        <v>126919792</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655956</v>
+        <v>655919</v>
       </c>
       <c r="R11" t="n">
-        <v>7122866</v>
+        <v>7122887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1693,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1705,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1721,32 +1726,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916316</v>
+        <v>126918646</v>
       </c>
       <c r="B12" t="n">
-        <v>92620</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655863</v>
+        <v>656298</v>
       </c>
       <c r="R12" t="n">
-        <v>7122755</v>
+        <v>7122812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,12 +1811,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,45 +1827,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918044</v>
+        <v>126916316</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656088</v>
+        <v>655863</v>
       </c>
       <c r="R13" t="n">
-        <v>7122850</v>
+        <v>7122755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,30 +1909,15 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126918421</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>92813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>655890</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2039,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916844</v>
+        <v>126916306</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2040,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655905</v>
+        <v>655956</v>
       </c>
       <c r="R15" t="n">
-        <v>7122985</v>
+        <v>7122866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,21 +2097,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2130,36 +2110,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2170,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126919792</v>
+        <v>126916844</v>
       </c>
       <c r="B16" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655919</v>
+        <v>655905</v>
       </c>
       <c r="R16" t="n">
-        <v>7122887</v>
+        <v>7122985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,14 +2198,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spilning</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,16 +2221,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2579,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918646</v>
+        <v>126918044</v>
       </c>
       <c r="B20" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,34 +2575,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656298</v>
+        <v>656088</v>
       </c>
       <c r="R20" t="n">
-        <v>7122812</v>
+        <v>7122850</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,15 +2646,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918421</v>
+        <v>126916299</v>
       </c>
       <c r="B21" t="n">
-        <v>92813</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655890</v>
+        <v>655995</v>
       </c>
       <c r="R21" t="n">
-        <v>7122888</v>
+        <v>7122921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918712</v>
+        <v>126916397</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655899</v>
+        <v>655893</v>
       </c>
       <c r="R27" t="n">
-        <v>7122835</v>
+        <v>7122752</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917813</v>
+        <v>126918712</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655710</v>
+        <v>655899</v>
       </c>
       <c r="R28" t="n">
-        <v>7122853</v>
+        <v>7122835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,32 +3503,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126916397</v>
+        <v>126910403</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>79607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655893</v>
+        <v>655885</v>
       </c>
       <c r="R29" t="n">
-        <v>7122752</v>
+        <v>7122738</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126910403</v>
+        <v>126917813</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655885</v>
+        <v>655710</v>
       </c>
       <c r="R30" t="n">
-        <v>7122738</v>
+        <v>7122853</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R31" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916289</v>
+        <v>126916288</v>
       </c>
       <c r="B32" t="n">
         <v>78777</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655996</v>
+        <v>655965</v>
       </c>
       <c r="R32" t="n">
-        <v>7122934</v>
+        <v>7122873</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126918450</v>
+        <v>126916289</v>
       </c>
       <c r="B33" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655906</v>
+        <v>655996</v>
       </c>
       <c r="R33" t="n">
-        <v>7122852</v>
+        <v>7122934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126920137</v>
+        <v>126918458</v>
       </c>
       <c r="B34" t="n">
-        <v>78685</v>
+        <v>78424</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,21 +4019,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655990</v>
+        <v>655914</v>
       </c>
       <c r="R34" t="n">
-        <v>7122926</v>
+        <v>7122985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126917804</v>
+        <v>126920137</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>78685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655834</v>
+        <v>655990</v>
       </c>
       <c r="R36" t="n">
-        <v>7122923</v>
+        <v>7122926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,12 +4291,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4307,10 +4307,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126918458</v>
+        <v>126917804</v>
       </c>
       <c r="B37" t="n">
-        <v>78424</v>
+        <v>80121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655914</v>
+        <v>655834</v>
       </c>
       <c r="R37" t="n">
-        <v>7122985</v>
+        <v>7122923</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919804</v>
+        <v>126918037</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,34 +4520,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655989</v>
+        <v>655903</v>
       </c>
       <c r="R39" t="n">
-        <v>7122922</v>
+        <v>7122984</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,15 +4591,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4610,10 +4625,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918037</v>
+        <v>126916287</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,34 +4636,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655903</v>
+        <v>655900</v>
       </c>
       <c r="R40" t="n">
-        <v>7122984</v>
+        <v>7122798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,30 +4707,15 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4726,7 +4726,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126916287</v>
+        <v>126919804</v>
       </c>
       <c r="B41" t="n">
         <v>78777</v>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655900</v>
+        <v>655989</v>
       </c>
       <c r="R41" t="n">
-        <v>7122798</v>
+        <v>7122922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126916741</v>
+        <v>126917825</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>77996</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655895</v>
+        <v>655749</v>
       </c>
       <c r="R45" t="n">
-        <v>7122747</v>
+        <v>7122779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126917825</v>
+        <v>126916741</v>
       </c>
       <c r="B46" t="n">
-        <v>77996</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655749</v>
+        <v>655895</v>
       </c>
       <c r="R46" t="n">
-        <v>7122779</v>
+        <v>7122747</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126918397</v>
+        <v>126910294</v>
       </c>
       <c r="B51" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655892</v>
+        <v>655845</v>
       </c>
       <c r="R51" t="n">
-        <v>7122986</v>
+        <v>7122750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126910294</v>
+        <v>126920128</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655845</v>
+        <v>655942</v>
       </c>
       <c r="R53" t="n">
-        <v>7122750</v>
+        <v>7122804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126920128</v>
+        <v>126918672</v>
       </c>
       <c r="B54" t="n">
         <v>78777</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655942</v>
+        <v>655882</v>
       </c>
       <c r="R54" t="n">
-        <v>7122804</v>
+        <v>7122787</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915088</v>
+        <v>126918397</v>
       </c>
       <c r="B55" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655950</v>
+        <v>655892</v>
       </c>
       <c r="R55" t="n">
-        <v>7122893</v>
+        <v>7122986</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,7 +6241,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918672</v>
+        <v>126915088</v>
       </c>
       <c r="B56" t="n">
         <v>78777</v>
@@ -6272,14 +6272,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655882</v>
+        <v>655950</v>
       </c>
       <c r="R56" t="n">
-        <v>7122787</v>
+        <v>7122893</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6559,32 +6559,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126916312</v>
+        <v>126916745</v>
       </c>
       <c r="B59" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656104</v>
+        <v>655840</v>
       </c>
       <c r="R59" t="n">
-        <v>7122796</v>
+        <v>7122839</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,26 +6644,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126915955</v>
+        <v>126918047</v>
       </c>
       <c r="B60" t="n">
-        <v>92646</v>
+        <v>78685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6671,40 +6667,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655885</v>
+        <v>656203</v>
       </c>
       <c r="R60" t="n">
-        <v>7122754</v>
+        <v>7122806</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6742,19 +6735,33 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6967,10 +6974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126917791</v>
+        <v>126918041</v>
       </c>
       <c r="B63" t="n">
-        <v>78777</v>
+        <v>92813</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6978,34 +6985,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656327</v>
+        <v>655965</v>
       </c>
       <c r="R63" t="n">
-        <v>7122772</v>
+        <v>7122890</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7049,15 +7056,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7068,10 +7090,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126916274</v>
+        <v>126915955</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>92646</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7079,37 +7101,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>5448</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656012</v>
+        <v>655885</v>
       </c>
       <c r="R64" t="n">
-        <v>7122821</v>
+        <v>7122754</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7147,18 +7172,19 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7169,45 +7195,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918045</v>
+        <v>126916312</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656177</v>
+        <v>656104</v>
       </c>
       <c r="R65" t="n">
-        <v>7122815</v>
+        <v>7122796</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,30 +7277,15 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7285,7 +7296,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126919808</v>
+        <v>126917791</v>
       </c>
       <c r="B66" t="n">
         <v>78777</v>
@@ -7320,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>655921</v>
+        <v>656327</v>
       </c>
       <c r="R66" t="n">
-        <v>7122999</v>
+        <v>7122772</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,12 +7381,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7386,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126916745</v>
+        <v>126916274</v>
       </c>
       <c r="B67" t="n">
-        <v>78685</v>
+        <v>79607</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7397,21 +7408,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7421,10 +7432,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>655840</v>
+        <v>656012</v>
       </c>
       <c r="R67" t="n">
-        <v>7122839</v>
+        <v>7122821</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7471,22 +7482,26 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918047</v>
+        <v>126919808</v>
       </c>
       <c r="B68" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7494,34 +7509,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656203</v>
+        <v>655921</v>
       </c>
       <c r="R68" t="n">
-        <v>7122806</v>
+        <v>7122999</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7565,30 +7580,15 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7599,10 +7599,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126918041</v>
+        <v>126918045</v>
       </c>
       <c r="B69" t="n">
-        <v>92813</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,21 +7610,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>655965</v>
+        <v>656177</v>
       </c>
       <c r="R69" t="n">
-        <v>7122890</v>
+        <v>7122815</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7715,32 +7715,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126917789</v>
+        <v>126916315</v>
       </c>
       <c r="B70" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655760</v>
+        <v>655879</v>
       </c>
       <c r="R70" t="n">
-        <v>7122811</v>
+        <v>7122817</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,12 +7800,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7816,32 +7816,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126916315</v>
+        <v>126918422</v>
       </c>
       <c r="B71" t="n">
-        <v>92620</v>
+        <v>91491</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655879</v>
+        <v>655890</v>
       </c>
       <c r="R71" t="n">
-        <v>7122817</v>
+        <v>7122888</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,12 +7901,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7917,32 +7917,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918650</v>
+        <v>126918443</v>
       </c>
       <c r="B72" t="n">
-        <v>80150</v>
+        <v>80993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656291</v>
+        <v>655875</v>
       </c>
       <c r="R72" t="n">
-        <v>7122816</v>
+        <v>7122959</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,15 +7999,30 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8018,45 +8033,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918042</v>
+        <v>126918650</v>
       </c>
       <c r="B73" t="n">
-        <v>78424</v>
+        <v>80150</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>655954</v>
+        <v>656291</v>
       </c>
       <c r="R73" t="n">
-        <v>7122886</v>
+        <v>7122816</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8100,30 +8115,15 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,10 +8134,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918443</v>
+        <v>126918042</v>
       </c>
       <c r="B74" t="n">
-        <v>80993</v>
+        <v>78424</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8145,34 +8145,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655875</v>
+        <v>655954</v>
       </c>
       <c r="R74" t="n">
-        <v>7122959</v>
+        <v>7122886</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8234,12 +8234,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,32 +8250,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126918422</v>
+        <v>126917789</v>
       </c>
       <c r="B75" t="n">
-        <v>91491</v>
+        <v>78777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655890</v>
+        <v>655760</v>
       </c>
       <c r="R75" t="n">
-        <v>7122888</v>
+        <v>7122811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,12 +8335,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,32 +8351,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916729</v>
+        <v>126915964</v>
       </c>
       <c r="B76" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655892</v>
+        <v>655800</v>
       </c>
       <c r="R76" t="n">
-        <v>7122748</v>
+        <v>7122929</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8422,11 +8422,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8441,12 +8436,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8457,45 +8452,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126918050</v>
+        <v>126917772</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656266</v>
+        <v>655768</v>
       </c>
       <c r="R77" t="n">
-        <v>7122789</v>
+        <v>7122903</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8539,30 +8534,15 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8573,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915970</v>
+        <v>126918050</v>
       </c>
       <c r="B78" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8584,37 +8564,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655778</v>
+        <v>656266</v>
       </c>
       <c r="R78" t="n">
-        <v>7122904</v>
+        <v>7122789</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8654,16 +8634,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8674,10 +8669,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915964</v>
+        <v>126915970</v>
       </c>
       <c r="B79" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8685,21 +8680,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8709,10 +8704,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655800</v>
+        <v>655778</v>
       </c>
       <c r="R79" t="n">
-        <v>7122929</v>
+        <v>7122904</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8775,10 +8770,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126917772</v>
+        <v>126916729</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>56853</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8786,21 +8781,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8810,10 +8805,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655768</v>
+        <v>655892</v>
       </c>
       <c r="R80" t="n">
-        <v>7122903</v>
+        <v>7122748</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8848,6 +8843,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8860,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918040</v>
+        <v>126915959</v>
       </c>
       <c r="B86" t="n">
-        <v>78685</v>
+        <v>92813</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,37 +9392,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655945</v>
+        <v>655849</v>
       </c>
       <c r="R86" t="n">
-        <v>7122909</v>
+        <v>7122806</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9462,31 +9462,16 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9497,10 +9482,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915959</v>
+        <v>126918040</v>
       </c>
       <c r="B87" t="n">
-        <v>92813</v>
+        <v>78685</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9508,37 +9493,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655849</v>
+        <v>655945</v>
       </c>
       <c r="R87" t="n">
-        <v>7122806</v>
+        <v>7122909</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9578,16 +9563,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918711</v>
+        <v>126918038</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,34 +9913,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655898</v>
+        <v>655904</v>
       </c>
       <c r="R91" t="n">
-        <v>7122802</v>
+        <v>7122984</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,15 +9984,30 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10003,10 +10018,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918038</v>
+        <v>126918711</v>
       </c>
       <c r="B92" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10014,34 +10029,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655904</v>
+        <v>655898</v>
       </c>
       <c r="R92" t="n">
-        <v>7122984</v>
+        <v>7122802</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10085,30 +10100,15 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126915962</v>
+        <v>126918681</v>
       </c>
       <c r="B95" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>655854</v>
+        <v>656291</v>
       </c>
       <c r="R95" t="n">
-        <v>7122777</v>
+        <v>7122808</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126916276</v>
+        <v>126918395</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655925</v>
+        <v>655892</v>
       </c>
       <c r="R96" t="n">
-        <v>7122825</v>
+        <v>7122986</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,7 +10523,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126914201</v>
+        <v>126916276</v>
       </c>
       <c r="B97" t="n">
         <v>79607</v>
@@ -10554,17 +10554,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655947</v>
+        <v>655925</v>
       </c>
       <c r="R97" t="n">
-        <v>7122837</v>
+        <v>7122825</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,19 +10591,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10618,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10634,48 +10624,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126916313</v>
+        <v>126914201</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>79607</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656087</v>
+        <v>655947</v>
       </c>
       <c r="R98" t="n">
-        <v>7122806</v>
+        <v>7122837</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10702,9 +10692,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10719,12 +10719,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10735,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918713</v>
+        <v>126915962</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10746,21 +10746,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10770,13 +10770,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656004</v>
+        <v>655854</v>
       </c>
       <c r="R99" t="n">
-        <v>7122974</v>
+        <v>7122777</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10820,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,32 +10836,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918681</v>
+        <v>126916313</v>
       </c>
       <c r="B100" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656291</v>
+        <v>656087</v>
       </c>
       <c r="R100" t="n">
-        <v>7122808</v>
+        <v>7122806</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10921,12 +10921,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10937,10 +10937,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918395</v>
+        <v>126918713</v>
       </c>
       <c r="B101" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,21 +10948,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10972,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>655892</v>
+        <v>656004</v>
       </c>
       <c r="R101" t="n">
-        <v>7122986</v>
+        <v>7122974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,50 +11038,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918049</v>
+        <v>126918715</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656225</v>
+        <v>656372</v>
       </c>
       <c r="R102" t="n">
-        <v>7122794</v>
+        <v>7122721</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11125,30 +11120,15 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11159,45 +11139,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B103" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R103" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11241,15 +11226,30 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11260,10 +11260,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918715</v>
+        <v>126918407</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11271,21 +11271,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656372</v>
+        <v>655901</v>
       </c>
       <c r="R104" t="n">
-        <v>7122721</v>
+        <v>7122844</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11345,12 +11345,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11361,10 +11361,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918407</v>
+        <v>126916277</v>
       </c>
       <c r="B105" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11372,21 +11372,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655901</v>
+        <v>655921</v>
       </c>
       <c r="R105" t="n">
-        <v>7122844</v>
+        <v>7122873</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,12 +11446,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B106" t="n">
-        <v>58091</v>
+        <v>78776</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R106" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126919802</v>
+        <v>126918657</v>
       </c>
       <c r="B107" t="n">
-        <v>78777</v>
+        <v>58091</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656007</v>
+        <v>655908</v>
       </c>
       <c r="R107" t="n">
-        <v>7122964</v>
+        <v>7122774</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126916298</v>
+        <v>126919802</v>
       </c>
       <c r="B111" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655900</v>
+        <v>656007</v>
       </c>
       <c r="R111" t="n">
-        <v>7122796</v>
+        <v>7122964</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12069,10 +12069,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126914200</v>
+        <v>126918410</v>
       </c>
       <c r="B112" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12080,37 +12080,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>655892</v>
+        <v>655904</v>
       </c>
       <c r="R112" t="n">
-        <v>7122864</v>
+        <v>7122985</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12137,19 +12137,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12164,12 +12154,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12180,7 +12170,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126916733</v>
+        <v>126914200</v>
       </c>
       <c r="B113" t="n">
         <v>78777</v>
@@ -12211,17 +12201,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>655793</v>
+        <v>655892</v>
       </c>
       <c r="R113" t="n">
-        <v>7122849</v>
+        <v>7122864</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12248,9 +12238,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12265,12 +12265,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12281,10 +12281,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918410</v>
+        <v>126916733</v>
       </c>
       <c r="B114" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655904</v>
+        <v>655793</v>
       </c>
       <c r="R114" t="n">
-        <v>7122985</v>
+        <v>7122849</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12366,12 +12366,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919792</v>
+        <v>126916316</v>
       </c>
       <c r="B11" t="n">
-        <v>56853</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655919</v>
+        <v>655863</v>
       </c>
       <c r="R11" t="n">
-        <v>7122887</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,11 +1693,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1710,12 +1705,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1726,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918646</v>
+        <v>126918421</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>92813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656298</v>
+        <v>655890</v>
       </c>
       <c r="R12" t="n">
-        <v>7122812</v>
+        <v>7122888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,12 +1806,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1827,32 +1822,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916316</v>
+        <v>126916306</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655863</v>
+        <v>655956</v>
       </c>
       <c r="R13" t="n">
-        <v>7122755</v>
+        <v>7122866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918421</v>
+        <v>126916299</v>
       </c>
       <c r="B14" t="n">
-        <v>92813</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655890</v>
+        <v>655995</v>
       </c>
       <c r="R14" t="n">
-        <v>7122888</v>
+        <v>7122921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,12 +2008,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2029,32 +2024,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916306</v>
+        <v>126919792</v>
       </c>
       <c r="B15" t="n">
-        <v>78685</v>
+        <v>56853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655956</v>
+        <v>655919</v>
       </c>
       <c r="R15" t="n">
-        <v>7122866</v>
+        <v>7122887</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2097,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2114,12 +2114,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916844</v>
+        <v>126916278</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655905</v>
+        <v>655957</v>
       </c>
       <c r="R16" t="n">
-        <v>7122985</v>
+        <v>7122864</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,21 +2198,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2221,36 +2211,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2261,7 +2231,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916278</v>
+        <v>126917770</v>
       </c>
       <c r="B17" t="n">
         <v>79607</v>
@@ -2296,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655957</v>
+        <v>655852</v>
       </c>
       <c r="R17" t="n">
-        <v>7122864</v>
+        <v>7122942</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,12 +2316,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2362,7 +2332,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917770</v>
+        <v>126909344</v>
       </c>
       <c r="B18" t="n">
         <v>79607</v>
@@ -2397,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655852</v>
+        <v>655890</v>
       </c>
       <c r="R18" t="n">
-        <v>7122942</v>
+        <v>7122814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,12 +2417,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2463,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126909344</v>
+        <v>126916844</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,21 +2444,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2498,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655890</v>
+        <v>655905</v>
       </c>
       <c r="R19" t="n">
-        <v>7122814</v>
+        <v>7122985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,11 +2501,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2544,16 +2524,36 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126916299</v>
+        <v>126918646</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>57821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655995</v>
+        <v>656298</v>
       </c>
       <c r="R21" t="n">
-        <v>7122921</v>
+        <v>7122812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918439</v>
+        <v>126918039</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,34 +2792,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655882</v>
+        <v>655917</v>
       </c>
       <c r="R22" t="n">
-        <v>7122978</v>
+        <v>7122980</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,15 +2863,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3084,10 +3099,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126918039</v>
+        <v>126918439</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,34 +3110,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655917</v>
+        <v>655882</v>
       </c>
       <c r="R25" t="n">
-        <v>7122980</v>
+        <v>7122978</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3166,30 +3181,15 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918712</v>
+        <v>126917813</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655899</v>
+        <v>655710</v>
       </c>
       <c r="R28" t="n">
-        <v>7122835</v>
+        <v>7122853</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126910403</v>
+        <v>126918712</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655885</v>
+        <v>655899</v>
       </c>
       <c r="R29" t="n">
-        <v>7122738</v>
+        <v>7122835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126917813</v>
+        <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>79607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655710</v>
+        <v>655885</v>
       </c>
       <c r="R30" t="n">
-        <v>7122853</v>
+        <v>7122738</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3806,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126916288</v>
+        <v>126916289</v>
       </c>
       <c r="B32" t="n">
         <v>78777</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655965</v>
+        <v>655996</v>
       </c>
       <c r="R32" t="n">
-        <v>7122873</v>
+        <v>7122934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916289</v>
+        <v>126916288</v>
       </c>
       <c r="B33" t="n">
         <v>78777</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655996</v>
+        <v>655965</v>
       </c>
       <c r="R33" t="n">
-        <v>7122934</v>
+        <v>7122873</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917825</v>
+        <v>126916272</v>
       </c>
       <c r="B45" t="n">
-        <v>77996</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655749</v>
+        <v>655957</v>
       </c>
       <c r="R45" t="n">
-        <v>7122779</v>
+        <v>7122864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916741</v>
+        <v>126917825</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>77996</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655895</v>
+        <v>655749</v>
       </c>
       <c r="R46" t="n">
-        <v>7122747</v>
+        <v>7122779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126916272</v>
+        <v>126917785</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655957</v>
+        <v>655776</v>
       </c>
       <c r="R47" t="n">
-        <v>7122864</v>
+        <v>7122760</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126917785</v>
+        <v>126919790</v>
       </c>
       <c r="B48" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655776</v>
+        <v>655973</v>
       </c>
       <c r="R48" t="n">
-        <v>7122760</v>
+        <v>7122926</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919790</v>
+        <v>126918406</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655973</v>
+        <v>655901</v>
       </c>
       <c r="R49" t="n">
-        <v>7122926</v>
+        <v>7122844</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918406</v>
+        <v>126916741</v>
       </c>
       <c r="B50" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655901</v>
+        <v>655895</v>
       </c>
       <c r="R50" t="n">
-        <v>7122844</v>
+        <v>7122747</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919778</v>
+        <v>126915088</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,34 +5848,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655919</v>
+        <v>655950</v>
       </c>
       <c r="R52" t="n">
-        <v>7122981</v>
+        <v>7122893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126915088</v>
+        <v>126919778</v>
       </c>
       <c r="B56" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,34 +6252,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655950</v>
+        <v>655919</v>
       </c>
       <c r="R56" t="n">
-        <v>7122893</v>
+        <v>7122981</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R57" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,15 +6424,30 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6443,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B58" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6454,34 +6469,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R58" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6525,30 +6540,15 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -11139,50 +11139,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79607</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R103" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11226,30 +11221,15 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11361,45 +11341,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126916277</v>
+        <v>126918049</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>655921</v>
+        <v>656225</v>
       </c>
       <c r="R105" t="n">
-        <v>7122873</v>
+        <v>7122794</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,15 +11428,30 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126916298</v>
+        <v>126918657</v>
       </c>
       <c r="B106" t="n">
-        <v>78776</v>
+        <v>58091</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R106" t="n">
-        <v>7122796</v>
+        <v>7122774</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126918657</v>
+        <v>126916275</v>
       </c>
       <c r="B107" t="n">
-        <v>58091</v>
+        <v>79607</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R107" t="n">
-        <v>7122774</v>
+        <v>7122800</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126916275</v>
+        <v>126920127</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655900</v>
+        <v>656146</v>
       </c>
       <c r="R108" t="n">
-        <v>7122800</v>
+        <v>7122791</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11743,18 +11743,19 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,10 +11766,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126920127</v>
+        <v>126920120</v>
       </c>
       <c r="B109" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11776,21 +11777,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11800,10 +11801,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>656146</v>
+        <v>655982</v>
       </c>
       <c r="R109" t="n">
-        <v>7122791</v>
+        <v>7122865</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,7 +11845,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11867,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920120</v>
+        <v>126919802</v>
       </c>
       <c r="B110" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11878,21 +11878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11902,10 +11902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>655982</v>
+        <v>656007</v>
       </c>
       <c r="R110" t="n">
-        <v>7122865</v>
+        <v>7122964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11952,12 +11952,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126919802</v>
+        <v>126916298</v>
       </c>
       <c r="B111" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656007</v>
+        <v>655900</v>
       </c>
       <c r="R111" t="n">
-        <v>7122964</v>
+        <v>7122796</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126918405</v>
       </c>
       <c r="B4" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>126916842</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916285</v>
+        <v>126910394</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655855</v>
+        <v>655885</v>
       </c>
       <c r="R6" t="n">
-        <v>7122774</v>
+        <v>7122738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916284</v>
+        <v>126910130</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655943</v>
+        <v>655841</v>
       </c>
       <c r="R7" t="n">
-        <v>7122816</v>
+        <v>7122800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126910130</v>
+        <v>126916285</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655841</v>
+        <v>655855</v>
       </c>
       <c r="R8" t="n">
-        <v>7122800</v>
+        <v>7122774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1392,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         <v>126914199</v>
       </c>
       <c r="B9" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126910394</v>
+        <v>126916284</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655885</v>
+        <v>655943</v>
       </c>
       <c r="R10" t="n">
-        <v>7122738</v>
+        <v>7122816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1623,7 +1623,7 @@
         <v>126916316</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>126918421</v>
       </c>
       <c r="B12" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916306</v>
+        <v>126918044</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1833,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655956</v>
+        <v>656088</v>
       </c>
       <c r="R13" t="n">
-        <v>7122866</v>
+        <v>7122850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,15 +1904,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1923,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126916306</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>655956</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919792</v>
+        <v>126916299</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>78778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655919</v>
+        <v>655995</v>
       </c>
       <c r="R15" t="n">
-        <v>7122887</v>
+        <v>7122921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2112,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2114,12 +2124,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2130,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916278</v>
+        <v>126916844</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655957</v>
+        <v>655905</v>
       </c>
       <c r="R16" t="n">
-        <v>7122864</v>
+        <v>7122985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,11 +2208,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2211,16 +2231,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2231,32 +2271,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917770</v>
+        <v>126919792</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>56855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2266,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655852</v>
+        <v>655919</v>
       </c>
       <c r="R17" t="n">
-        <v>7122942</v>
+        <v>7122887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,6 +2344,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2316,12 +2361,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2332,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126909344</v>
+        <v>126918646</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655890</v>
+        <v>656298</v>
       </c>
       <c r="R18" t="n">
-        <v>7122814</v>
+        <v>7122812</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,12 +2462,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916844</v>
+        <v>126916278</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655905</v>
+        <v>655957</v>
       </c>
       <c r="R19" t="n">
-        <v>7122985</v>
+        <v>7122864</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,21 +2546,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2524,36 +2559,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2564,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918044</v>
+        <v>126917770</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,34 +2590,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656088</v>
+        <v>655852</v>
       </c>
       <c r="R20" t="n">
-        <v>7122850</v>
+        <v>7122942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,30 +2661,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2680,10 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918646</v>
+        <v>126909344</v>
       </c>
       <c r="B21" t="n">
-        <v>57821</v>
+        <v>79609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656298</v>
+        <v>655890</v>
       </c>
       <c r="R21" t="n">
-        <v>7122812</v>
+        <v>7122814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,12 +2765,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918039</v>
+        <v>126910226</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,34 +2792,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655917</v>
+        <v>655873</v>
       </c>
       <c r="R22" t="n">
-        <v>7122980</v>
+        <v>7122775</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,30 +2863,15 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2897,10 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126910226</v>
+        <v>126917790</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655873</v>
+        <v>656241</v>
       </c>
       <c r="R23" t="n">
-        <v>7122775</v>
+        <v>7122853</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2998,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917790</v>
+        <v>126918439</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656241</v>
+        <v>655882</v>
       </c>
       <c r="R24" t="n">
-        <v>7122853</v>
+        <v>7122978</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,12 +3068,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3099,10 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126918439</v>
+        <v>126918039</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3110,34 +3095,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655882</v>
+        <v>655917</v>
       </c>
       <c r="R25" t="n">
-        <v>7122978</v>
+        <v>7122980</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,15 +3166,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3203,7 +3203,7 @@
         <v>126918424</v>
       </c>
       <c r="B26" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>126916397</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917813</v>
+        <v>126918712</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655710</v>
+        <v>655899</v>
       </c>
       <c r="R28" t="n">
-        <v>7122853</v>
+        <v>7122835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,12 +3487,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918712</v>
+        <v>126917813</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655899</v>
+        <v>655710</v>
       </c>
       <c r="R29" t="n">
-        <v>7122835</v>
+        <v>7122853</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3588,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3607,7 +3607,7 @@
         <v>126910403</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918450</v>
+        <v>126916288</v>
       </c>
       <c r="B31" t="n">
-        <v>78685</v>
+        <v>78779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655906</v>
+        <v>655965</v>
       </c>
       <c r="R31" t="n">
-        <v>7122852</v>
+        <v>7122873</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3809,7 +3809,7 @@
         <v>126916289</v>
       </c>
       <c r="B32" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916288</v>
+        <v>126918450</v>
       </c>
       <c r="B33" t="n">
-        <v>78777</v>
+        <v>78687</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655965</v>
+        <v>655906</v>
       </c>
       <c r="R33" t="n">
-        <v>7122873</v>
+        <v>7122852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,10 +4008,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918458</v>
+        <v>126917804</v>
       </c>
       <c r="B34" t="n">
-        <v>78424</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4019,21 +4019,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655914</v>
+        <v>655834</v>
       </c>
       <c r="R34" t="n">
-        <v>7122985</v>
+        <v>7122923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,32 +4109,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126916746</v>
+        <v>126918458</v>
       </c>
       <c r="B35" t="n">
-        <v>91904</v>
+        <v>78426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655785</v>
+        <v>655914</v>
       </c>
       <c r="R35" t="n">
-        <v>7122898</v>
+        <v>7122985</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,44 +4194,48 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126920137</v>
+        <v>126916746</v>
       </c>
       <c r="B36" t="n">
-        <v>78685</v>
+        <v>91906</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>760</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4245,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655990</v>
+        <v>655785</v>
       </c>
       <c r="R36" t="n">
-        <v>7122926</v>
+        <v>7122898</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,26 +4295,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126917804</v>
+        <v>126920137</v>
       </c>
       <c r="B37" t="n">
-        <v>80121</v>
+        <v>78687</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655834</v>
+        <v>655990</v>
       </c>
       <c r="R37" t="n">
-        <v>7122923</v>
+        <v>7122926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>126918438</v>
       </c>
       <c r="B38" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126918037</v>
+        <v>126919804</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>78779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,34 +4520,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655903</v>
+        <v>655989</v>
       </c>
       <c r="R39" t="n">
-        <v>7122984</v>
+        <v>7122922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,30 +4591,15 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4628,7 +4613,7 @@
         <v>126916287</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4726,10 +4711,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919804</v>
+        <v>126918037</v>
       </c>
       <c r="B41" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4737,34 +4722,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655989</v>
+        <v>655903</v>
       </c>
       <c r="R41" t="n">
-        <v>7122922</v>
+        <v>7122984</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,15 +4793,30 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126916304</v>
+        <v>126917830</v>
       </c>
       <c r="B42" t="n">
-        <v>78685</v>
+        <v>78426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4838,21 +4838,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655978</v>
+        <v>655749</v>
       </c>
       <c r="R42" t="n">
-        <v>7122825</v>
+        <v>7122779</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4912,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126920136</v>
+        <v>126916304</v>
       </c>
       <c r="B43" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655941</v>
+        <v>655978</v>
       </c>
       <c r="R43" t="n">
-        <v>7122804</v>
+        <v>7122825</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,12 +5013,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5029,10 +5029,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126917830</v>
+        <v>126920136</v>
       </c>
       <c r="B44" t="n">
-        <v>78424</v>
+        <v>78687</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655749</v>
+        <v>655941</v>
       </c>
       <c r="R44" t="n">
-        <v>7122779</v>
+        <v>7122804</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,12 +5114,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126916272</v>
+        <v>126917825</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>77998</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655957</v>
+        <v>655749</v>
       </c>
       <c r="R45" t="n">
-        <v>7122864</v>
+        <v>7122779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5215,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126917825</v>
+        <v>126916272</v>
       </c>
       <c r="B46" t="n">
-        <v>77996</v>
+        <v>79638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>655749</v>
+        <v>655957</v>
       </c>
       <c r="R46" t="n">
-        <v>7122779</v>
+        <v>7122864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5316,12 +5316,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126917785</v>
+        <v>126919790</v>
       </c>
       <c r="B47" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655776</v>
+        <v>655973</v>
       </c>
       <c r="R47" t="n">
-        <v>7122760</v>
+        <v>7122926</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919790</v>
+        <v>126918406</v>
       </c>
       <c r="B48" t="n">
-        <v>79607</v>
+        <v>78779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655973</v>
+        <v>655901</v>
       </c>
       <c r="R48" t="n">
-        <v>7122926</v>
+        <v>7122844</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126918406</v>
+        <v>126917785</v>
       </c>
       <c r="B49" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>655901</v>
+        <v>655776</v>
       </c>
       <c r="R49" t="n">
-        <v>7122844</v>
+        <v>7122760</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,12 +5619,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5638,7 +5638,7 @@
         <v>126916741</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126910294</v>
+        <v>126919778</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655845</v>
+        <v>655919</v>
       </c>
       <c r="R51" t="n">
-        <v>7122750</v>
+        <v>7122981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126915088</v>
+        <v>126920128</v>
       </c>
       <c r="B52" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5868,14 +5868,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655950</v>
+        <v>655942</v>
       </c>
       <c r="R52" t="n">
-        <v>7122893</v>
+        <v>7122804</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126920128</v>
+        <v>126915088</v>
       </c>
       <c r="B53" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5969,14 +5969,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655942</v>
+        <v>655950</v>
       </c>
       <c r="R53" t="n">
-        <v>7122804</v>
+        <v>7122893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6042,7 +6042,7 @@
         <v>126918672</v>
       </c>
       <c r="B54" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>126918397</v>
       </c>
       <c r="B55" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919778</v>
+        <v>126910294</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655919</v>
+        <v>655845</v>
       </c>
       <c r="R56" t="n">
-        <v>7122981</v>
+        <v>7122750</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126918043</v>
+        <v>126917762</v>
       </c>
       <c r="B57" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6353,34 +6353,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655957</v>
+        <v>655878</v>
       </c>
       <c r="R57" t="n">
-        <v>7122886</v>
+        <v>7122958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,30 +6424,15 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6458,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126917762</v>
+        <v>126918043</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>78779</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6469,34 +6454,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655878</v>
+        <v>655957</v>
       </c>
       <c r="R58" t="n">
-        <v>7122958</v>
+        <v>7122886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,15 +6525,30 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126916745</v>
+        <v>126915955</v>
       </c>
       <c r="B59" t="n">
-        <v>78685</v>
+        <v>92648</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,37 +6570,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655840</v>
+        <v>655885</v>
       </c>
       <c r="R59" t="n">
-        <v>7122839</v>
+        <v>7122754</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6638,28 +6641,33 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>kristina stenmarck</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918047</v>
+        <v>126916274</v>
       </c>
       <c r="B60" t="n">
-        <v>78685</v>
+        <v>79609</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6667,34 +6675,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656203</v>
+        <v>656012</v>
       </c>
       <c r="R60" t="n">
-        <v>7122806</v>
+        <v>7122821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6738,30 +6746,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6772,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917803</v>
+        <v>126917791</v>
       </c>
       <c r="B61" t="n">
-        <v>80121</v>
+        <v>78779</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,21 +6776,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6800,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655792</v>
+        <v>656327</v>
       </c>
       <c r="R61" t="n">
-        <v>7122889</v>
+        <v>7122772</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6873,10 +6866,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126917763</v>
+        <v>126918045</v>
       </c>
       <c r="B62" t="n">
-        <v>79636</v>
+        <v>78779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6884,34 +6877,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656241</v>
+        <v>656177</v>
       </c>
       <c r="R62" t="n">
-        <v>7122853</v>
+        <v>7122815</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6955,15 +6948,30 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6974,10 +6982,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918041</v>
+        <v>126919808</v>
       </c>
       <c r="B63" t="n">
-        <v>92813</v>
+        <v>78779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6985,34 +6993,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>655965</v>
+        <v>655921</v>
       </c>
       <c r="R63" t="n">
-        <v>7122890</v>
+        <v>7122999</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7056,30 +7064,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7090,10 +7083,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126915955</v>
+        <v>126916745</v>
       </c>
       <c r="B64" t="n">
-        <v>92646</v>
+        <v>78687</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7101,40 +7094,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655885</v>
+        <v>655840</v>
       </c>
       <c r="R64" t="n">
-        <v>7122754</v>
+        <v>7122839</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7172,68 +7162,63 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126916312</v>
+        <v>126918047</v>
       </c>
       <c r="B65" t="n">
-        <v>92620</v>
+        <v>78687</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656104</v>
+        <v>656203</v>
       </c>
       <c r="R65" t="n">
-        <v>7122796</v>
+        <v>7122806</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,15 +7262,30 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7296,10 +7296,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917791</v>
+        <v>126918041</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>92815</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7307,34 +7307,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656327</v>
+        <v>655965</v>
       </c>
       <c r="R66" t="n">
-        <v>7122772</v>
+        <v>7122890</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7378,15 +7378,30 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7397,32 +7412,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126916274</v>
+        <v>126916312</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>92622</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7432,10 +7447,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656012</v>
+        <v>656104</v>
       </c>
       <c r="R67" t="n">
-        <v>7122821</v>
+        <v>7122796</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7498,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126919808</v>
+        <v>126917803</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>80123</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7509,21 +7524,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7533,10 +7548,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>655921</v>
+        <v>655792</v>
       </c>
       <c r="R68" t="n">
-        <v>7122999</v>
+        <v>7122889</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7583,12 +7598,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7599,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126918045</v>
+        <v>126917763</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7610,34 +7625,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>656177</v>
+        <v>656241</v>
       </c>
       <c r="R69" t="n">
-        <v>7122815</v>
+        <v>7122853</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,30 +7696,15 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7715,10 +7715,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126916315</v>
+        <v>126918650</v>
       </c>
       <c r="B70" t="n">
-        <v>92620</v>
+        <v>80152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7726,21 +7726,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>655879</v>
+        <v>656291</v>
       </c>
       <c r="R70" t="n">
-        <v>7122817</v>
+        <v>7122816</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,12 +7800,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7816,32 +7816,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918422</v>
+        <v>126917789</v>
       </c>
       <c r="B71" t="n">
-        <v>91491</v>
+        <v>78779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655890</v>
+        <v>655760</v>
       </c>
       <c r="R71" t="n">
-        <v>7122888</v>
+        <v>7122811</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,12 +7901,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7920,7 +7920,7 @@
         <v>126918443</v>
       </c>
       <c r="B72" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8033,32 +8033,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918650</v>
+        <v>126918422</v>
       </c>
       <c r="B73" t="n">
-        <v>80150</v>
+        <v>91493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656291</v>
+        <v>655890</v>
       </c>
       <c r="R73" t="n">
-        <v>7122816</v>
+        <v>7122888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,12 +8118,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,45 +8134,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126918042</v>
+        <v>126916315</v>
       </c>
       <c r="B74" t="n">
-        <v>78424</v>
+        <v>92622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655954</v>
+        <v>655879</v>
       </c>
       <c r="R74" t="n">
-        <v>7122886</v>
+        <v>7122817</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8216,30 +8216,15 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8250,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917789</v>
+        <v>126918042</v>
       </c>
       <c r="B75" t="n">
-        <v>78777</v>
+        <v>78426</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8261,34 +8246,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655760</v>
+        <v>655954</v>
       </c>
       <c r="R75" t="n">
-        <v>7122811</v>
+        <v>7122886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8332,15 +8317,30 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8351,32 +8351,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126915964</v>
+        <v>126916729</v>
       </c>
       <c r="B76" t="n">
-        <v>80121</v>
+        <v>56855</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8386,13 +8386,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655800</v>
+        <v>655892</v>
       </c>
       <c r="R76" t="n">
-        <v>7122929</v>
+        <v>7122748</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8422,6 +8422,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8436,12 +8441,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8452,32 +8457,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126917772</v>
+        <v>126919806</v>
       </c>
       <c r="B77" t="n">
-        <v>80150</v>
+        <v>78779</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,10 +8492,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655768</v>
+        <v>655917</v>
       </c>
       <c r="R77" t="n">
-        <v>7122903</v>
+        <v>7122874</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8537,12 +8542,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8553,10 +8558,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126918050</v>
+        <v>126915963</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8564,37 +8569,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656266</v>
+        <v>655813</v>
       </c>
       <c r="R78" t="n">
-        <v>7122789</v>
+        <v>7122846</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8634,31 +8639,16 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8669,10 +8659,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915970</v>
+        <v>126916286</v>
       </c>
       <c r="B79" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8680,21 +8670,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,13 +8694,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655778</v>
+        <v>655866</v>
       </c>
       <c r="R79" t="n">
-        <v>7122904</v>
+        <v>7122779</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8754,12 +8744,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8770,10 +8760,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916729</v>
+        <v>126917772</v>
       </c>
       <c r="B80" t="n">
-        <v>56853</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,21 +8771,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8805,10 +8795,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655892</v>
+        <v>655768</v>
       </c>
       <c r="R80" t="n">
-        <v>7122748</v>
+        <v>7122903</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,11 +8833,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8860,12 +8845,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8876,10 +8861,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126919806</v>
+        <v>126918050</v>
       </c>
       <c r="B81" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8887,34 +8872,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655917</v>
+        <v>656266</v>
       </c>
       <c r="R81" t="n">
-        <v>7122874</v>
+        <v>7122789</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8958,15 +8943,30 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918404</v>
+        <v>126915970</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>78778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655901</v>
+        <v>655778</v>
       </c>
       <c r="R82" t="n">
-        <v>7122844</v>
+        <v>7122904</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,10 +9078,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915963</v>
+        <v>126915964</v>
       </c>
       <c r="B83" t="n">
-        <v>78777</v>
+        <v>80123</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9089,21 +9089,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655813</v>
+        <v>655800</v>
       </c>
       <c r="R83" t="n">
-        <v>7122846</v>
+        <v>7122929</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916286</v>
+        <v>126918404</v>
       </c>
       <c r="B84" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655866</v>
+        <v>655901</v>
       </c>
       <c r="R84" t="n">
-        <v>7122779</v>
+        <v>7122844</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>126918104</v>
       </c>
       <c r="B85" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126915959</v>
+        <v>126918677</v>
       </c>
       <c r="B86" t="n">
-        <v>92813</v>
+        <v>78779</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,21 +9392,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655849</v>
+        <v>655893</v>
       </c>
       <c r="R86" t="n">
-        <v>7122806</v>
+        <v>7122814</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9466,12 +9466,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9485,7 +9485,7 @@
         <v>126918040</v>
       </c>
       <c r="B87" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9598,10 +9598,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126916394</v>
+        <v>126915959</v>
       </c>
       <c r="B88" t="n">
-        <v>78776</v>
+        <v>92815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9609,21 +9609,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>655798</v>
+        <v>655849</v>
       </c>
       <c r="R88" t="n">
-        <v>7122934</v>
+        <v>7122806</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -9677,7 +9677,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9689,7 +9688,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9700,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126918677</v>
+        <v>126916394</v>
       </c>
       <c r="B89" t="n">
-        <v>78777</v>
+        <v>78778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9711,21 +9710,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9735,13 +9734,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655893</v>
+        <v>655798</v>
       </c>
       <c r="R89" t="n">
-        <v>7122814</v>
+        <v>7122934</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9779,18 +9778,19 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918423</v>
+        <v>126918100</v>
       </c>
       <c r="B90" t="n">
-        <v>92813</v>
+        <v>78779</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,37 +9812,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655881</v>
+        <v>655957</v>
       </c>
       <c r="R90" t="n">
-        <v>7122919</v>
+        <v>7122879</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918038</v>
+        <v>126917788</v>
       </c>
       <c r="B91" t="n">
-        <v>78424</v>
+        <v>78779</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,34 +9913,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655904</v>
+        <v>655780</v>
       </c>
       <c r="R91" t="n">
-        <v>7122984</v>
+        <v>7122780</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9984,30 +9984,15 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10018,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918711</v>
+        <v>126918423</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>92815</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10029,21 +10014,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10053,10 +10038,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655898</v>
+        <v>655881</v>
       </c>
       <c r="R92" t="n">
-        <v>7122802</v>
+        <v>7122919</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10103,12 +10088,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10119,10 +10104,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918100</v>
+        <v>126918038</v>
       </c>
       <c r="B93" t="n">
-        <v>78777</v>
+        <v>78426</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10130,37 +10115,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655957</v>
+        <v>655904</v>
       </c>
       <c r="R93" t="n">
-        <v>7122879</v>
+        <v>7122984</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10200,16 +10185,31 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126917788</v>
+        <v>126918711</v>
       </c>
       <c r="B94" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655780</v>
+        <v>655898</v>
       </c>
       <c r="R94" t="n">
-        <v>7122780</v>
+        <v>7122802</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10321,10 +10321,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918681</v>
+        <v>126915962</v>
       </c>
       <c r="B95" t="n">
-        <v>80121</v>
+        <v>78779</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10332,21 +10332,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656291</v>
+        <v>655854</v>
       </c>
       <c r="R95" t="n">
-        <v>7122808</v>
+        <v>7122777</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918395</v>
+        <v>126916276</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655892</v>
+        <v>655925</v>
       </c>
       <c r="R96" t="n">
-        <v>7122986</v>
+        <v>7122825</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126916276</v>
+        <v>126914201</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10554,17 +10554,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655925</v>
+        <v>655947</v>
       </c>
       <c r="R97" t="n">
-        <v>7122825</v>
+        <v>7122837</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,9 +10591,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10608,12 +10618,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10624,10 +10634,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126914201</v>
+        <v>126918681</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>80123</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10635,37 +10645,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>655947</v>
+        <v>656291</v>
       </c>
       <c r="R98" t="n">
-        <v>7122837</v>
+        <v>7122808</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10692,19 +10702,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10719,12 +10719,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10735,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915962</v>
+        <v>126918395</v>
       </c>
       <c r="B99" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10746,21 +10746,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10770,13 +10770,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655854</v>
+        <v>655892</v>
       </c>
       <c r="R99" t="n">
-        <v>7122777</v>
+        <v>7122986</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10820,12 +10820,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10839,7 +10839,7 @@
         <v>126916313</v>
       </c>
       <c r="B100" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>126918713</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>126918715</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,10 +11139,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126916277</v>
+        <v>126918407</v>
       </c>
       <c r="B103" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11150,21 +11150,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11174,10 +11174,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655921</v>
+        <v>655901</v>
       </c>
       <c r="R103" t="n">
-        <v>7122873</v>
+        <v>7122844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11224,12 +11224,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11240,45 +11240,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918407</v>
+        <v>126918049</v>
       </c>
       <c r="B104" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>655901</v>
+        <v>656225</v>
       </c>
       <c r="R104" t="n">
-        <v>7122844</v>
+        <v>7122794</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11322,15 +11327,30 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11341,50 +11361,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126918049</v>
+        <v>126916277</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656225</v>
+        <v>655921</v>
       </c>
       <c r="R105" t="n">
-        <v>7122794</v>
+        <v>7122873</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11428,30 +11443,15 @@
       <c r="AG105" t="b">
         <v>0</v>
       </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918657</v>
+        <v>126916298</v>
       </c>
       <c r="B106" t="n">
-        <v>58091</v>
+        <v>78778</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11473,21 +11473,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>655908</v>
+        <v>655900</v>
       </c>
       <c r="R106" t="n">
-        <v>7122774</v>
+        <v>7122796</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11566,7 +11566,7 @@
         <v>126916275</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126920127</v>
+        <v>126920120</v>
       </c>
       <c r="B108" t="n">
-        <v>78777</v>
+        <v>79609</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656146</v>
+        <v>655982</v>
       </c>
       <c r="R108" t="n">
-        <v>7122791</v>
+        <v>7122865</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11743,7 +11743,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11766,10 +11765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126920120</v>
+        <v>126919802</v>
       </c>
       <c r="B109" t="n">
-        <v>79607</v>
+        <v>78779</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11777,21 +11776,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11801,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>655982</v>
+        <v>656007</v>
       </c>
       <c r="R109" t="n">
-        <v>7122865</v>
+        <v>7122964</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11851,12 +11850,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11867,10 +11866,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126919802</v>
+        <v>126920127</v>
       </c>
       <c r="B110" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11902,10 +11901,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656007</v>
+        <v>656146</v>
       </c>
       <c r="R110" t="n">
-        <v>7122964</v>
+        <v>7122791</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11946,18 +11945,19 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126916298</v>
+        <v>126918657</v>
       </c>
       <c r="B111" t="n">
-        <v>78776</v>
+        <v>58093</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R111" t="n">
-        <v>7122796</v>
+        <v>7122774</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12072,7 +12072,7 @@
         <v>126918410</v>
       </c>
       <c r="B112" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>126914200</v>
       </c>
       <c r="B113" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>126916733</v>
       </c>
       <c r="B114" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>126950497</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>126950494</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>126950495</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>126950493</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>126950496</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>126950482</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>126950498</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>126914202</v>
       </c>
       <c r="B122" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126916314</v>
+        <v>126918405</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>77998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655893</v>
+        <v>655901</v>
       </c>
       <c r="R3" t="n">
-        <v>7122779</v>
+        <v>7122844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918405</v>
+        <v>126910394</v>
       </c>
       <c r="B4" t="n">
-        <v>77998</v>
+        <v>78778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655901</v>
+        <v>655885</v>
       </c>
       <c r="R4" t="n">
-        <v>7122844</v>
+        <v>7122738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,50 +989,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916842</v>
+        <v>126910130</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>79609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655948</v>
+        <v>655841</v>
       </c>
       <c r="R5" t="n">
-        <v>7122908</v>
+        <v>7122800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,19 +1057,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1105,32 +1090,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126910394</v>
+        <v>126916314</v>
       </c>
       <c r="B6" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655885</v>
+        <v>655893</v>
       </c>
       <c r="R6" t="n">
-        <v>7122738</v>
+        <v>7122779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,12 +1175,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,45 +1191,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126910130</v>
+        <v>126916842</v>
       </c>
       <c r="B7" t="n">
-        <v>79609</v>
+        <v>56855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655841</v>
+        <v>655948</v>
       </c>
       <c r="R7" t="n">
-        <v>7122800</v>
+        <v>7122908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,9 +1264,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1721,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918421</v>
+        <v>126918044</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,34 +1732,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655890</v>
+        <v>656088</v>
       </c>
       <c r="R12" t="n">
-        <v>7122888</v>
+        <v>7122850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,15 +1803,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1822,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918044</v>
+        <v>126916844</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656088</v>
+        <v>655905</v>
       </c>
       <c r="R13" t="n">
-        <v>7122850</v>
+        <v>7122985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,11 +1905,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1914,20 +1939,25 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal tallved</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Gammal tallved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1938,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916306</v>
+        <v>126916299</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>78778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655956</v>
+        <v>655995</v>
       </c>
       <c r="R14" t="n">
-        <v>7122866</v>
+        <v>7122921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,32 +2069,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916299</v>
+        <v>126919792</v>
       </c>
       <c r="B15" t="n">
-        <v>78778</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655995</v>
+        <v>655919</v>
       </c>
       <c r="R15" t="n">
-        <v>7122921</v>
+        <v>7122887</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2142,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2124,12 +2159,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2140,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916844</v>
+        <v>126916306</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,21 +2186,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655905</v>
+        <v>655956</v>
       </c>
       <c r="R16" t="n">
-        <v>7122985</v>
+        <v>7122866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,21 +2243,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2231,36 +2256,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2271,32 +2276,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126919792</v>
+        <v>126918421</v>
       </c>
       <c r="B17" t="n">
-        <v>56855</v>
+        <v>92815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655919</v>
+        <v>655890</v>
       </c>
       <c r="R17" t="n">
-        <v>7122887</v>
+        <v>7122888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,11 +2349,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spilning</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2361,12 +2361,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2478,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916278</v>
+        <v>126917770</v>
       </c>
       <c r="B19" t="n">
         <v>79609</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655957</v>
+        <v>655852</v>
       </c>
       <c r="R19" t="n">
-        <v>7122864</v>
+        <v>7122942</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,12 +2563,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917770</v>
+        <v>126916278</v>
       </c>
       <c r="B20" t="n">
         <v>79609</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655852</v>
+        <v>655957</v>
       </c>
       <c r="R20" t="n">
-        <v>7122942</v>
+        <v>7122864</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,12 +2664,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126910226</v>
+        <v>126918439</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655873</v>
+        <v>655882</v>
       </c>
       <c r="R22" t="n">
-        <v>7122775</v>
+        <v>7122978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2866,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2882,7 +2882,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917790</v>
+        <v>126910226</v>
       </c>
       <c r="B23" t="n">
         <v>78779</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656241</v>
+        <v>655873</v>
       </c>
       <c r="R23" t="n">
-        <v>7122853</v>
+        <v>7122775</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,12 +2967,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2983,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918439</v>
+        <v>126917790</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655882</v>
+        <v>656241</v>
       </c>
       <c r="R24" t="n">
-        <v>7122978</v>
+        <v>7122853</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3200,32 +3200,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126918424</v>
+        <v>126916397</v>
       </c>
       <c r="B26" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655961</v>
+        <v>655893</v>
       </c>
       <c r="R26" t="n">
-        <v>7122865</v>
+        <v>7122752</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3285,12 +3285,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3301,32 +3301,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126916397</v>
+        <v>126918424</v>
       </c>
       <c r="B27" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655893</v>
+        <v>655961</v>
       </c>
       <c r="R27" t="n">
-        <v>7122752</v>
+        <v>7122865</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3386,12 +3386,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126917804</v>
+        <v>126916746</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>91906</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655834</v>
+        <v>655785</v>
       </c>
       <c r="R34" t="n">
-        <v>7122923</v>
+        <v>7122898</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,26 +4093,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918458</v>
+        <v>126920137</v>
       </c>
       <c r="B35" t="n">
-        <v>78426</v>
+        <v>78687</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,21 +4116,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4140,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655914</v>
+        <v>655990</v>
       </c>
       <c r="R35" t="n">
-        <v>7122985</v>
+        <v>7122926</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,12 +4190,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4210,32 +4206,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126916746</v>
+        <v>126917804</v>
       </c>
       <c r="B36" t="n">
-        <v>91906</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4245,10 +4241,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655785</v>
+        <v>655834</v>
       </c>
       <c r="R36" t="n">
-        <v>7122898</v>
+        <v>7122923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,22 +4291,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126920137</v>
+        <v>126918458</v>
       </c>
       <c r="B37" t="n">
-        <v>78687</v>
+        <v>78426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655990</v>
+        <v>655914</v>
       </c>
       <c r="R37" t="n">
-        <v>7122926</v>
+        <v>7122985</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5332,10 +5332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919790</v>
+        <v>126916741</v>
       </c>
       <c r="B47" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>655973</v>
+        <v>655895</v>
       </c>
       <c r="R47" t="n">
-        <v>7122926</v>
+        <v>7122747</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,12 +5417,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5433,10 +5433,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126918406</v>
+        <v>126919790</v>
       </c>
       <c r="B48" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655901</v>
+        <v>655973</v>
       </c>
       <c r="R48" t="n">
-        <v>7122844</v>
+        <v>7122926</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,12 +5518,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126916741</v>
+        <v>126918406</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5646,21 +5646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655895</v>
+        <v>655901</v>
       </c>
       <c r="R50" t="n">
-        <v>7122747</v>
+        <v>7122844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,12 +5720,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919778</v>
+        <v>126910294</v>
       </c>
       <c r="B51" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5747,21 +5747,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655919</v>
+        <v>655845</v>
       </c>
       <c r="R51" t="n">
-        <v>7122981</v>
+        <v>7122750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5821,12 +5821,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5837,10 +5837,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126920128</v>
+        <v>126919778</v>
       </c>
       <c r="B52" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655942</v>
+        <v>655919</v>
       </c>
       <c r="R52" t="n">
-        <v>7122804</v>
+        <v>7122981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,12 +5922,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915088</v>
+        <v>126918397</v>
       </c>
       <c r="B53" t="n">
-        <v>78779</v>
+        <v>78687</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,34 +5949,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655950</v>
+        <v>655892</v>
       </c>
       <c r="R53" t="n">
-        <v>7122893</v>
+        <v>7122986</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918672</v>
+        <v>126920128</v>
       </c>
       <c r="B54" t="n">
         <v>78779</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655882</v>
+        <v>655942</v>
       </c>
       <c r="R54" t="n">
-        <v>7122787</v>
+        <v>7122804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6124,12 +6124,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6140,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918397</v>
+        <v>126915088</v>
       </c>
       <c r="B55" t="n">
-        <v>78687</v>
+        <v>78779</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,34 +6151,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655892</v>
+        <v>655950</v>
       </c>
       <c r="R55" t="n">
-        <v>7122986</v>
+        <v>7122893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,12 +6225,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6241,10 +6241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126910294</v>
+        <v>126918672</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,21 +6252,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655845</v>
+        <v>655882</v>
       </c>
       <c r="R56" t="n">
-        <v>7122750</v>
+        <v>7122787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6326,12 +6326,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126915955</v>
+        <v>126916745</v>
       </c>
       <c r="B59" t="n">
-        <v>92648</v>
+        <v>78687</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,40 +6570,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655885</v>
+        <v>655840</v>
       </c>
       <c r="R59" t="n">
-        <v>7122754</v>
+        <v>7122839</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6641,33 +6638,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126916274</v>
+        <v>126918047</v>
       </c>
       <c r="B60" t="n">
-        <v>79609</v>
+        <v>78687</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6675,34 +6667,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656012</v>
+        <v>656203</v>
       </c>
       <c r="R60" t="n">
-        <v>7122821</v>
+        <v>7122806</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6746,15 +6738,30 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6765,10 +6772,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917791</v>
+        <v>126917803</v>
       </c>
       <c r="B61" t="n">
-        <v>78779</v>
+        <v>80123</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6776,21 +6783,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6800,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656327</v>
+        <v>655792</v>
       </c>
       <c r="R61" t="n">
-        <v>7122772</v>
+        <v>7122889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6866,10 +6873,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918045</v>
+        <v>126917763</v>
       </c>
       <c r="B62" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6877,34 +6884,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656177</v>
+        <v>656241</v>
       </c>
       <c r="R62" t="n">
-        <v>7122815</v>
+        <v>7122853</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6948,30 +6955,15 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6982,32 +6974,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126919808</v>
+        <v>126916312</v>
       </c>
       <c r="B63" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7017,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>655921</v>
+        <v>656104</v>
       </c>
       <c r="R63" t="n">
-        <v>7122999</v>
+        <v>7122796</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7067,12 +7059,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7083,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126916745</v>
+        <v>126915955</v>
       </c>
       <c r="B64" t="n">
-        <v>78687</v>
+        <v>92648</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7094,37 +7086,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>655840</v>
+        <v>655885</v>
       </c>
       <c r="R64" t="n">
-        <v>7122839</v>
+        <v>7122754</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7162,28 +7157,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>kristina stenmarck</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918047</v>
+        <v>126918041</v>
       </c>
       <c r="B65" t="n">
-        <v>78687</v>
+        <v>92815</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656203</v>
+        <v>655965</v>
       </c>
       <c r="R65" t="n">
-        <v>7122806</v>
+        <v>7122890</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7296,10 +7296,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918041</v>
+        <v>126916274</v>
       </c>
       <c r="B66" t="n">
-        <v>92815</v>
+        <v>79609</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7307,34 +7307,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>655965</v>
+        <v>656012</v>
       </c>
       <c r="R66" t="n">
-        <v>7122890</v>
+        <v>7122821</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7378,30 +7378,15 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7412,32 +7397,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126916312</v>
+        <v>126917791</v>
       </c>
       <c r="B67" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7447,10 +7432,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656104</v>
+        <v>656327</v>
       </c>
       <c r="R67" t="n">
-        <v>7122796</v>
+        <v>7122772</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7497,12 +7482,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7513,10 +7498,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917803</v>
+        <v>126918045</v>
       </c>
       <c r="B68" t="n">
-        <v>80123</v>
+        <v>78779</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7524,34 +7509,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>655792</v>
+        <v>656177</v>
       </c>
       <c r="R68" t="n">
-        <v>7122889</v>
+        <v>7122815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7595,15 +7580,30 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7614,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126917763</v>
+        <v>126919808</v>
       </c>
       <c r="B69" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>656241</v>
+        <v>655921</v>
       </c>
       <c r="R69" t="n">
-        <v>7122853</v>
+        <v>7122999</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7699,12 +7699,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7715,32 +7715,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918650</v>
+        <v>126917789</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>78779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>656291</v>
+        <v>655760</v>
       </c>
       <c r="R70" t="n">
-        <v>7122816</v>
+        <v>7122811</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7800,12 +7800,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7816,32 +7816,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917789</v>
+        <v>126916315</v>
       </c>
       <c r="B71" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>655760</v>
+        <v>655879</v>
       </c>
       <c r="R71" t="n">
-        <v>7122811</v>
+        <v>7122817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,12 +7901,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8134,10 +8134,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126916315</v>
+        <v>126918650</v>
       </c>
       <c r="B74" t="n">
-        <v>92622</v>
+        <v>80152</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>655879</v>
+        <v>656291</v>
       </c>
       <c r="R74" t="n">
-        <v>7122817</v>
+        <v>7122816</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8351,45 +8351,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916729</v>
+        <v>126918050</v>
       </c>
       <c r="B76" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655892</v>
+        <v>656266</v>
       </c>
       <c r="R76" t="n">
-        <v>7122748</v>
+        <v>7122789</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,11 +8424,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8437,16 +8432,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8457,10 +8467,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126919806</v>
+        <v>126915964</v>
       </c>
       <c r="B77" t="n">
-        <v>78779</v>
+        <v>80123</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8468,21 +8478,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8492,13 +8502,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655917</v>
+        <v>655800</v>
       </c>
       <c r="R77" t="n">
-        <v>7122874</v>
+        <v>7122929</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8542,12 +8552,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8558,32 +8568,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915963</v>
+        <v>126917772</v>
       </c>
       <c r="B78" t="n">
-        <v>78779</v>
+        <v>80152</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8593,13 +8603,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>655813</v>
+        <v>655768</v>
       </c>
       <c r="R78" t="n">
-        <v>7122846</v>
+        <v>7122903</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8643,12 +8653,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8659,32 +8669,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126916286</v>
+        <v>126916729</v>
       </c>
       <c r="B79" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,10 +8704,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655866</v>
+        <v>655892</v>
       </c>
       <c r="R79" t="n">
-        <v>7122779</v>
+        <v>7122748</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8732,6 +8742,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8744,12 +8759,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8760,32 +8775,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126917772</v>
+        <v>126915963</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>78779</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8795,13 +8810,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>655768</v>
+        <v>655813</v>
       </c>
       <c r="R80" t="n">
-        <v>7122903</v>
+        <v>7122846</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8845,12 +8860,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8861,10 +8876,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918050</v>
+        <v>126916286</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8872,34 +8887,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>656266</v>
+        <v>655866</v>
       </c>
       <c r="R81" t="n">
-        <v>7122789</v>
+        <v>7122779</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8943,30 +8958,15 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8977,10 +8977,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915970</v>
+        <v>126918404</v>
       </c>
       <c r="B82" t="n">
-        <v>78778</v>
+        <v>79609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>655778</v>
+        <v>655901</v>
       </c>
       <c r="R82" t="n">
-        <v>7122904</v>
+        <v>7122844</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9078,10 +9078,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915964</v>
+        <v>126915970</v>
       </c>
       <c r="B83" t="n">
-        <v>80123</v>
+        <v>78778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9089,21 +9089,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>655800</v>
+        <v>655778</v>
       </c>
       <c r="R83" t="n">
-        <v>7122929</v>
+        <v>7122904</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126918404</v>
+        <v>126919806</v>
       </c>
       <c r="B84" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9190,21 +9190,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>655901</v>
+        <v>655917</v>
       </c>
       <c r="R84" t="n">
-        <v>7122844</v>
+        <v>7122874</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9264,12 +9264,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9381,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918677</v>
+        <v>126918040</v>
       </c>
       <c r="B86" t="n">
-        <v>78779</v>
+        <v>78687</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9392,34 +9392,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>655893</v>
+        <v>655945</v>
       </c>
       <c r="R86" t="n">
-        <v>7122814</v>
+        <v>7122909</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9463,15 +9463,30 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9482,10 +9497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126918040</v>
+        <v>126916394</v>
       </c>
       <c r="B87" t="n">
-        <v>78687</v>
+        <v>78778</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9493,37 +9508,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>655945</v>
+        <v>655798</v>
       </c>
       <c r="R87" t="n">
-        <v>7122909</v>
+        <v>7122934</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9561,33 +9576,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9699,10 +9700,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126916394</v>
+        <v>126918677</v>
       </c>
       <c r="B89" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9710,21 +9711,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9734,13 +9735,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655798</v>
+        <v>655893</v>
       </c>
       <c r="R89" t="n">
-        <v>7122934</v>
+        <v>7122814</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9778,19 +9779,18 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918100</v>
+        <v>126918423</v>
       </c>
       <c r="B90" t="n">
-        <v>78779</v>
+        <v>92815</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9812,37 +9812,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>655957</v>
+        <v>655881</v>
       </c>
       <c r="R90" t="n">
-        <v>7122879</v>
+        <v>7122919</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9886,12 +9886,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Peder Winding, Anders Heggestad, Lise Mortensen, Lisa Requin, Carl Jansson, Gunilla R Burke, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9902,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126917788</v>
+        <v>126918711</v>
       </c>
       <c r="B91" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>655780</v>
+        <v>655898</v>
       </c>
       <c r="R91" t="n">
-        <v>7122780</v>
+        <v>7122802</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9987,12 +9987,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10003,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918423</v>
+        <v>126918038</v>
       </c>
       <c r="B92" t="n">
-        <v>92815</v>
+        <v>78426</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10014,34 +10014,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>655881</v>
+        <v>655904</v>
       </c>
       <c r="R92" t="n">
-        <v>7122919</v>
+        <v>7122984</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10085,15 +10085,30 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10104,10 +10119,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918038</v>
+        <v>126918100</v>
       </c>
       <c r="B93" t="n">
-        <v>78426</v>
+        <v>78779</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10115,37 +10130,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>655904</v>
+        <v>655957</v>
       </c>
       <c r="R93" t="n">
-        <v>7122984</v>
+        <v>7122879</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10185,31 +10200,16 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin, Gunilla R Burke, Mattias Dalkvist, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10220,10 +10220,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918711</v>
+        <v>126917788</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>655898</v>
+        <v>655780</v>
       </c>
       <c r="R94" t="n">
-        <v>7122802</v>
+        <v>7122780</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10305,12 +10305,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10321,32 +10321,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126915962</v>
+        <v>126916313</v>
       </c>
       <c r="B95" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>655854</v>
+        <v>656087</v>
       </c>
       <c r="R95" t="n">
-        <v>7122777</v>
+        <v>7122806</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10406,12 +10406,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126916276</v>
+        <v>126918395</v>
       </c>
       <c r="B96" t="n">
-        <v>79609</v>
+        <v>79638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>655925</v>
+        <v>655892</v>
       </c>
       <c r="R96" t="n">
-        <v>7122825</v>
+        <v>7122986</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10507,12 +10507,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10523,10 +10523,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126914201</v>
+        <v>126918681</v>
       </c>
       <c r="B97" t="n">
-        <v>79609</v>
+        <v>80123</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10534,37 +10534,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>655947</v>
+        <v>656291</v>
       </c>
       <c r="R97" t="n">
-        <v>7122837</v>
+        <v>7122808</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10591,19 +10591,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10618,12 +10608,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10634,10 +10624,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918681</v>
+        <v>126918713</v>
       </c>
       <c r="B98" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10645,21 +10635,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10669,10 +10659,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656291</v>
+        <v>656004</v>
       </c>
       <c r="R98" t="n">
-        <v>7122808</v>
+        <v>7122974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10735,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918395</v>
+        <v>126915962</v>
       </c>
       <c r="B99" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10746,21 +10736,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10770,13 +10760,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>655892</v>
+        <v>655854</v>
       </c>
       <c r="R99" t="n">
-        <v>7122986</v>
+        <v>7122777</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10820,12 +10810,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10836,32 +10826,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126916313</v>
+        <v>126916276</v>
       </c>
       <c r="B100" t="n">
-        <v>92622</v>
+        <v>79609</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10871,10 +10861,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656087</v>
+        <v>655925</v>
       </c>
       <c r="R100" t="n">
-        <v>7122806</v>
+        <v>7122825</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10937,10 +10927,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918713</v>
+        <v>126914201</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10948,37 +10938,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656004</v>
+        <v>655947</v>
       </c>
       <c r="R101" t="n">
-        <v>7122974</v>
+        <v>7122837</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11005,9 +10995,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11022,12 +11022,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11038,45 +11038,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918715</v>
+        <v>126918049</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656372</v>
+        <v>656225</v>
       </c>
       <c r="R102" t="n">
-        <v>7122721</v>
+        <v>7122794</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11120,15 +11125,30 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11139,10 +11159,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918407</v>
+        <v>126918715</v>
       </c>
       <c r="B103" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11150,21 +11170,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11174,10 +11194,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>655901</v>
+        <v>656372</v>
       </c>
       <c r="R103" t="n">
-        <v>7122844</v>
+        <v>7122721</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11224,12 +11244,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11240,50 +11260,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918049</v>
+        <v>126918407</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656225</v>
+        <v>655901</v>
       </c>
       <c r="R104" t="n">
-        <v>7122794</v>
+        <v>7122844</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11327,30 +11342,15 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11563,10 +11563,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126916275</v>
+        <v>126918657</v>
       </c>
       <c r="B107" t="n">
-        <v>79609</v>
+        <v>58093</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11574,21 +11574,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>655900</v>
+        <v>655908</v>
       </c>
       <c r="R107" t="n">
-        <v>7122800</v>
+        <v>7122774</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,12 +11648,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126920120</v>
+        <v>126919802</v>
       </c>
       <c r="B108" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>655982</v>
+        <v>656007</v>
       </c>
       <c r="R108" t="n">
-        <v>7122865</v>
+        <v>7122964</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,12 +11749,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11765,7 +11765,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126919802</v>
+        <v>126920127</v>
       </c>
       <c r="B109" t="n">
         <v>78779</v>
@@ -11800,10 +11800,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>656007</v>
+        <v>656146</v>
       </c>
       <c r="R109" t="n">
-        <v>7122964</v>
+        <v>7122791</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11844,18 +11844,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11866,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126920127</v>
+        <v>126916275</v>
       </c>
       <c r="B110" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11877,21 +11878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11901,10 +11902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656146</v>
+        <v>655900</v>
       </c>
       <c r="R110" t="n">
-        <v>7122791</v>
+        <v>7122800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11945,19 +11946,18 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11968,10 +11968,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126918657</v>
+        <v>126920120</v>
       </c>
       <c r="B111" t="n">
-        <v>58093</v>
+        <v>79609</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>655908</v>
+        <v>655982</v>
       </c>
       <c r="R111" t="n">
-        <v>7122774</v>
+        <v>7122865</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12053,12 +12053,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12069,10 +12069,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918410</v>
+        <v>126914200</v>
       </c>
       <c r="B112" t="n">
-        <v>79609</v>
+        <v>78779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12080,37 +12080,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>655904</v>
+        <v>655892</v>
       </c>
       <c r="R112" t="n">
-        <v>7122985</v>
+        <v>7122864</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12137,9 +12137,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12154,12 +12164,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12170,7 +12180,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126914200</v>
+        <v>126916733</v>
       </c>
       <c r="B113" t="n">
         <v>78779</v>
@@ -12201,17 +12211,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>655892</v>
+        <v>655793</v>
       </c>
       <c r="R113" t="n">
-        <v>7122864</v>
+        <v>7122849</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12238,19 +12248,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12265,12 +12265,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12281,10 +12281,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126916733</v>
+        <v>126918410</v>
       </c>
       <c r="B114" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>655793</v>
+        <v>655904</v>
       </c>
       <c r="R114" t="n">
-        <v>7122849</v>
+        <v>7122985</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12366,12 +12366,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13092,7 +13092,7 @@
         <v>126914202</v>
       </c>
       <c r="B122" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13092,7 +13092,7 @@
         <v>126914202</v>
       </c>
       <c r="B122" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13092,7 +13092,7 @@
         <v>126914202</v>
       </c>
       <c r="B122" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13198,6 +13198,112 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129688528</v>
+      </c>
+      <c r="B123" t="n">
+        <v>90614</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>655706</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7122807</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90614</v>
+        <v>90619</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90631</v>
+        <v>90634</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90634</v>
+        <v>90637</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90637</v>
+        <v>90638</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -13203,7 +13203,7 @@
         <v>129688528</v>
       </c>
       <c r="B123" t="n">
-        <v>90638</v>
+        <v>90655</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 28969-2024 artfynd.xlsx
+++ b/artfynd/A 28969-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918405</v>
+        <v>126916314</v>
       </c>
       <c r="B3" t="n">
-        <v>77998</v>
+        <v>92609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655901</v>
+        <v>655893</v>
       </c>
       <c r="R3" t="n">
-        <v>7122844</v>
+        <v>7122779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126910394</v>
+        <v>126918405</v>
       </c>
       <c r="B4" t="n">
-        <v>78778</v>
+        <v>77989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655885</v>
+        <v>655901</v>
       </c>
       <c r="R4" t="n">
-        <v>7122738</v>
+        <v>7122844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126910130</v>
+        <v>126916285</v>
       </c>
       <c r="B5" t="n">
-        <v>79609</v>
+        <v>78770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655841</v>
+        <v>655855</v>
       </c>
       <c r="R5" t="n">
-        <v>7122800</v>
+        <v>7122774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1074,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,48 +1090,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126916314</v>
+        <v>126914199</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>78770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655893</v>
+        <v>655888</v>
       </c>
       <c r="R6" t="n">
-        <v>7122779</v>
+        <v>7122973</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,9 +1158,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,12 +1185,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1191,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916842</v>
+        <v>126916284</v>
       </c>
       <c r="B7" t="n">
-        <v>56855</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655948</v>
+        <v>655943</v>
       </c>
       <c r="R7" t="n">
-        <v>7122908</v>
+        <v>7122816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,19 +1269,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,12 +1286,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126916285</v>
+        <v>126910394</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655855</v>
+        <v>655885</v>
       </c>
       <c r="R8" t="n">
-        <v>7122774</v>
+        <v>7122738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,12 +1387,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1408,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126914199</v>
+        <v>126910130</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,37 +1414,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655888</v>
+        <v>655841</v>
       </c>
       <c r="R9" t="n">
-        <v>7122973</v>
+        <v>7122800</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1476,19 +1471,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1519,45 +1504,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916284</v>
+        <v>126916842</v>
       </c>
       <c r="B10" t="n">
-        <v>78779</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655943</v>
+        <v>655948</v>
       </c>
       <c r="R10" t="n">
-        <v>7122816</v>
+        <v>7122908</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,9 +1577,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,12 +1604,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916316</v>
+        <v>126919792</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655863</v>
+        <v>655919</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1693,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spilning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1705,12 +1710,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1721,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918044</v>
+        <v>126918646</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,34 +1737,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656088</v>
+        <v>656298</v>
       </c>
       <c r="R12" t="n">
-        <v>7122850</v>
+        <v>7122812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,30 +1808,15 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1837,32 +1827,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126916844</v>
+        <v>126916316</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>92609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655905</v>
+        <v>655863</v>
       </c>
       <c r="R13" t="n">
-        <v>7122985</v>
+        <v>7122755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,21 +1895,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1928,36 +1908,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal tallved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallved</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1968,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916299</v>
+        <v>126918421</v>
       </c>
       <c r="B14" t="n">
-        <v>78778</v>
+        <v>92802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655995</v>
+        <v>655890</v>
       </c>
       <c r="R14" t="n">
-        <v>7122921</v>
+        <v>7122888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,12 +2013,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2069,32 +2029,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919792</v>
+        <v>126916306</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>78678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655919</v>
+        <v>655956</v